--- a/research/traditional_assets/database/data/germany/germany_software_internet.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_software_internet.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="xtra_ios" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -351,7 +353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +581,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,31 +590,31 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.139</v>
+        <v>-0.143</v>
       </c>
       <c r="E2">
-        <v>0.343</v>
+        <v>0.773</v>
       </c>
       <c r="F2">
-        <v>0.26</v>
+        <v>0.294</v>
       </c>
       <c r="G2">
-        <v>0.01446291091286814</v>
+        <v>0.1795754576352036</v>
       </c>
       <c r="H2">
-        <v>-0.03341072956128559</v>
+        <v>0.1761779261821</v>
       </c>
       <c r="I2">
-        <v>-0.08899541893452625</v>
+        <v>0.1395262732266498</v>
       </c>
       <c r="J2">
-        <v>-0.08899541893452625</v>
+        <v>0.1286100164784766</v>
       </c>
       <c r="K2">
-        <v>-13.049</v>
+        <v>117.572</v>
       </c>
       <c r="L2">
-        <v>-0.07973237199071247</v>
+        <v>0.07010434678910021</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -621,7 +623,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,79 +632,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>43.72</v>
+        <v>68.8</v>
       </c>
       <c r="V2">
-        <v>0.4104393541119039</v>
+        <v>0.02465022124290141</v>
       </c>
       <c r="W2">
-        <v>0.05048374144720921</v>
+        <v>-0.283271375464684</v>
       </c>
       <c r="X2">
-        <v>0.1168698521002822</v>
+        <v>0.1019964182031853</v>
       </c>
       <c r="Y2">
-        <v>-0.06638611065307297</v>
+        <v>-0.3852677936678693</v>
       </c>
       <c r="Z2">
-        <v>1.303856464941011</v>
+        <v>3.823648995997076</v>
       </c>
       <c r="AA2">
-        <v>-0.1033963718966162</v>
+        <v>-0.06790568236979554</v>
       </c>
       <c r="AB2">
-        <v>0.1122264000659296</v>
+        <v>0.09472289354101426</v>
       </c>
       <c r="AC2">
-        <v>-0.2156227719625458</v>
+        <v>-0.1644823747717802</v>
       </c>
       <c r="AD2">
-        <v>6.86</v>
+        <v>1384</v>
       </c>
       <c r="AE2">
-        <v>0.2099513141228267</v>
+        <v>0.1424358579284049</v>
       </c>
       <c r="AF2">
-        <v>7.069951314122827</v>
+        <v>1384.142435857929</v>
       </c>
       <c r="AG2">
-        <v>-36.65004868587717</v>
+        <v>1315.342435857929</v>
       </c>
       <c r="AH2">
-        <v>0.06224099255550793</v>
+        <v>0.331515841993403</v>
       </c>
       <c r="AI2">
-        <v>0.04816044726741449</v>
+        <v>0.9434403032958352</v>
       </c>
       <c r="AJ2">
-        <v>-0.5245466469713869</v>
+        <v>0.3203158140396098</v>
       </c>
       <c r="AK2">
-        <v>-0.3555497283287502</v>
+        <v>0.9406574636349245</v>
       </c>
       <c r="AL2">
-        <v>0.014</v>
+        <v>96.85299999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.06</v>
+        <v>95.64099999999999</v>
       </c>
       <c r="AN2">
-        <v>-2.044709388971684</v>
+        <v>4.095413669330855</v>
       </c>
       <c r="AO2">
-        <v>-1045.428571428572</v>
+        <v>2.415237524908883</v>
       </c>
       <c r="AP2">
-        <v>10.92400855018694</v>
+        <v>3.892248115363804</v>
       </c>
       <c r="AQ2">
-        <v>243.9333333333334</v>
+        <v>2.445844355454251</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +715,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DCI Database for Commerce and Industry AG (DB:DCIK)</t>
+          <t>IONOS Group SE (XTRA:IOS)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -721,29 +723,26 @@
           <t>Software (Internet)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.135</v>
-      </c>
-      <c r="E3">
-        <v>0.343</v>
+      <c r="F3">
+        <v>0.294</v>
       </c>
       <c r="G3">
-        <v>-0.05961538461538461</v>
+        <v>0.2134892207879975</v>
       </c>
       <c r="H3">
-        <v>-0.1012820512820513</v>
+        <v>0.2134892207879975</v>
       </c>
       <c r="I3">
-        <v>-0.1698655530926701</v>
+        <v>0.1842265324052173</v>
       </c>
       <c r="J3">
-        <v>-0.1698655530926701</v>
+        <v>0.1409859853515272</v>
       </c>
       <c r="K3">
-        <v>0.751</v>
+        <v>155.2</v>
       </c>
       <c r="L3">
-        <v>0.4814102564102564</v>
+        <v>0.1048861255659931</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -767,67 +766,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.62</v>
+        <v>27.4</v>
       </c>
       <c r="V3">
-        <v>0.4354838709677419</v>
+        <v>0.01014101188052852</v>
       </c>
       <c r="W3">
-        <v>0.1800959232613909</v>
+        <v>-1.033288948069241</v>
       </c>
       <c r="X3">
-        <v>0.1166002252502451</v>
+        <v>0.1176967639004739</v>
       </c>
       <c r="Y3">
-        <v>0.06349569801114578</v>
+        <v>-1.150985711969715</v>
       </c>
       <c r="Z3">
-        <v>0.5306210318878858</v>
+        <v>4.096622369878183</v>
       </c>
       <c r="AA3">
-        <v>-0.09013423506423907</v>
+        <v>0.5775663414303844</v>
       </c>
       <c r="AB3">
-        <v>0.112569952821146</v>
+        <v>0.09065227020528253</v>
       </c>
       <c r="AC3">
-        <v>-0.2027041878853851</v>
+        <v>0.4869140712251019</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1373.9</v>
       </c>
       <c r="AE3">
-        <v>0.2099513141228267</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.2099513141228267</v>
+        <v>1373.9</v>
       </c>
       <c r="AG3">
-        <v>-1.410048685877173</v>
+        <v>1346.5</v>
       </c>
       <c r="AH3">
-        <v>0.05342338806293539</v>
+        <v>0.3370871976053781</v>
       </c>
       <c r="AI3">
-        <v>0.04524860282128144</v>
+        <v>1.024457534859444</v>
       </c>
       <c r="AJ3">
-        <v>-0.6104235518975086</v>
+        <v>0.3326005335441162</v>
       </c>
       <c r="AK3">
-        <v>-0.4669110655138941</v>
+        <v>1.024967648626018</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>95.85299999999999</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
+        <v>3.794255730461199</v>
+      </c>
+      <c r="AO3">
+        <v>2.821946169772257</v>
       </c>
       <c r="AP3">
-        <v>6.558365980824062</v>
+        <v>3.718586025959679</v>
+      </c>
+      <c r="AQ3">
+        <v>2.843938113569737</v>
       </c>
     </row>
     <row r="4">
@@ -838,7 +843,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>q.beyond AG (XTRA:QBY)</t>
+          <t>DCI Database for Commerce and Industry AG (DB:DCIK)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -847,28 +852,28 @@
         </is>
       </c>
       <c r="D4">
-        <v>-0.143</v>
-      </c>
-      <c r="F4">
-        <v>0.26</v>
+        <v>-0.157</v>
+      </c>
+      <c r="E4">
+        <v>0.773</v>
       </c>
       <c r="G4">
-        <v>0.01517581739666872</v>
+        <v>-0.3226666666666667</v>
       </c>
       <c r="H4">
-        <v>-0.03275755706354103</v>
+        <v>-0.2213333333333334</v>
       </c>
       <c r="I4">
-        <v>-0.08821714990746453</v>
+        <v>-0.133658114390454</v>
       </c>
       <c r="J4">
-        <v>-0.08821714990746453</v>
+        <v>-0.133658114390454</v>
       </c>
       <c r="K4">
-        <v>-13.8</v>
+        <v>0.472</v>
       </c>
       <c r="L4">
-        <v>-0.08513263417643431</v>
+        <v>0.3146666666666667</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -877,7 +882,7 @@
         <v>-0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P4">
         <v>-0</v>
@@ -886,79 +891,8973 @@
         <v>-0</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S4">
         <v>0</v>
       </c>
       <c r="U4">
-        <v>42.1</v>
+        <v>1.9</v>
       </c>
       <c r="V4">
-        <v>0.4095330739299611</v>
+        <v>0.2695035460992908</v>
       </c>
       <c r="W4">
-        <v>-0.07912844036697247</v>
+        <v>0.1065462753950339</v>
       </c>
       <c r="X4">
-        <v>0.1171394789503192</v>
+        <v>0.09780867554378606</v>
       </c>
       <c r="Y4">
-        <v>-0.1962679193172917</v>
+        <v>0.008737599851247807</v>
       </c>
       <c r="Z4">
-        <v>1.322401696851036</v>
+        <v>0.5080550678084789</v>
       </c>
       <c r="AA4">
-        <v>-0.1166585087289933</v>
+        <v>-0.06790568236979554</v>
       </c>
       <c r="AB4">
-        <v>0.1118828473107133</v>
+        <v>0.09657669240198463</v>
       </c>
       <c r="AC4">
-        <v>-0.2285413560397066</v>
+        <v>-0.1644823747717802</v>
       </c>
       <c r="AD4">
-        <v>6.86</v>
+        <v>0</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>0.1424358579284049</v>
       </c>
       <c r="AF4">
-        <v>6.86</v>
+        <v>0.1424358579284049</v>
       </c>
       <c r="AG4">
-        <v>-35.24</v>
+        <v>-1.757564142071595</v>
       </c>
       <c r="AH4">
-        <v>0.06255699434616087</v>
+        <v>0.01980356317969722</v>
       </c>
       <c r="AI4">
-        <v>0.04825548677546426</v>
+        <v>0.02533347850070194</v>
       </c>
       <c r="AJ4">
-        <v>-0.5216104203670812</v>
+        <v>-0.3320898333493551</v>
       </c>
       <c r="AK4">
-        <v>-0.3521886867879273</v>
+        <v>-0.4721543121631402</v>
       </c>
       <c r="AL4">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>-0.06</v>
+        <v>-0.004</v>
       </c>
       <c r="AN4">
-        <v>-2.184713375796179</v>
-      </c>
-      <c r="AO4">
-        <v>-1021.428571428571</v>
+        <v>-0</v>
       </c>
       <c r="AP4">
-        <v>11.22292993630573</v>
+        <v>10.9165474662832</v>
       </c>
       <c r="AQ4">
-        <v>238.3333333333333</v>
+        <v>69.25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>q.beyond AG (XTRA:QBY)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Software (Internet)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>-0.129</v>
+      </c>
+      <c r="G5">
+        <v>-0.07274119448698316</v>
+      </c>
+      <c r="H5">
+        <v>-0.1026033690658499</v>
+      </c>
+      <c r="I5">
+        <v>-0.1960183767228177</v>
+      </c>
+      <c r="J5">
+        <v>-0.1960183767228177</v>
+      </c>
+      <c r="K5">
+        <v>-38.1</v>
+      </c>
+      <c r="L5">
+        <v>-0.1944869831546708</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>39.5</v>
+      </c>
+      <c r="V5">
+        <v>0.4811205846528624</v>
+      </c>
+      <c r="W5">
+        <v>-0.283271375464684</v>
+      </c>
+      <c r="X5">
+        <v>0.1019964182031853</v>
+      </c>
+      <c r="Y5">
+        <v>-0.3852677936678693</v>
+      </c>
+      <c r="Z5">
+        <v>2.630942788074133</v>
+      </c>
+      <c r="AA5">
+        <v>-0.5157131345688959</v>
+      </c>
+      <c r="AB5">
+        <v>0.09472289354101426</v>
+      </c>
+      <c r="AC5">
+        <v>-0.6104360281099102</v>
+      </c>
+      <c r="AD5">
+        <v>10.1</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>10.1</v>
+      </c>
+      <c r="AG5">
+        <v>-29.4</v>
+      </c>
+      <c r="AH5">
+        <v>0.1095444685466378</v>
+      </c>
+      <c r="AI5">
+        <v>0.08388704318936878</v>
+      </c>
+      <c r="AJ5">
+        <v>-0.5578747628083491</v>
+      </c>
+      <c r="AK5">
+        <v>-0.3634116192830655</v>
+      </c>
+      <c r="AL5">
+        <v>0.253</v>
+      </c>
+      <c r="AM5">
+        <v>-0.208</v>
+      </c>
+      <c r="AN5">
+        <v>-0.4208333333333333</v>
+      </c>
+      <c r="AO5">
+        <v>-151.7786561264822</v>
+      </c>
+      <c r="AP5">
+        <v>1.225</v>
+      </c>
+      <c r="AQ5">
+        <v>184.6153846153846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>IONOS Group SE (XTRA:IOS)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>XTRA:IOS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Software (Internet)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>2.82194616977226</v>
+      </c>
+      <c r="F2">
+        <v>4.60619061159957</v>
+      </c>
+      <c r="G2">
+        <v>3.7942557304612</v>
+      </c>
+      <c r="H2">
+        <v>4.27728251864126</v>
+      </c>
+      <c r="I2">
+        <v>0.337087197605378</v>
+      </c>
+      <c r="J2">
+        <v>0.38</v>
+      </c>
+      <c r="K2">
+        <v>2701.9</v>
+      </c>
+      <c r="L2">
+        <v>2647.95186355185</v>
+      </c>
+      <c r="M2">
+        <v>4048.4</v>
+      </c>
+      <c r="N2">
+        <v>4169.35586355185</v>
+      </c>
+      <c r="O2">
+        <v>1373.9</v>
+      </c>
+      <c r="P2">
+        <v>1548.804</v>
+      </c>
+      <c r="Q2">
+        <v>0.09065227020528251</v>
+      </c>
+      <c r="R2">
+        <v>0.0891480004031695</v>
+      </c>
+      <c r="S2">
+        <v>0.0374668</v>
+      </c>
+      <c r="T2">
+        <v>0.03563</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.117696763900474</v>
+      </c>
+      <c r="X2">
+        <v>0.121949355488983</v>
+      </c>
+      <c r="Y2">
+        <v>1.71514704131465</v>
+      </c>
+      <c r="Z2">
+        <v>1.80759468454311</v>
+      </c>
+      <c r="AA2">
+        <v>1373.9</v>
+      </c>
+      <c r="AB2">
+        <v>0.053524</v>
+      </c>
+      <c r="AC2">
+        <v>2.821946169772257</v>
+      </c>
+      <c r="AD2">
+        <v>1373.9</v>
+      </c>
+      <c r="AE2">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AF2">
+        <v>89.5</v>
+      </c>
+      <c r="AG2">
+        <v>362.1</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>2701.9</v>
+      </c>
+      <c r="AK2">
+        <v>0.046</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.3</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>169.97</v>
+      </c>
+      <c r="AR2">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>27.4</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09698577923608293</v>
+      </c>
+      <c r="C2">
+        <v>3635.132567219591</v>
+      </c>
+      <c r="D2">
+        <v>3607.732567219591</v>
+      </c>
+      <c r="E2">
+        <v>-1373.9</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>27.4</v>
+      </c>
+      <c r="H2">
+        <v>2701.9</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>452.625</v>
+      </c>
+      <c r="K2">
+        <v>89.5</v>
+      </c>
+      <c r="L2">
+        <v>363.125</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>363.125</v>
+      </c>
+      <c r="O2">
+        <v>108.9375</v>
+      </c>
+      <c r="P2">
+        <v>254.1875</v>
+      </c>
+      <c r="Q2">
+        <v>343.6875</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09698577923608293</v>
+      </c>
+      <c r="T2">
+        <v>1.264908244262672</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.3</v>
+      </c>
+      <c r="W2">
+        <v>0.03129</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.0967361218983747</v>
+      </c>
+      <c r="C3">
+        <v>3609.92094620359</v>
+      </c>
+      <c r="D3">
+        <v>3623.27894620359</v>
+      </c>
+      <c r="E3">
+        <v>-1333.142</v>
+      </c>
+      <c r="F3">
+        <v>40.758</v>
+      </c>
+      <c r="G3">
+        <v>27.4</v>
+      </c>
+      <c r="H3">
+        <v>2701.9</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>452.625</v>
+      </c>
+      <c r="K3">
+        <v>89.5</v>
+      </c>
+      <c r="L3">
+        <v>363.125</v>
+      </c>
+      <c r="M3">
+        <v>1.8218826</v>
+      </c>
+      <c r="N3">
+        <v>361.3031174</v>
+      </c>
+      <c r="O3">
+        <v>108.39093522</v>
+      </c>
+      <c r="P3">
+        <v>252.91218218</v>
+      </c>
+      <c r="Q3">
+        <v>342.41218218</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09739719383674211</v>
+      </c>
+      <c r="T3">
+        <v>1.273852039929176</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.3</v>
+      </c>
+      <c r="W3">
+        <v>0.03129</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>199.3130622137782</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09648646456066642</v>
+      </c>
+      <c r="C4">
+        <v>3584.843889426108</v>
+      </c>
+      <c r="D4">
+        <v>3638.959889426108</v>
+      </c>
+      <c r="E4">
+        <v>-1292.384</v>
+      </c>
+      <c r="F4">
+        <v>81.51600000000001</v>
+      </c>
+      <c r="G4">
+        <v>27.4</v>
+      </c>
+      <c r="H4">
+        <v>2701.9</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>452.625</v>
+      </c>
+      <c r="K4">
+        <v>89.5</v>
+      </c>
+      <c r="L4">
+        <v>363.125</v>
+      </c>
+      <c r="M4">
+        <v>3.643765200000001</v>
+      </c>
+      <c r="N4">
+        <v>359.4812348</v>
+      </c>
+      <c r="O4">
+        <v>107.84437044</v>
+      </c>
+      <c r="P4">
+        <v>251.63686436</v>
+      </c>
+      <c r="Q4">
+        <v>341.13686436</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09781700465374125</v>
+      </c>
+      <c r="T4">
+        <v>1.282978362037853</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.3</v>
+      </c>
+      <c r="W4">
+        <v>0.03129</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>99.65653110688908</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09623680722295819</v>
+      </c>
+      <c r="C5">
+        <v>3559.90315159555</v>
+      </c>
+      <c r="D5">
+        <v>3654.77715159555</v>
+      </c>
+      <c r="E5">
+        <v>-1251.626</v>
+      </c>
+      <c r="F5">
+        <v>122.274</v>
+      </c>
+      <c r="G5">
+        <v>27.4</v>
+      </c>
+      <c r="H5">
+        <v>2701.9</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>452.625</v>
+      </c>
+      <c r="K5">
+        <v>89.5</v>
+      </c>
+      <c r="L5">
+        <v>363.125</v>
+      </c>
+      <c r="M5">
+        <v>5.4656478</v>
+      </c>
+      <c r="N5">
+        <v>357.6593522</v>
+      </c>
+      <c r="O5">
+        <v>107.29780566</v>
+      </c>
+      <c r="P5">
+        <v>250.36154654</v>
+      </c>
+      <c r="Q5">
+        <v>339.86154654</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09824547136387442</v>
+      </c>
+      <c r="T5">
+        <v>1.2922928557364</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.3</v>
+      </c>
+      <c r="W5">
+        <v>0.03129</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>66.43768740459274</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09598714988524992</v>
+      </c>
+      <c r="C6">
+        <v>3535.100518061884</v>
+      </c>
+      <c r="D6">
+        <v>3670.732518061884</v>
+      </c>
+      <c r="E6">
+        <v>-1210.868</v>
+      </c>
+      <c r="F6">
+        <v>163.032</v>
+      </c>
+      <c r="G6">
+        <v>27.4</v>
+      </c>
+      <c r="H6">
+        <v>2701.9</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>452.625</v>
+      </c>
+      <c r="K6">
+        <v>89.5</v>
+      </c>
+      <c r="L6">
+        <v>363.125</v>
+      </c>
+      <c r="M6">
+        <v>7.287530400000001</v>
+      </c>
+      <c r="N6">
+        <v>355.8374696</v>
+      </c>
+      <c r="O6">
+        <v>106.75124088</v>
+      </c>
+      <c r="P6">
+        <v>249.08622872</v>
+      </c>
+      <c r="Q6">
+        <v>338.58622872</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.09868286446380201</v>
+      </c>
+      <c r="T6">
+        <v>1.301801401387</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.3</v>
+      </c>
+      <c r="W6">
+        <v>0.03129</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>49.82826555344455</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09573749254754169</v>
+      </c>
+      <c r="C7">
+        <v>3510.437805488411</v>
+      </c>
+      <c r="D7">
+        <v>3686.82780548841</v>
+      </c>
+      <c r="E7">
+        <v>-1170.11</v>
+      </c>
+      <c r="F7">
+        <v>203.79</v>
+      </c>
+      <c r="G7">
+        <v>27.4</v>
+      </c>
+      <c r="H7">
+        <v>2701.9</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>452.625</v>
+      </c>
+      <c r="K7">
+        <v>89.5</v>
+      </c>
+      <c r="L7">
+        <v>363.125</v>
+      </c>
+      <c r="M7">
+        <v>9.109413000000002</v>
+      </c>
+      <c r="N7">
+        <v>354.015587</v>
+      </c>
+      <c r="O7">
+        <v>106.2046761</v>
+      </c>
+      <c r="P7">
+        <v>247.8109109</v>
+      </c>
+      <c r="Q7">
+        <v>337.3109109</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09912946583951757</v>
+      </c>
+      <c r="T7">
+        <v>1.311510126946034</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.3</v>
+      </c>
+      <c r="W7">
+        <v>0.03129</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>39.86261244275563</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09548783520983344</v>
+      </c>
+      <c r="C8">
+        <v>3485.916862541302</v>
+      </c>
+      <c r="D8">
+        <v>3703.064862541302</v>
+      </c>
+      <c r="E8">
+        <v>-1129.352</v>
+      </c>
+      <c r="F8">
+        <v>244.548</v>
+      </c>
+      <c r="G8">
+        <v>27.4</v>
+      </c>
+      <c r="H8">
+        <v>2701.9</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>452.625</v>
+      </c>
+      <c r="K8">
+        <v>89.5</v>
+      </c>
+      <c r="L8">
+        <v>363.125</v>
+      </c>
+      <c r="M8">
+        <v>10.9312956</v>
+      </c>
+      <c r="N8">
+        <v>352.1937044</v>
+      </c>
+      <c r="O8">
+        <v>105.65811132</v>
+      </c>
+      <c r="P8">
+        <v>246.53559308</v>
+      </c>
+      <c r="Q8">
+        <v>336.03559308</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09958556937216323</v>
+      </c>
+      <c r="T8">
+        <v>1.321425421133983</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.3</v>
+      </c>
+      <c r="W8">
+        <v>0.03129</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>33.21884370229637</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09523817787212518</v>
+      </c>
+      <c r="C9">
+        <v>3461.539570597428</v>
+      </c>
+      <c r="D9">
+        <v>3719.445570597428</v>
+      </c>
+      <c r="E9">
+        <v>-1088.594</v>
+      </c>
+      <c r="F9">
+        <v>285.306</v>
+      </c>
+      <c r="G9">
+        <v>27.4</v>
+      </c>
+      <c r="H9">
+        <v>2701.9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>452.625</v>
+      </c>
+      <c r="K9">
+        <v>89.5</v>
+      </c>
+      <c r="L9">
+        <v>363.125</v>
+      </c>
+      <c r="M9">
+        <v>12.7531782</v>
+      </c>
+      <c r="N9">
+        <v>350.3718218</v>
+      </c>
+      <c r="O9">
+        <v>105.11154654</v>
+      </c>
+      <c r="P9">
+        <v>245.26027526</v>
+      </c>
+      <c r="Q9">
+        <v>334.76027526</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1000514815829303</v>
+      </c>
+      <c r="T9">
+        <v>1.331553947455007</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.3</v>
+      </c>
+      <c r="W9">
+        <v>0.03129</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>28.47329460196831</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09498852053441693</v>
+      </c>
+      <c r="C10">
+        <v>3437.307844471063</v>
+      </c>
+      <c r="D10">
+        <v>3735.971844471062</v>
+      </c>
+      <c r="E10">
+        <v>-1047.836</v>
+      </c>
+      <c r="F10">
+        <v>326.064</v>
+      </c>
+      <c r="G10">
+        <v>27.4</v>
+      </c>
+      <c r="H10">
+        <v>2701.9</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>452.625</v>
+      </c>
+      <c r="K10">
+        <v>89.5</v>
+      </c>
+      <c r="L10">
+        <v>363.125</v>
+      </c>
+      <c r="M10">
+        <v>14.5750608</v>
+      </c>
+      <c r="N10">
+        <v>348.5499392</v>
+      </c>
+      <c r="O10">
+        <v>104.56498176</v>
+      </c>
+      <c r="P10">
+        <v>243.98495744</v>
+      </c>
+      <c r="Q10">
+        <v>333.48495744</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1005275223200184</v>
+      </c>
+      <c r="T10">
+        <v>1.341902659130835</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.3</v>
+      </c>
+      <c r="W10">
+        <v>0.03129</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>24.91413277672227</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.0947388631967087</v>
+      </c>
+      <c r="C11">
+        <v>3413.223633160041</v>
+      </c>
+      <c r="D11">
+        <v>3752.645633160041</v>
+      </c>
+      <c r="E11">
+        <v>-1007.078</v>
+      </c>
+      <c r="F11">
+        <v>366.822</v>
+      </c>
+      <c r="G11">
+        <v>27.4</v>
+      </c>
+      <c r="H11">
+        <v>2701.9</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>452.625</v>
+      </c>
+      <c r="K11">
+        <v>89.5</v>
+      </c>
+      <c r="L11">
+        <v>363.125</v>
+      </c>
+      <c r="M11">
+        <v>16.3969434</v>
+      </c>
+      <c r="N11">
+        <v>346.7280566</v>
+      </c>
+      <c r="O11">
+        <v>104.01841698</v>
+      </c>
+      <c r="P11">
+        <v>242.70963962</v>
+      </c>
+      <c r="Q11">
+        <v>332.20963962</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1010140254908887</v>
+      </c>
+      <c r="T11">
+        <v>1.352478815019319</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.3</v>
+      </c>
+      <c r="W11">
+        <v>0.03129</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>22.14589580153091</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09448920585900045</v>
+      </c>
+      <c r="C12">
+        <v>3389.288920611999</v>
+      </c>
+      <c r="D12">
+        <v>3769.468920611999</v>
+      </c>
+      <c r="E12">
+        <v>-966.3200000000001</v>
+      </c>
+      <c r="F12">
+        <v>407.58</v>
+      </c>
+      <c r="G12">
+        <v>27.4</v>
+      </c>
+      <c r="H12">
+        <v>2701.9</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>452.625</v>
+      </c>
+      <c r="K12">
+        <v>89.5</v>
+      </c>
+      <c r="L12">
+        <v>363.125</v>
+      </c>
+      <c r="M12">
+        <v>18.218826</v>
+      </c>
+      <c r="N12">
+        <v>344.906174</v>
+      </c>
+      <c r="O12">
+        <v>103.4718522</v>
+      </c>
+      <c r="P12">
+        <v>241.4343218</v>
+      </c>
+      <c r="Q12">
+        <v>330.9343218</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1015113398433338</v>
+      </c>
+      <c r="T12">
+        <v>1.363289996594214</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.3</v>
+      </c>
+      <c r="W12">
+        <v>0.03129</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>19.93130622137782</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.0942395485212922</v>
+      </c>
+      <c r="C13">
+        <v>3365.505726511303</v>
+      </c>
+      <c r="D13">
+        <v>3786.443726511303</v>
+      </c>
+      <c r="E13">
+        <v>-925.5620000000001</v>
+      </c>
+      <c r="F13">
+        <v>448.338</v>
+      </c>
+      <c r="G13">
+        <v>27.4</v>
+      </c>
+      <c r="H13">
+        <v>2701.9</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>452.625</v>
+      </c>
+      <c r="K13">
+        <v>89.5</v>
+      </c>
+      <c r="L13">
+        <v>363.125</v>
+      </c>
+      <c r="M13">
+        <v>20.0407086</v>
+      </c>
+      <c r="N13">
+        <v>343.0842914</v>
+      </c>
+      <c r="O13">
+        <v>102.92528742</v>
+      </c>
+      <c r="P13">
+        <v>240.15900398</v>
+      </c>
+      <c r="Q13">
+        <v>329.65900398</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1020198297992047</v>
+      </c>
+      <c r="T13">
+        <v>1.374344126069668</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.3</v>
+      </c>
+      <c r="W13">
+        <v>0.03129</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>18.11936929216165</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.09398989118358396</v>
+      </c>
+      <c r="C14">
+        <v>3341.876107087347</v>
+      </c>
+      <c r="D14">
+        <v>3803.572107087346</v>
+      </c>
+      <c r="E14">
+        <v>-884.8040000000001</v>
+      </c>
+      <c r="F14">
+        <v>489.096</v>
+      </c>
+      <c r="G14">
+        <v>27.4</v>
+      </c>
+      <c r="H14">
+        <v>2701.9</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>452.625</v>
+      </c>
+      <c r="K14">
+        <v>89.5</v>
+      </c>
+      <c r="L14">
+        <v>363.125</v>
+      </c>
+      <c r="M14">
+        <v>21.8625912</v>
+      </c>
+      <c r="N14">
+        <v>341.2624088</v>
+      </c>
+      <c r="O14">
+        <v>102.37872264</v>
+      </c>
+      <c r="P14">
+        <v>238.88368616</v>
+      </c>
+      <c r="Q14">
+        <v>328.38368616</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1025398763449818</v>
+      </c>
+      <c r="T14">
+        <v>1.385649485760473</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.3</v>
+      </c>
+      <c r="W14">
+        <v>0.03129</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>16.60942185114818</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09374023384587568</v>
+      </c>
+      <c r="C15">
+        <v>3318.402155944888</v>
+      </c>
+      <c r="D15">
+        <v>3820.856155944889</v>
+      </c>
+      <c r="E15">
+        <v>-844.046</v>
+      </c>
+      <c r="F15">
+        <v>529.854</v>
+      </c>
+      <c r="G15">
+        <v>27.4</v>
+      </c>
+      <c r="H15">
+        <v>2701.9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>452.625</v>
+      </c>
+      <c r="K15">
+        <v>89.5</v>
+      </c>
+      <c r="L15">
+        <v>363.125</v>
+      </c>
+      <c r="M15">
+        <v>23.6844738</v>
+      </c>
+      <c r="N15">
+        <v>339.4405262</v>
+      </c>
+      <c r="O15">
+        <v>101.83215786</v>
+      </c>
+      <c r="P15">
+        <v>237.60836834</v>
+      </c>
+      <c r="Q15">
+        <v>327.10836834</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1030718779837652</v>
+      </c>
+      <c r="T15">
+        <v>1.397214738777504</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.3</v>
+      </c>
+      <c r="W15">
+        <v>0.03129</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>15.33177401644448</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09349057650816744</v>
+      </c>
+      <c r="C16">
+        <v>3295.086004917112</v>
+      </c>
+      <c r="D16">
+        <v>3838.298004917112</v>
+      </c>
+      <c r="E16">
+        <v>-803.288</v>
+      </c>
+      <c r="F16">
+        <v>570.6120000000001</v>
+      </c>
+      <c r="G16">
+        <v>27.4</v>
+      </c>
+      <c r="H16">
+        <v>2701.9</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>452.625</v>
+      </c>
+      <c r="K16">
+        <v>89.5</v>
+      </c>
+      <c r="L16">
+        <v>363.125</v>
+      </c>
+      <c r="M16">
+        <v>25.5063564</v>
+      </c>
+      <c r="N16">
+        <v>337.6186436</v>
+      </c>
+      <c r="O16">
+        <v>101.28559308</v>
+      </c>
+      <c r="P16">
+        <v>236.33305052</v>
+      </c>
+      <c r="Q16">
+        <v>325.83305052</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1036162517536831</v>
+      </c>
+      <c r="T16">
+        <v>1.409048951167023</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.3</v>
+      </c>
+      <c r="W16">
+        <v>0.03129</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>14.23664730098415</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09324091917045919</v>
+      </c>
+      <c r="C17">
+        <v>3271.929824942195</v>
+      </c>
+      <c r="D17">
+        <v>3855.899824942195</v>
+      </c>
+      <c r="E17">
+        <v>-762.5300000000001</v>
+      </c>
+      <c r="F17">
+        <v>611.37</v>
+      </c>
+      <c r="G17">
+        <v>27.4</v>
+      </c>
+      <c r="H17">
+        <v>2701.9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>452.625</v>
+      </c>
+      <c r="K17">
+        <v>89.5</v>
+      </c>
+      <c r="L17">
+        <v>363.125</v>
+      </c>
+      <c r="M17">
+        <v>27.328239</v>
+      </c>
+      <c r="N17">
+        <v>335.796761</v>
+      </c>
+      <c r="O17">
+        <v>100.7390283</v>
+      </c>
+      <c r="P17">
+        <v>235.0577327</v>
+      </c>
+      <c r="Q17">
+        <v>324.5577327</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1041734343181873</v>
+      </c>
+      <c r="T17">
+        <v>1.421161615612767</v>
+      </c>
+      <c r="U17">
+        <v>0.0447</v>
+      </c>
+      <c r="V17">
+        <v>0.3</v>
+      </c>
+      <c r="W17">
+        <v>0.03129</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>13.28753748091855</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09311446183275095</v>
+      </c>
+      <c r="C18">
+        <v>3240.149301840215</v>
+      </c>
+      <c r="D18">
+        <v>3864.877301840215</v>
+      </c>
+      <c r="E18">
+        <v>-721.772</v>
+      </c>
+      <c r="F18">
+        <v>652.128</v>
+      </c>
+      <c r="G18">
+        <v>27.4</v>
+      </c>
+      <c r="H18">
+        <v>2701.9</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>452.625</v>
+      </c>
+      <c r="K18">
+        <v>89.5</v>
+      </c>
+      <c r="L18">
+        <v>363.125</v>
+      </c>
+      <c r="M18">
+        <v>29.8674624</v>
+      </c>
+      <c r="N18">
+        <v>333.2575376</v>
+      </c>
+      <c r="O18">
+        <v>99.97726127999999</v>
+      </c>
+      <c r="P18">
+        <v>233.28027632</v>
+      </c>
+      <c r="Q18">
+        <v>322.78027632</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1047438831342273</v>
+      </c>
+      <c r="T18">
+        <v>1.433562676831029</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.3</v>
+      </c>
+      <c r="W18">
+        <v>0.03206</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>12.1578792043612</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09287250449504271</v>
+      </c>
+      <c r="C19">
+        <v>3216.68540410633</v>
+      </c>
+      <c r="D19">
+        <v>3882.17140410633</v>
+      </c>
+      <c r="E19">
+        <v>-681.014</v>
+      </c>
+      <c r="F19">
+        <v>692.8860000000001</v>
+      </c>
+      <c r="G19">
+        <v>27.4</v>
+      </c>
+      <c r="H19">
+        <v>2701.9</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>452.625</v>
+      </c>
+      <c r="K19">
+        <v>89.5</v>
+      </c>
+      <c r="L19">
+        <v>363.125</v>
+      </c>
+      <c r="M19">
+        <v>31.7341788</v>
+      </c>
+      <c r="N19">
+        <v>331.3908212</v>
+      </c>
+      <c r="O19">
+        <v>99.41724635999999</v>
+      </c>
+      <c r="P19">
+        <v>231.97357484</v>
+      </c>
+      <c r="Q19">
+        <v>321.47357484</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1053280777048707</v>
+      </c>
+      <c r="T19">
+        <v>1.446262558801538</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.3</v>
+      </c>
+      <c r="W19">
+        <v>0.03206</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>11.44270983939877</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09263054715733446</v>
+      </c>
+      <c r="C20">
+        <v>3193.376973302037</v>
+      </c>
+      <c r="D20">
+        <v>3899.620973302037</v>
+      </c>
+      <c r="E20">
+        <v>-640.2560000000001</v>
+      </c>
+      <c r="F20">
+        <v>733.644</v>
+      </c>
+      <c r="G20">
+        <v>27.4</v>
+      </c>
+      <c r="H20">
+        <v>2701.9</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>452.625</v>
+      </c>
+      <c r="K20">
+        <v>89.5</v>
+      </c>
+      <c r="L20">
+        <v>363.125</v>
+      </c>
+      <c r="M20">
+        <v>33.6008952</v>
+      </c>
+      <c r="N20">
+        <v>329.5241048</v>
+      </c>
+      <c r="O20">
+        <v>98.85723143999999</v>
+      </c>
+      <c r="P20">
+        <v>230.66687336</v>
+      </c>
+      <c r="Q20">
+        <v>320.16687336</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1059265209235786</v>
+      </c>
+      <c r="T20">
+        <v>1.459272193990839</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.3</v>
+      </c>
+      <c r="W20">
+        <v>0.03206</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.80700373720995</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09238858981962621</v>
+      </c>
+      <c r="C21">
+        <v>3170.226115269148</v>
+      </c>
+      <c r="D21">
+        <v>3917.228115269148</v>
+      </c>
+      <c r="E21">
+        <v>-599.498</v>
+      </c>
+      <c r="F21">
+        <v>774.402</v>
+      </c>
+      <c r="G21">
+        <v>27.4</v>
+      </c>
+      <c r="H21">
+        <v>2701.9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>452.625</v>
+      </c>
+      <c r="K21">
+        <v>89.5</v>
+      </c>
+      <c r="L21">
+        <v>363.125</v>
+      </c>
+      <c r="M21">
+        <v>35.46761160000001</v>
+      </c>
+      <c r="N21">
+        <v>327.6573884</v>
+      </c>
+      <c r="O21">
+        <v>98.29721651999999</v>
+      </c>
+      <c r="P21">
+        <v>229.36017188</v>
+      </c>
+      <c r="Q21">
+        <v>318.86017188</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.106539740518057</v>
+      </c>
+      <c r="T21">
+        <v>1.47260305474037</v>
+      </c>
+      <c r="U21">
+        <v>0.0458</v>
+      </c>
+      <c r="V21">
+        <v>0.3</v>
+      </c>
+      <c r="W21">
+        <v>0.03206</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>10.23821406683048</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09245463248191797</v>
+      </c>
+      <c r="C22">
+        <v>3124.646459401433</v>
+      </c>
+      <c r="D22">
+        <v>3912.406459401433</v>
+      </c>
+      <c r="E22">
+        <v>-558.74</v>
+      </c>
+      <c r="F22">
+        <v>815.1600000000001</v>
+      </c>
+      <c r="G22">
+        <v>27.4</v>
+      </c>
+      <c r="H22">
+        <v>2701.9</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>452.625</v>
+      </c>
+      <c r="K22">
+        <v>89.5</v>
+      </c>
+      <c r="L22">
+        <v>363.125</v>
+      </c>
+      <c r="M22">
+        <v>39.12768000000001</v>
+      </c>
+      <c r="N22">
+        <v>323.99732</v>
+      </c>
+      <c r="O22">
+        <v>97.199196</v>
+      </c>
+      <c r="P22">
+        <v>226.798124</v>
+      </c>
+      <c r="Q22">
+        <v>316.298124</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1071682906023975</v>
+      </c>
+      <c r="T22">
+        <v>1.48626718700864</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.3</v>
+      </c>
+      <c r="W22">
+        <v>0.0336</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>9.280514459329046</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09222807514420969</v>
+      </c>
+      <c r="C23">
+        <v>3100.478695697279</v>
+      </c>
+      <c r="D23">
+        <v>3928.996695697279</v>
+      </c>
+      <c r="E23">
+        <v>-517.9820000000001</v>
+      </c>
+      <c r="F23">
+        <v>855.918</v>
+      </c>
+      <c r="G23">
+        <v>27.4</v>
+      </c>
+      <c r="H23">
+        <v>2701.9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>452.625</v>
+      </c>
+      <c r="K23">
+        <v>89.5</v>
+      </c>
+      <c r="L23">
+        <v>363.125</v>
+      </c>
+      <c r="M23">
+        <v>41.084064</v>
+      </c>
+      <c r="N23">
+        <v>322.040936</v>
+      </c>
+      <c r="O23">
+        <v>96.61228079999999</v>
+      </c>
+      <c r="P23">
+        <v>225.4286552</v>
+      </c>
+      <c r="Q23">
+        <v>314.9286552</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1078127533471009</v>
+      </c>
+      <c r="T23">
+        <v>1.500277246676106</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.3</v>
+      </c>
+      <c r="W23">
+        <v>0.0336</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.838585199360999</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09200151780650145</v>
+      </c>
+      <c r="C24">
+        <v>3076.452230208741</v>
+      </c>
+      <c r="D24">
+        <v>3945.728230208741</v>
+      </c>
+      <c r="E24">
+        <v>-477.224</v>
+      </c>
+      <c r="F24">
+        <v>896.676</v>
+      </c>
+      <c r="G24">
+        <v>27.4</v>
+      </c>
+      <c r="H24">
+        <v>2701.9</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>452.625</v>
+      </c>
+      <c r="K24">
+        <v>89.5</v>
+      </c>
+      <c r="L24">
+        <v>363.125</v>
+      </c>
+      <c r="M24">
+        <v>43.040448</v>
+      </c>
+      <c r="N24">
+        <v>320.084552</v>
+      </c>
+      <c r="O24">
+        <v>96.02536559999999</v>
+      </c>
+      <c r="P24">
+        <v>224.0591864</v>
+      </c>
+      <c r="Q24">
+        <v>313.5591864</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.108473740777566</v>
+      </c>
+      <c r="T24">
+        <v>1.514646538642739</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.3</v>
+      </c>
+      <c r="W24">
+        <v>0.0336</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>8.436831326662769</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09177496046879322</v>
+      </c>
+      <c r="C25">
+        <v>3052.568875800651</v>
+      </c>
+      <c r="D25">
+        <v>3962.602875800651</v>
+      </c>
+      <c r="E25">
+        <v>-436.466</v>
+      </c>
+      <c r="F25">
+        <v>937.4340000000001</v>
+      </c>
+      <c r="G25">
+        <v>27.4</v>
+      </c>
+      <c r="H25">
+        <v>2701.9</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>452.625</v>
+      </c>
+      <c r="K25">
+        <v>89.5</v>
+      </c>
+      <c r="L25">
+        <v>363.125</v>
+      </c>
+      <c r="M25">
+        <v>44.996832</v>
+      </c>
+      <c r="N25">
+        <v>318.128168</v>
+      </c>
+      <c r="O25">
+        <v>95.43845040000001</v>
+      </c>
+      <c r="P25">
+        <v>222.6897176</v>
+      </c>
+      <c r="Q25">
+        <v>312.1897176</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1091518967127185</v>
+      </c>
+      <c r="T25">
+        <v>1.52938905897214</v>
+      </c>
+      <c r="U25">
+        <v>0.048</v>
+      </c>
+      <c r="V25">
+        <v>0.3</v>
+      </c>
+      <c r="W25">
+        <v>0.0336</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>8.070012573329606</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09180040313108496</v>
+      </c>
+      <c r="C26">
+        <v>3009.908641839978</v>
+      </c>
+      <c r="D26">
+        <v>3960.700641839978</v>
+      </c>
+      <c r="E26">
+        <v>-395.7080000000001</v>
+      </c>
+      <c r="F26">
+        <v>978.192</v>
+      </c>
+      <c r="G26">
+        <v>27.4</v>
+      </c>
+      <c r="H26">
+        <v>2701.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>452.625</v>
+      </c>
+      <c r="K26">
+        <v>89.5</v>
+      </c>
+      <c r="L26">
+        <v>363.125</v>
+      </c>
+      <c r="M26">
+        <v>48.420504</v>
+      </c>
+      <c r="N26">
+        <v>314.704496</v>
+      </c>
+      <c r="O26">
+        <v>94.4113488</v>
+      </c>
+      <c r="P26">
+        <v>220.2931472</v>
+      </c>
+      <c r="Q26">
+        <v>309.7931472</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1098478988566907</v>
+      </c>
+      <c r="T26">
+        <v>1.544519540362842</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.3</v>
+      </c>
+      <c r="W26">
+        <v>0.03465</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>7.499405623700241</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.09158434579337671</v>
+      </c>
+      <c r="C27">
+        <v>2985.362615736275</v>
+      </c>
+      <c r="D27">
+        <v>3976.912615736275</v>
+      </c>
+      <c r="E27">
+        <v>-354.95</v>
+      </c>
+      <c r="F27">
+        <v>1018.95</v>
+      </c>
+      <c r="G27">
+        <v>27.4</v>
+      </c>
+      <c r="H27">
+        <v>2701.9</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>452.625</v>
+      </c>
+      <c r="K27">
+        <v>89.5</v>
+      </c>
+      <c r="L27">
+        <v>363.125</v>
+      </c>
+      <c r="M27">
+        <v>50.438025</v>
+      </c>
+      <c r="N27">
+        <v>312.686975</v>
+      </c>
+      <c r="O27">
+        <v>93.80609250000001</v>
+      </c>
+      <c r="P27">
+        <v>218.8808825</v>
+      </c>
+      <c r="Q27">
+        <v>308.3808825</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1105624610578356</v>
+      </c>
+      <c r="T27">
+        <v>1.560053501257296</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.3</v>
+      </c>
+      <c r="W27">
+        <v>0.03465</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>7.199429398752231</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09136828845566847</v>
+      </c>
+      <c r="C28">
+        <v>2960.949853089378</v>
+      </c>
+      <c r="D28">
+        <v>3993.257853089378</v>
+      </c>
+      <c r="E28">
+        <v>-314.192</v>
+      </c>
+      <c r="F28">
+        <v>1059.708</v>
+      </c>
+      <c r="G28">
+        <v>27.4</v>
+      </c>
+      <c r="H28">
+        <v>2701.9</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>452.625</v>
+      </c>
+      <c r="K28">
+        <v>89.5</v>
+      </c>
+      <c r="L28">
+        <v>363.125</v>
+      </c>
+      <c r="M28">
+        <v>52.45554600000001</v>
+      </c>
+      <c r="N28">
+        <v>310.669454</v>
+      </c>
+      <c r="O28">
+        <v>93.20083619999998</v>
+      </c>
+      <c r="P28">
+        <v>217.4686178</v>
+      </c>
+      <c r="Q28">
+        <v>306.9686178</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1112963357509033</v>
+      </c>
+      <c r="T28">
+        <v>1.576007298932681</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.3</v>
+      </c>
+      <c r="W28">
+        <v>0.03465</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.92252826803099</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09115223111796023</v>
+      </c>
+      <c r="C29">
+        <v>2936.672003831703</v>
+      </c>
+      <c r="D29">
+        <v>4009.738003831703</v>
+      </c>
+      <c r="E29">
+        <v>-273.434</v>
+      </c>
+      <c r="F29">
+        <v>1100.466</v>
+      </c>
+      <c r="G29">
+        <v>27.4</v>
+      </c>
+      <c r="H29">
+        <v>2701.9</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>452.625</v>
+      </c>
+      <c r="K29">
+        <v>89.5</v>
+      </c>
+      <c r="L29">
+        <v>363.125</v>
+      </c>
+      <c r="M29">
+        <v>54.47306700000001</v>
+      </c>
+      <c r="N29">
+        <v>308.651933</v>
+      </c>
+      <c r="O29">
+        <v>92.59557989999999</v>
+      </c>
+      <c r="P29">
+        <v>216.0563531</v>
+      </c>
+      <c r="Q29">
+        <v>305.5563531</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1120503165999455</v>
+      </c>
+      <c r="T29">
+        <v>1.592398186955337</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.3</v>
+      </c>
+      <c r="W29">
+        <v>0.03465</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.666138332177991</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09093617378025197</v>
+      </c>
+      <c r="C30">
+        <v>2912.530745245582</v>
+      </c>
+      <c r="D30">
+        <v>4026.354745245582</v>
+      </c>
+      <c r="E30">
+        <v>-232.6759999999999</v>
+      </c>
+      <c r="F30">
+        <v>1141.224</v>
+      </c>
+      <c r="G30">
+        <v>27.4</v>
+      </c>
+      <c r="H30">
+        <v>2701.9</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>452.625</v>
+      </c>
+      <c r="K30">
+        <v>89.5</v>
+      </c>
+      <c r="L30">
+        <v>363.125</v>
+      </c>
+      <c r="M30">
+        <v>56.49058800000001</v>
+      </c>
+      <c r="N30">
+        <v>306.634412</v>
+      </c>
+      <c r="O30">
+        <v>91.9903236</v>
+      </c>
+      <c r="P30">
+        <v>214.6440884</v>
+      </c>
+      <c r="Q30">
+        <v>304.1440884</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1128252413614611</v>
+      </c>
+      <c r="T30">
+        <v>1.609244377423066</v>
+      </c>
+      <c r="U30">
+        <v>0.0495</v>
+      </c>
+      <c r="V30">
+        <v>0.3</v>
+      </c>
+      <c r="W30">
+        <v>0.03465</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>6.428061963171634</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09072011644254371</v>
+      </c>
+      <c r="C31">
+        <v>2888.527782532324</v>
+      </c>
+      <c r="D31">
+        <v>4043.109782532324</v>
+      </c>
+      <c r="E31">
+        <v>-191.9180000000001</v>
+      </c>
+      <c r="F31">
+        <v>1181.982</v>
+      </c>
+      <c r="G31">
+        <v>27.4</v>
+      </c>
+      <c r="H31">
+        <v>2701.9</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>452.625</v>
+      </c>
+      <c r="K31">
+        <v>89.5</v>
+      </c>
+      <c r="L31">
+        <v>363.125</v>
+      </c>
+      <c r="M31">
+        <v>58.508109</v>
+      </c>
+      <c r="N31">
+        <v>304.616891</v>
+      </c>
+      <c r="O31">
+        <v>91.3850673</v>
+      </c>
+      <c r="P31">
+        <v>213.2318237</v>
+      </c>
+      <c r="Q31">
+        <v>302.7318237</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1136219949894982</v>
+      </c>
+      <c r="T31">
+        <v>1.626565108467352</v>
+      </c>
+      <c r="U31">
+        <v>0.0495</v>
+      </c>
+      <c r="V31">
+        <v>0.3</v>
+      </c>
+      <c r="W31">
+        <v>0.03465</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>6.206404654096751</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09079805910483547</v>
+      </c>
+      <c r="C32">
+        <v>2841.709349781303</v>
+      </c>
+      <c r="D32">
+        <v>4037.049349781303</v>
+      </c>
+      <c r="E32">
+        <v>-151.1600000000001</v>
+      </c>
+      <c r="F32">
+        <v>1222.74</v>
+      </c>
+      <c r="G32">
+        <v>27.4</v>
+      </c>
+      <c r="H32">
+        <v>2701.9</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>452.625</v>
+      </c>
+      <c r="K32">
+        <v>89.5</v>
+      </c>
+      <c r="L32">
+        <v>363.125</v>
+      </c>
+      <c r="M32">
+        <v>62.237466</v>
+      </c>
+      <c r="N32">
+        <v>300.887534</v>
+      </c>
+      <c r="O32">
+        <v>90.2662602</v>
+      </c>
+      <c r="P32">
+        <v>210.6212738</v>
+      </c>
+      <c r="Q32">
+        <v>300.1212738</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1144415130069078</v>
+      </c>
+      <c r="T32">
+        <v>1.644380717541474</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.3</v>
+      </c>
+      <c r="W32">
+        <v>0.03563</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.83450810802612</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09059180176712721</v>
+      </c>
+      <c r="C33">
+        <v>2817.028625000009</v>
+      </c>
+      <c r="D33">
+        <v>4053.126625000009</v>
+      </c>
+      <c r="E33">
+        <v>-110.402</v>
+      </c>
+      <c r="F33">
+        <v>1263.498</v>
+      </c>
+      <c r="G33">
+        <v>27.4</v>
+      </c>
+      <c r="H33">
+        <v>2701.9</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>452.625</v>
+      </c>
+      <c r="K33">
+        <v>89.5</v>
+      </c>
+      <c r="L33">
+        <v>363.125</v>
+      </c>
+      <c r="M33">
+        <v>64.31204820000001</v>
+      </c>
+      <c r="N33">
+        <v>298.8129518</v>
+      </c>
+      <c r="O33">
+        <v>89.64388554</v>
+      </c>
+      <c r="P33">
+        <v>209.16906626</v>
+      </c>
+      <c r="Q33">
+        <v>298.66906626</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1152847851697496</v>
+      </c>
+      <c r="T33">
+        <v>1.662712721081513</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.3</v>
+      </c>
+      <c r="W33">
+        <v>0.03563</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.646298169057536</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09038554442941896</v>
+      </c>
+      <c r="C34">
+        <v>2792.476465537579</v>
+      </c>
+      <c r="D34">
+        <v>4069.33246553758</v>
+      </c>
+      <c r="E34">
+        <v>-69.64400000000001</v>
+      </c>
+      <c r="F34">
+        <v>1304.256</v>
+      </c>
+      <c r="G34">
+        <v>27.4</v>
+      </c>
+      <c r="H34">
+        <v>2701.9</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>452.625</v>
+      </c>
+      <c r="K34">
+        <v>89.5</v>
+      </c>
+      <c r="L34">
+        <v>363.125</v>
+      </c>
+      <c r="M34">
+        <v>66.3866304</v>
+      </c>
+      <c r="N34">
+        <v>296.7383696</v>
+      </c>
+      <c r="O34">
+        <v>89.02151087999999</v>
+      </c>
+      <c r="P34">
+        <v>207.71685872</v>
+      </c>
+      <c r="Q34">
+        <v>297.21685872</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1161528594550279</v>
+      </c>
+      <c r="T34">
+        <v>1.681583901196259</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.3</v>
+      </c>
+      <c r="W34">
+        <v>0.03563</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.469851351274488</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09017928709171072</v>
+      </c>
+      <c r="C35">
+        <v>2768.054419734322</v>
+      </c>
+      <c r="D35">
+        <v>4085.668419734322</v>
+      </c>
+      <c r="E35">
+        <v>-28.88599999999997</v>
+      </c>
+      <c r="F35">
+        <v>1345.014</v>
+      </c>
+      <c r="G35">
+        <v>27.4</v>
+      </c>
+      <c r="H35">
+        <v>2701.9</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>452.625</v>
+      </c>
+      <c r="K35">
+        <v>89.5</v>
+      </c>
+      <c r="L35">
+        <v>363.125</v>
+      </c>
+      <c r="M35">
+        <v>68.46121260000001</v>
+      </c>
+      <c r="N35">
+        <v>294.6637874</v>
+      </c>
+      <c r="O35">
+        <v>88.39913621999999</v>
+      </c>
+      <c r="P35">
+        <v>206.26465118</v>
+      </c>
+      <c r="Q35">
+        <v>295.76465118</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1170468464055384</v>
+      </c>
+      <c r="T35">
+        <v>1.7010184001204</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.3</v>
+      </c>
+      <c r="W35">
+        <v>0.03563</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>5.304098280023745</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.08997302975400245</v>
+      </c>
+      <c r="C36">
+        <v>2743.764060893428</v>
+      </c>
+      <c r="D36">
+        <v>4102.136060893428</v>
+      </c>
+      <c r="E36">
+        <v>11.87200000000007</v>
+      </c>
+      <c r="F36">
+        <v>1385.772</v>
+      </c>
+      <c r="G36">
+        <v>27.4</v>
+      </c>
+      <c r="H36">
+        <v>2701.9</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>452.625</v>
+      </c>
+      <c r="K36">
+        <v>89.5</v>
+      </c>
+      <c r="L36">
+        <v>363.125</v>
+      </c>
+      <c r="M36">
+        <v>70.53579480000001</v>
+      </c>
+      <c r="N36">
+        <v>292.5892052</v>
+      </c>
+      <c r="O36">
+        <v>87.77676156</v>
+      </c>
+      <c r="P36">
+        <v>204.81244364</v>
+      </c>
+      <c r="Q36">
+        <v>294.31244364</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1179679238697007</v>
+      </c>
+      <c r="T36">
+        <v>1.721041823254363</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.3</v>
+      </c>
+      <c r="W36">
+        <v>0.03563</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>5.148095389434812</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.0897667724162942</v>
+      </c>
+      <c r="C37">
+        <v>2719.606987786071</v>
+      </c>
+      <c r="D37">
+        <v>4118.736987786072</v>
+      </c>
+      <c r="E37">
+        <v>52.63000000000011</v>
+      </c>
+      <c r="F37">
+        <v>1426.53</v>
+      </c>
+      <c r="G37">
+        <v>27.4</v>
+      </c>
+      <c r="H37">
+        <v>2701.9</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>452.625</v>
+      </c>
+      <c r="K37">
+        <v>89.5</v>
+      </c>
+      <c r="L37">
+        <v>363.125</v>
+      </c>
+      <c r="M37">
+        <v>72.61037700000001</v>
+      </c>
+      <c r="N37">
+        <v>290.514623</v>
+      </c>
+      <c r="O37">
+        <v>87.15438689999999</v>
+      </c>
+      <c r="P37">
+        <v>203.3602361</v>
+      </c>
+      <c r="Q37">
+        <v>292.8602361</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1189173421789142</v>
+      </c>
+      <c r="T37">
+        <v>1.741681351715526</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.3</v>
+      </c>
+      <c r="W37">
+        <v>0.03563</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>5.001006949736674</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.08956051507858598</v>
+      </c>
+      <c r="C38">
+        <v>2695.584825168847</v>
+      </c>
+      <c r="D38">
+        <v>4135.472825168848</v>
+      </c>
+      <c r="E38">
+        <v>93.38799999999992</v>
+      </c>
+      <c r="F38">
+        <v>1467.288</v>
+      </c>
+      <c r="G38">
+        <v>27.4</v>
+      </c>
+      <c r="H38">
+        <v>2701.9</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>452.625</v>
+      </c>
+      <c r="K38">
+        <v>89.5</v>
+      </c>
+      <c r="L38">
+        <v>363.125</v>
+      </c>
+      <c r="M38">
+        <v>74.68495920000001</v>
+      </c>
+      <c r="N38">
+        <v>288.4400408</v>
+      </c>
+      <c r="O38">
+        <v>86.53201224</v>
+      </c>
+      <c r="P38">
+        <v>201.90802856</v>
+      </c>
+      <c r="Q38">
+        <v>291.40802856</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1198964298102906</v>
+      </c>
+      <c r="T38">
+        <v>1.7629658654411</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.3</v>
+      </c>
+      <c r="W38">
+        <v>0.03563</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.862090090021766</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.08935425774087773</v>
+      </c>
+      <c r="C39">
+        <v>2671.699224313864</v>
+      </c>
+      <c r="D39">
+        <v>4152.345224313864</v>
+      </c>
+      <c r="E39">
+        <v>134.146</v>
+      </c>
+      <c r="F39">
+        <v>1508.046</v>
+      </c>
+      <c r="G39">
+        <v>27.4</v>
+      </c>
+      <c r="H39">
+        <v>2701.9</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>452.625</v>
+      </c>
+      <c r="K39">
+        <v>89.5</v>
+      </c>
+      <c r="L39">
+        <v>363.125</v>
+      </c>
+      <c r="M39">
+        <v>76.7595414</v>
+      </c>
+      <c r="N39">
+        <v>286.3654586</v>
+      </c>
+      <c r="O39">
+        <v>85.90963757999999</v>
+      </c>
+      <c r="P39">
+        <v>200.45582102</v>
+      </c>
+      <c r="Q39">
+        <v>289.95582102</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1209065995886948</v>
+      </c>
+      <c r="T39">
+        <v>1.784926078015104</v>
+      </c>
+      <c r="U39">
+        <v>0.0509</v>
+      </c>
+      <c r="V39">
+        <v>0.3</v>
+      </c>
+      <c r="W39">
+        <v>0.03563</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.730682249750909</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.08914800040316948</v>
+      </c>
+      <c r="C40">
+        <v>2647.951863551854</v>
+      </c>
+      <c r="D40">
+        <v>4169.355863551855</v>
+      </c>
+      <c r="E40">
+        <v>174.904</v>
+      </c>
+      <c r="F40">
+        <v>1548.804</v>
+      </c>
+      <c r="G40">
+        <v>27.4</v>
+      </c>
+      <c r="H40">
+        <v>2701.9</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>452.625</v>
+      </c>
+      <c r="K40">
+        <v>89.5</v>
+      </c>
+      <c r="L40">
+        <v>363.125</v>
+      </c>
+      <c r="M40">
+        <v>78.83412360000001</v>
+      </c>
+      <c r="N40">
+        <v>284.2908764</v>
+      </c>
+      <c r="O40">
+        <v>85.28726292</v>
+      </c>
+      <c r="P40">
+        <v>199.00361348</v>
+      </c>
+      <c r="Q40">
+        <v>288.50361348</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.121949355488983</v>
+      </c>
+      <c r="T40">
+        <v>1.807594684543109</v>
+      </c>
+      <c r="U40">
+        <v>0.0509</v>
+      </c>
+      <c r="V40">
+        <v>0.3</v>
+      </c>
+      <c r="W40">
+        <v>0.03563</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.606190611599568</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.08965154306546122</v>
+      </c>
+      <c r="C41">
+        <v>2565.908025895523</v>
+      </c>
+      <c r="D41">
+        <v>4128.070025895523</v>
+      </c>
+      <c r="E41">
+        <v>215.662</v>
+      </c>
+      <c r="F41">
+        <v>1589.562</v>
+      </c>
+      <c r="G41">
+        <v>27.4</v>
+      </c>
+      <c r="H41">
+        <v>2701.9</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>452.625</v>
+      </c>
+      <c r="K41">
+        <v>89.5</v>
+      </c>
+      <c r="L41">
+        <v>363.125</v>
+      </c>
+      <c r="M41">
+        <v>85.041567</v>
+      </c>
+      <c r="N41">
+        <v>278.083433</v>
+      </c>
+      <c r="O41">
+        <v>83.4250299</v>
+      </c>
+      <c r="P41">
+        <v>194.6584031</v>
+      </c>
+      <c r="Q41">
+        <v>284.1584031</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1230263001073135</v>
+      </c>
+      <c r="T41">
+        <v>1.831006524072032</v>
+      </c>
+      <c r="U41">
+        <v>0.0535</v>
+      </c>
+      <c r="V41">
+        <v>0.3</v>
+      </c>
+      <c r="W41">
+        <v>0.03745</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>4.269970707383602</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.08946348572775298</v>
+      </c>
+      <c r="C42">
+        <v>2540.472971954046</v>
+      </c>
+      <c r="D42">
+        <v>4143.392971954047</v>
+      </c>
+      <c r="E42">
+        <v>256.4200000000001</v>
+      </c>
+      <c r="F42">
+        <v>1630.32</v>
+      </c>
+      <c r="G42">
+        <v>27.4</v>
+      </c>
+      <c r="H42">
+        <v>2701.9</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>452.625</v>
+      </c>
+      <c r="K42">
+        <v>89.5</v>
+      </c>
+      <c r="L42">
+        <v>363.125</v>
+      </c>
+      <c r="M42">
+        <v>87.22212</v>
+      </c>
+      <c r="N42">
+        <v>275.90288</v>
+      </c>
+      <c r="O42">
+        <v>82.77086399999999</v>
+      </c>
+      <c r="P42">
+        <v>193.132016</v>
+      </c>
+      <c r="Q42">
+        <v>282.632016</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1241391428795883</v>
+      </c>
+      <c r="T42">
+        <v>1.85519875825192</v>
+      </c>
+      <c r="U42">
+        <v>0.0535</v>
+      </c>
+      <c r="V42">
+        <v>0.3</v>
+      </c>
+      <c r="W42">
+        <v>0.03745</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>4.163221439699011</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.08927542839004474</v>
+      </c>
+      <c r="C43">
+        <v>2515.152096040711</v>
+      </c>
+      <c r="D43">
+        <v>4158.830096040711</v>
+      </c>
+      <c r="E43">
+        <v>297.1780000000001</v>
+      </c>
+      <c r="F43">
+        <v>1671.078</v>
+      </c>
+      <c r="G43">
+        <v>27.4</v>
+      </c>
+      <c r="H43">
+        <v>2701.9</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>452.625</v>
+      </c>
+      <c r="K43">
+        <v>89.5</v>
+      </c>
+      <c r="L43">
+        <v>363.125</v>
+      </c>
+      <c r="M43">
+        <v>89.40267300000001</v>
+      </c>
+      <c r="N43">
+        <v>273.722327</v>
+      </c>
+      <c r="O43">
+        <v>82.11669809999999</v>
+      </c>
+      <c r="P43">
+        <v>191.6056289</v>
+      </c>
+      <c r="Q43">
+        <v>281.1056289</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.125289709135669</v>
+      </c>
+      <c r="T43">
+        <v>1.880211068166718</v>
+      </c>
+      <c r="U43">
+        <v>0.0535</v>
+      </c>
+      <c r="V43">
+        <v>0.3</v>
+      </c>
+      <c r="W43">
+        <v>0.03745</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>4.06167945336489</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.08988117105233651</v>
+      </c>
+      <c r="C44">
+        <v>2425.076886538726</v>
+      </c>
+      <c r="D44">
+        <v>4109.512886538727</v>
+      </c>
+      <c r="E44">
+        <v>337.9359999999999</v>
+      </c>
+      <c r="F44">
+        <v>1711.836</v>
+      </c>
+      <c r="G44">
+        <v>27.4</v>
+      </c>
+      <c r="H44">
+        <v>2701.9</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>452.625</v>
+      </c>
+      <c r="K44">
+        <v>89.5</v>
+      </c>
+      <c r="L44">
+        <v>363.125</v>
+      </c>
+      <c r="M44">
+        <v>96.20518320000001</v>
+      </c>
+      <c r="N44">
+        <v>266.9198168</v>
+      </c>
+      <c r="O44">
+        <v>80.07594503999999</v>
+      </c>
+      <c r="P44">
+        <v>186.84387176</v>
+      </c>
+      <c r="Q44">
+        <v>276.34387176</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1264799500902353</v>
+      </c>
+      <c r="T44">
+        <v>1.906085871526854</v>
+      </c>
+      <c r="U44">
+        <v>0.0562</v>
+      </c>
+      <c r="V44">
+        <v>0.3</v>
+      </c>
+      <c r="W44">
+        <v>0.03934</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>3.774484782645266</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.08971201371462825</v>
+      </c>
+      <c r="C45">
+        <v>2397.972918435031</v>
+      </c>
+      <c r="D45">
+        <v>4123.166918435031</v>
+      </c>
+      <c r="E45">
+        <v>378.694</v>
+      </c>
+      <c r="F45">
+        <v>1752.594</v>
+      </c>
+      <c r="G45">
+        <v>27.4</v>
+      </c>
+      <c r="H45">
+        <v>2701.9</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>452.625</v>
+      </c>
+      <c r="K45">
+        <v>89.5</v>
+      </c>
+      <c r="L45">
+        <v>363.125</v>
+      </c>
+      <c r="M45">
+        <v>98.4957828</v>
+      </c>
+      <c r="N45">
+        <v>264.6292172</v>
+      </c>
+      <c r="O45">
+        <v>79.38876515999999</v>
+      </c>
+      <c r="P45">
+        <v>185.24045204</v>
+      </c>
+      <c r="Q45">
+        <v>274.74045204</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1277119538853127</v>
+      </c>
+      <c r="T45">
+        <v>1.932868562724189</v>
+      </c>
+      <c r="U45">
+        <v>0.0562</v>
+      </c>
+      <c r="V45">
+        <v>0.3</v>
+      </c>
+      <c r="W45">
+        <v>0.03934</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.686706066769795</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.08954285637692</v>
+      </c>
+      <c r="C46">
+        <v>2370.959985004962</v>
+      </c>
+      <c r="D46">
+        <v>4136.911985004962</v>
+      </c>
+      <c r="E46">
+        <v>419.452</v>
+      </c>
+      <c r="F46">
+        <v>1793.352</v>
+      </c>
+      <c r="G46">
+        <v>27.4</v>
+      </c>
+      <c r="H46">
+        <v>2701.9</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>452.625</v>
+      </c>
+      <c r="K46">
+        <v>89.5</v>
+      </c>
+      <c r="L46">
+        <v>363.125</v>
+      </c>
+      <c r="M46">
+        <v>100.7863824</v>
+      </c>
+      <c r="N46">
+        <v>262.3386176</v>
+      </c>
+      <c r="O46">
+        <v>78.70158528</v>
+      </c>
+      <c r="P46">
+        <v>183.63703232</v>
+      </c>
+      <c r="Q46">
+        <v>273.13703232</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1289879578159285</v>
+      </c>
+      <c r="T46">
+        <v>1.960607778607142</v>
+      </c>
+      <c r="U46">
+        <v>0.0562</v>
+      </c>
+      <c r="V46">
+        <v>0.3</v>
+      </c>
+      <c r="W46">
+        <v>0.03934</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.602917292525027</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.08937369903921173</v>
+      </c>
+      <c r="C47">
+        <v>2344.038999718366</v>
+      </c>
+      <c r="D47">
+        <v>4150.748999718367</v>
+      </c>
+      <c r="E47">
+        <v>460.21</v>
+      </c>
+      <c r="F47">
+        <v>1834.11</v>
+      </c>
+      <c r="G47">
+        <v>27.4</v>
+      </c>
+      <c r="H47">
+        <v>2701.9</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>452.625</v>
+      </c>
+      <c r="K47">
+        <v>89.5</v>
+      </c>
+      <c r="L47">
+        <v>363.125</v>
+      </c>
+      <c r="M47">
+        <v>103.076982</v>
+      </c>
+      <c r="N47">
+        <v>260.048018</v>
+      </c>
+      <c r="O47">
+        <v>78.0144054</v>
+      </c>
+      <c r="P47">
+        <v>182.0336126</v>
+      </c>
+      <c r="Q47">
+        <v>271.5336126</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1303103618894759</v>
+      </c>
+      <c r="T47">
+        <v>1.989355693249476</v>
+      </c>
+      <c r="U47">
+        <v>0.0562</v>
+      </c>
+      <c r="V47">
+        <v>0.3</v>
+      </c>
+      <c r="W47">
+        <v>0.03934</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.522852463802248</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.0907179417015035</v>
+      </c>
+      <c r="C48">
+        <v>2195.811140493867</v>
+      </c>
+      <c r="D48">
+        <v>4043.279140493868</v>
+      </c>
+      <c r="E48">
+        <v>500.9680000000001</v>
+      </c>
+      <c r="F48">
+        <v>1874.868</v>
+      </c>
+      <c r="G48">
+        <v>27.4</v>
+      </c>
+      <c r="H48">
+        <v>2701.9</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>452.625</v>
+      </c>
+      <c r="K48">
+        <v>89.5</v>
+      </c>
+      <c r="L48">
+        <v>363.125</v>
+      </c>
+      <c r="M48">
+        <v>114.1794612</v>
+      </c>
+      <c r="N48">
+        <v>248.9455388</v>
+      </c>
+      <c r="O48">
+        <v>74.68366164</v>
+      </c>
+      <c r="P48">
+        <v>174.26187716</v>
+      </c>
+      <c r="Q48">
+        <v>263.76187716</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1316817438916731</v>
+      </c>
+      <c r="T48">
+        <v>2.019168345471155</v>
+      </c>
+      <c r="U48">
+        <v>0.0609</v>
+      </c>
+      <c r="V48">
+        <v>0.3</v>
+      </c>
+      <c r="W48">
+        <v>0.04263</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>3.180300521509204</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.09058168436379525</v>
+      </c>
+      <c r="C49">
+        <v>2165.692548193015</v>
+      </c>
+      <c r="D49">
+        <v>4053.918548193015</v>
+      </c>
+      <c r="E49">
+        <v>541.7260000000001</v>
+      </c>
+      <c r="F49">
+        <v>1915.626</v>
+      </c>
+      <c r="G49">
+        <v>27.4</v>
+      </c>
+      <c r="H49">
+        <v>2701.9</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>452.625</v>
+      </c>
+      <c r="K49">
+        <v>89.5</v>
+      </c>
+      <c r="L49">
+        <v>363.125</v>
+      </c>
+      <c r="M49">
+        <v>116.6616234</v>
+      </c>
+      <c r="N49">
+        <v>246.4633766</v>
+      </c>
+      <c r="O49">
+        <v>73.93901297999999</v>
+      </c>
+      <c r="P49">
+        <v>172.52436362</v>
+      </c>
+      <c r="Q49">
+        <v>262.02436362</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1331048761581042</v>
+      </c>
+      <c r="T49">
+        <v>2.050106003437048</v>
+      </c>
+      <c r="U49">
+        <v>0.0609</v>
+      </c>
+      <c r="V49">
+        <v>0.3</v>
+      </c>
+      <c r="W49">
+        <v>0.04263</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>3.112634552966455</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.09044542702608699</v>
+      </c>
+      <c r="C50">
+        <v>2135.630096288376</v>
+      </c>
+      <c r="D50">
+        <v>4064.614096288376</v>
+      </c>
+      <c r="E50">
+        <v>582.4839999999999</v>
+      </c>
+      <c r="F50">
+        <v>1956.384</v>
+      </c>
+      <c r="G50">
+        <v>27.4</v>
+      </c>
+      <c r="H50">
+        <v>2701.9</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>452.625</v>
+      </c>
+      <c r="K50">
+        <v>89.5</v>
+      </c>
+      <c r="L50">
+        <v>363.125</v>
+      </c>
+      <c r="M50">
+        <v>119.1437856</v>
+      </c>
+      <c r="N50">
+        <v>243.9812144</v>
+      </c>
+      <c r="O50">
+        <v>73.19436431999999</v>
+      </c>
+      <c r="P50">
+        <v>170.78685008</v>
+      </c>
+      <c r="Q50">
+        <v>260.28685008</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1345827442809365</v>
+      </c>
+      <c r="T50">
+        <v>2.082233571324707</v>
+      </c>
+      <c r="U50">
+        <v>0.0609</v>
+      </c>
+      <c r="V50">
+        <v>0.3</v>
+      </c>
+      <c r="W50">
+        <v>0.04263</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>3.047787999779655</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.09349906968837873</v>
+      </c>
+      <c r="C51">
+        <v>1867.960028480107</v>
+      </c>
+      <c r="D51">
+        <v>3837.702028480107</v>
+      </c>
+      <c r="E51">
+        <v>623.242</v>
+      </c>
+      <c r="F51">
+        <v>1997.142</v>
+      </c>
+      <c r="G51">
+        <v>27.4</v>
+      </c>
+      <c r="H51">
+        <v>2701.9</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>452.625</v>
+      </c>
+      <c r="K51">
+        <v>89.5</v>
+      </c>
+      <c r="L51">
+        <v>363.125</v>
+      </c>
+      <c r="M51">
+        <v>140.1993684</v>
+      </c>
+      <c r="N51">
+        <v>222.9256316</v>
+      </c>
+      <c r="O51">
+        <v>66.87768948</v>
+      </c>
+      <c r="P51">
+        <v>156.04794212</v>
+      </c>
+      <c r="Q51">
+        <v>245.54794212</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1361185680164289</v>
+      </c>
+      <c r="T51">
+        <v>2.115621043835411</v>
+      </c>
+      <c r="U51">
+        <v>0.0702</v>
+      </c>
+      <c r="V51">
+        <v>0.3</v>
+      </c>
+      <c r="W51">
+        <v>0.04914</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.590061596882344</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.09342791235067048</v>
+      </c>
+      <c r="C52">
+        <v>1832.200950231157</v>
+      </c>
+      <c r="D52">
+        <v>3842.700950231157</v>
+      </c>
+      <c r="E52">
+        <v>664</v>
+      </c>
+      <c r="F52">
+        <v>2037.9</v>
+      </c>
+      <c r="G52">
+        <v>27.4</v>
+      </c>
+      <c r="H52">
+        <v>2701.9</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>452.625</v>
+      </c>
+      <c r="K52">
+        <v>89.5</v>
+      </c>
+      <c r="L52">
+        <v>363.125</v>
+      </c>
+      <c r="M52">
+        <v>143.06058</v>
+      </c>
+      <c r="N52">
+        <v>220.06442</v>
+      </c>
+      <c r="O52">
+        <v>66.01932599999999</v>
+      </c>
+      <c r="P52">
+        <v>154.045094</v>
+      </c>
+      <c r="Q52">
+        <v>243.545094</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.137715824701341</v>
+      </c>
+      <c r="T52">
+        <v>2.150344015246543</v>
+      </c>
+      <c r="U52">
+        <v>0.0702</v>
+      </c>
+      <c r="V52">
+        <v>0.3</v>
+      </c>
+      <c r="W52">
+        <v>0.04914</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.538260364944697</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.09503465501296225</v>
+      </c>
+      <c r="C53">
+        <v>1681.648881898341</v>
+      </c>
+      <c r="D53">
+        <v>3732.906881898341</v>
+      </c>
+      <c r="E53">
+        <v>704.7579999999998</v>
+      </c>
+      <c r="F53">
+        <v>2078.658</v>
+      </c>
+      <c r="G53">
+        <v>27.4</v>
+      </c>
+      <c r="H53">
+        <v>2701.9</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>452.625</v>
+      </c>
+      <c r="K53">
+        <v>89.5</v>
+      </c>
+      <c r="L53">
+        <v>363.125</v>
+      </c>
+      <c r="M53">
+        <v>155.6914842</v>
+      </c>
+      <c r="N53">
+        <v>207.4335158</v>
+      </c>
+      <c r="O53">
+        <v>62.23005474</v>
+      </c>
+      <c r="P53">
+        <v>145.20346106</v>
+      </c>
+      <c r="Q53">
+        <v>234.70346106</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1393782755366577</v>
+      </c>
+      <c r="T53">
+        <v>2.186484250796906</v>
+      </c>
+      <c r="U53">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V53">
+        <v>0.3</v>
+      </c>
+      <c r="W53">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.33233694100785</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.09499639767525397</v>
+      </c>
+      <c r="C54">
+        <v>1643.43216719637</v>
+      </c>
+      <c r="D54">
+        <v>3735.44816719637</v>
+      </c>
+      <c r="E54">
+        <v>745.5160000000001</v>
+      </c>
+      <c r="F54">
+        <v>2119.416</v>
+      </c>
+      <c r="G54">
+        <v>27.4</v>
+      </c>
+      <c r="H54">
+        <v>2701.9</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>452.625</v>
+      </c>
+      <c r="K54">
+        <v>89.5</v>
+      </c>
+      <c r="L54">
+        <v>363.125</v>
+      </c>
+      <c r="M54">
+        <v>158.7442584</v>
+      </c>
+      <c r="N54">
+        <v>204.3807416</v>
+      </c>
+      <c r="O54">
+        <v>61.31422248</v>
+      </c>
+      <c r="P54">
+        <v>143.06651912</v>
+      </c>
+      <c r="Q54">
+        <v>232.56651912</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1411099951567791</v>
+      </c>
+      <c r="T54">
+        <v>2.224130329495199</v>
+      </c>
+      <c r="U54">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V54">
+        <v>0.3</v>
+      </c>
+      <c r="W54">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.287484307526929</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.09495814033754574</v>
+      </c>
+      <c r="C55">
+        <v>1605.21891495983</v>
+      </c>
+      <c r="D55">
+        <v>3737.99291495983</v>
+      </c>
+      <c r="E55">
+        <v>786.2739999999999</v>
+      </c>
+      <c r="F55">
+        <v>2160.174</v>
+      </c>
+      <c r="G55">
+        <v>27.4</v>
+      </c>
+      <c r="H55">
+        <v>2701.9</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>452.625</v>
+      </c>
+      <c r="K55">
+        <v>89.5</v>
+      </c>
+      <c r="L55">
+        <v>363.125</v>
+      </c>
+      <c r="M55">
+        <v>161.7970326</v>
+      </c>
+      <c r="N55">
+        <v>201.3279674</v>
+      </c>
+      <c r="O55">
+        <v>60.39839022</v>
+      </c>
+      <c r="P55">
+        <v>140.92957718</v>
+      </c>
+      <c r="Q55">
+        <v>230.42957718</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1429154049735016</v>
+      </c>
+      <c r="T55">
+        <v>2.263378368989165</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.3</v>
+      </c>
+      <c r="W55">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.244324226252837</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.09491988299983749</v>
+      </c>
+      <c r="C56">
+        <v>1567.009132269889</v>
+      </c>
+      <c r="D56">
+        <v>3740.541132269889</v>
+      </c>
+      <c r="E56">
+        <v>827.0320000000002</v>
+      </c>
+      <c r="F56">
+        <v>2200.932</v>
+      </c>
+      <c r="G56">
+        <v>27.4</v>
+      </c>
+      <c r="H56">
+        <v>2701.9</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>452.625</v>
+      </c>
+      <c r="K56">
+        <v>89.5</v>
+      </c>
+      <c r="L56">
+        <v>363.125</v>
+      </c>
+      <c r="M56">
+        <v>164.8498068</v>
+      </c>
+      <c r="N56">
+        <v>198.2751932</v>
+      </c>
+      <c r="O56">
+        <v>59.48255795999999</v>
+      </c>
+      <c r="P56">
+        <v>138.79263524</v>
+      </c>
+      <c r="Q56">
+        <v>228.29263524</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1447993108692119</v>
+      </c>
+      <c r="T56">
+        <v>2.304332844982869</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.3</v>
+      </c>
+      <c r="W56">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.202762666507414</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.09488162566212924</v>
+      </c>
+      <c r="C57">
+        <v>1528.802826227033</v>
+      </c>
+      <c r="D57">
+        <v>3743.092826227033</v>
+      </c>
+      <c r="E57">
+        <v>867.79</v>
+      </c>
+      <c r="F57">
+        <v>2241.69</v>
+      </c>
+      <c r="G57">
+        <v>27.4</v>
+      </c>
+      <c r="H57">
+        <v>2701.9</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>452.625</v>
+      </c>
+      <c r="K57">
+        <v>89.5</v>
+      </c>
+      <c r="L57">
+        <v>363.125</v>
+      </c>
+      <c r="M57">
+        <v>167.902581</v>
+      </c>
+      <c r="N57">
+        <v>195.222419</v>
+      </c>
+      <c r="O57">
+        <v>58.5667257</v>
+      </c>
+      <c r="P57">
+        <v>136.6556933</v>
+      </c>
+      <c r="Q57">
+        <v>226.1556933</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1467669459158428</v>
+      </c>
+      <c r="T57">
+        <v>2.347107519909626</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.3</v>
+      </c>
+      <c r="W57">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.162712436207279</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.09484336832442099</v>
+      </c>
+      <c r="C58">
+        <v>1490.600003951136</v>
+      </c>
+      <c r="D58">
+        <v>3745.648003951137</v>
+      </c>
+      <c r="E58">
+        <v>908.5480000000002</v>
+      </c>
+      <c r="F58">
+        <v>2282.448</v>
+      </c>
+      <c r="G58">
+        <v>27.4</v>
+      </c>
+      <c r="H58">
+        <v>2701.9</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>452.625</v>
+      </c>
+      <c r="K58">
+        <v>89.5</v>
+      </c>
+      <c r="L58">
+        <v>363.125</v>
+      </c>
+      <c r="M58">
+        <v>170.9553552</v>
+      </c>
+      <c r="N58">
+        <v>192.1696448</v>
+      </c>
+      <c r="O58">
+        <v>57.65089343999999</v>
+      </c>
+      <c r="P58">
+        <v>134.51875136</v>
+      </c>
+      <c r="Q58">
+        <v>224.01875136</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1488240189191387</v>
+      </c>
+      <c r="T58">
+        <v>2.391826498242144</v>
+      </c>
+      <c r="U58">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V58">
+        <v>0.3</v>
+      </c>
+      <c r="W58">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>2.124092571275006</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.09480511098671274</v>
+      </c>
+      <c r="C59">
+        <v>1452.400672581529</v>
+      </c>
+      <c r="D59">
+        <v>3748.206672581529</v>
+      </c>
+      <c r="E59">
+        <v>949.306</v>
+      </c>
+      <c r="F59">
+        <v>2323.206</v>
+      </c>
+      <c r="G59">
+        <v>27.4</v>
+      </c>
+      <c r="H59">
+        <v>2701.9</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>452.625</v>
+      </c>
+      <c r="K59">
+        <v>89.5</v>
+      </c>
+      <c r="L59">
+        <v>363.125</v>
+      </c>
+      <c r="M59">
+        <v>174.0081294</v>
+      </c>
+      <c r="N59">
+        <v>189.1168706</v>
+      </c>
+      <c r="O59">
+        <v>56.73506118</v>
+      </c>
+      <c r="P59">
+        <v>132.38180942</v>
+      </c>
+      <c r="Q59">
+        <v>221.88180942</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1509767697365413</v>
+      </c>
+      <c r="T59">
+        <v>2.438625429055245</v>
+      </c>
+      <c r="U59">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V59">
+        <v>0.3</v>
+      </c>
+      <c r="W59">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>2.086827789322813</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.09476685364900449</v>
+      </c>
+      <c r="C60">
+        <v>1414.204839277063</v>
+      </c>
+      <c r="D60">
+        <v>3750.768839277063</v>
+      </c>
+      <c r="E60">
+        <v>990.0639999999999</v>
+      </c>
+      <c r="F60">
+        <v>2363.964</v>
+      </c>
+      <c r="G60">
+        <v>27.4</v>
+      </c>
+      <c r="H60">
+        <v>2701.9</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>452.625</v>
+      </c>
+      <c r="K60">
+        <v>89.5</v>
+      </c>
+      <c r="L60">
+        <v>363.125</v>
+      </c>
+      <c r="M60">
+        <v>177.0609036</v>
+      </c>
+      <c r="N60">
+        <v>186.0640964</v>
+      </c>
+      <c r="O60">
+        <v>55.81922892</v>
+      </c>
+      <c r="P60">
+        <v>130.24486748</v>
+      </c>
+      <c r="Q60">
+        <v>219.74486748</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1532320324976297</v>
+      </c>
+      <c r="T60">
+        <v>2.487652880383255</v>
+      </c>
+      <c r="U60">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V60">
+        <v>0.3</v>
+      </c>
+      <c r="W60">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>2.05084799985173</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.09472859631129624</v>
+      </c>
+      <c r="C61">
+        <v>1376.012511216175</v>
+      </c>
+      <c r="D61">
+        <v>3753.334511216175</v>
+      </c>
+      <c r="E61">
+        <v>1030.822</v>
+      </c>
+      <c r="F61">
+        <v>2404.722</v>
+      </c>
+      <c r="G61">
+        <v>27.4</v>
+      </c>
+      <c r="H61">
+        <v>2701.9</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>452.625</v>
+      </c>
+      <c r="K61">
+        <v>89.5</v>
+      </c>
+      <c r="L61">
+        <v>363.125</v>
+      </c>
+      <c r="M61">
+        <v>180.1136778</v>
+      </c>
+      <c r="N61">
+        <v>183.0113222</v>
+      </c>
+      <c r="O61">
+        <v>54.90339666</v>
+      </c>
+      <c r="P61">
+        <v>128.10792554</v>
+      </c>
+      <c r="Q61">
+        <v>217.60792554</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1555973080763323</v>
+      </c>
+      <c r="T61">
+        <v>2.539071914702876</v>
+      </c>
+      <c r="U61">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V61">
+        <v>0.3</v>
+      </c>
+      <c r="W61">
+        <v>0.05242999999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>2.016087864261022</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.101536338973588</v>
+      </c>
+      <c r="C62">
+        <v>927.9668706572384</v>
+      </c>
+      <c r="D62">
+        <v>3346.046870657238</v>
+      </c>
+      <c r="E62">
+        <v>1071.58</v>
+      </c>
+      <c r="F62">
+        <v>2445.48</v>
+      </c>
+      <c r="G62">
+        <v>27.4</v>
+      </c>
+      <c r="H62">
+        <v>2701.9</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>452.625</v>
+      </c>
+      <c r="K62">
+        <v>89.5</v>
+      </c>
+      <c r="L62">
+        <v>363.125</v>
+      </c>
+      <c r="M62">
+        <v>223.027776</v>
+      </c>
+      <c r="N62">
+        <v>140.097224</v>
+      </c>
+      <c r="O62">
+        <v>42.0291672</v>
+      </c>
+      <c r="P62">
+        <v>98.06805679999999</v>
+      </c>
+      <c r="Q62">
+        <v>187.5680568</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.15808084743397</v>
+      </c>
+      <c r="T62">
+        <v>2.593061900738478</v>
+      </c>
+      <c r="U62">
+        <v>0.0912</v>
+      </c>
+      <c r="V62">
+        <v>0.3</v>
+      </c>
+      <c r="W62">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>1.628160431461236</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1016121816358798</v>
+      </c>
+      <c r="C63">
+        <v>883.1686813784318</v>
+      </c>
+      <c r="D63">
+        <v>3342.006681378432</v>
+      </c>
+      <c r="E63">
+        <v>1112.338</v>
+      </c>
+      <c r="F63">
+        <v>2486.238</v>
+      </c>
+      <c r="G63">
+        <v>27.4</v>
+      </c>
+      <c r="H63">
+        <v>2701.9</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>452.625</v>
+      </c>
+      <c r="K63">
+        <v>89.5</v>
+      </c>
+      <c r="L63">
+        <v>363.125</v>
+      </c>
+      <c r="M63">
+        <v>226.7449056</v>
+      </c>
+      <c r="N63">
+        <v>136.3800944</v>
+      </c>
+      <c r="O63">
+        <v>40.91402831999999</v>
+      </c>
+      <c r="P63">
+        <v>95.46606607999998</v>
+      </c>
+      <c r="Q63">
+        <v>184.96606608</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1606917477843071</v>
+      </c>
+      <c r="T63">
+        <v>2.649820604006675</v>
+      </c>
+      <c r="U63">
+        <v>0.0912</v>
+      </c>
+      <c r="V63">
+        <v>0.3</v>
+      </c>
+      <c r="W63">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>1.601469276847117</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1016880242981715</v>
+      </c>
+      <c r="C64">
+        <v>838.3802369982627</v>
+      </c>
+      <c r="D64">
+        <v>3337.976236998263</v>
+      </c>
+      <c r="E64">
+        <v>1153.096</v>
+      </c>
+      <c r="F64">
+        <v>2526.996</v>
+      </c>
+      <c r="G64">
+        <v>27.4</v>
+      </c>
+      <c r="H64">
+        <v>2701.9</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>452.625</v>
+      </c>
+      <c r="K64">
+        <v>89.5</v>
+      </c>
+      <c r="L64">
+        <v>363.125</v>
+      </c>
+      <c r="M64">
+        <v>230.4620352</v>
+      </c>
+      <c r="N64">
+        <v>132.6629648</v>
+      </c>
+      <c r="O64">
+        <v>39.79888943999999</v>
+      </c>
+      <c r="P64">
+        <v>92.86407535999999</v>
+      </c>
+      <c r="Q64">
+        <v>182.36407536</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1634400639425566</v>
+      </c>
+      <c r="T64">
+        <v>2.709566607446882</v>
+      </c>
+      <c r="U64">
+        <v>0.0912</v>
+      </c>
+      <c r="V64">
+        <v>0.3</v>
+      </c>
+      <c r="W64">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>1.575639127220551</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1017638669604633</v>
+      </c>
+      <c r="C65">
+        <v>793.6015023022896</v>
+      </c>
+      <c r="D65">
+        <v>3333.955502302289</v>
+      </c>
+      <c r="E65">
+        <v>1193.854</v>
+      </c>
+      <c r="F65">
+        <v>2567.754</v>
+      </c>
+      <c r="G65">
+        <v>27.4</v>
+      </c>
+      <c r="H65">
+        <v>2701.9</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>452.625</v>
+      </c>
+      <c r="K65">
+        <v>89.5</v>
+      </c>
+      <c r="L65">
+        <v>363.125</v>
+      </c>
+      <c r="M65">
+        <v>234.1791648</v>
+      </c>
+      <c r="N65">
+        <v>128.9458352</v>
+      </c>
+      <c r="O65">
+        <v>38.68375056</v>
+      </c>
+      <c r="P65">
+        <v>90.26208464000001</v>
+      </c>
+      <c r="Q65">
+        <v>179.76208464</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1663369377309818</v>
+      </c>
+      <c r="T65">
+        <v>2.772542124586561</v>
+      </c>
+      <c r="U65">
+        <v>0.0912</v>
+      </c>
+      <c r="V65">
+        <v>0.3</v>
+      </c>
+      <c r="W65">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>1.550628982344035</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.101839709622755</v>
+      </c>
+      <c r="C66">
+        <v>748.8324422455416</v>
+      </c>
+      <c r="D66">
+        <v>3329.944442245542</v>
+      </c>
+      <c r="E66">
+        <v>1234.612</v>
+      </c>
+      <c r="F66">
+        <v>2608.512</v>
+      </c>
+      <c r="G66">
+        <v>27.4</v>
+      </c>
+      <c r="H66">
+        <v>2701.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>452.625</v>
+      </c>
+      <c r="K66">
+        <v>89.5</v>
+      </c>
+      <c r="L66">
+        <v>363.125</v>
+      </c>
+      <c r="M66">
+        <v>237.8962944</v>
+      </c>
+      <c r="N66">
+        <v>125.2287056</v>
+      </c>
+      <c r="O66">
+        <v>37.56861168</v>
+      </c>
+      <c r="P66">
+        <v>87.66009391999998</v>
+      </c>
+      <c r="Q66">
+        <v>177.16009392</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1693947489520972</v>
+      </c>
+      <c r="T66">
+        <v>2.839016281567332</v>
+      </c>
+      <c r="U66">
+        <v>0.0912</v>
+      </c>
+      <c r="V66">
+        <v>0.3</v>
+      </c>
+      <c r="W66">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>1.526400404494909</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1019155522850468</v>
+      </c>
+      <c r="C67">
+        <v>704.0730219514921</v>
+      </c>
+      <c r="D67">
+        <v>3325.943021951492</v>
+      </c>
+      <c r="E67">
+        <v>1275.37</v>
+      </c>
+      <c r="F67">
+        <v>2649.27</v>
+      </c>
+      <c r="G67">
+        <v>27.4</v>
+      </c>
+      <c r="H67">
+        <v>2701.9</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>452.625</v>
+      </c>
+      <c r="K67">
+        <v>89.5</v>
+      </c>
+      <c r="L67">
+        <v>363.125</v>
+      </c>
+      <c r="M67">
+        <v>241.613424</v>
+      </c>
+      <c r="N67">
+        <v>121.511576</v>
+      </c>
+      <c r="O67">
+        <v>36.45347279999999</v>
+      </c>
+      <c r="P67">
+        <v>85.05810320000001</v>
+      </c>
+      <c r="Q67">
+        <v>174.5581032</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1726272922429907</v>
+      </c>
+      <c r="T67">
+        <v>2.909288961804146</v>
+      </c>
+      <c r="U67">
+        <v>0.0912</v>
+      </c>
+      <c r="V67">
+        <v>0.3</v>
+      </c>
+      <c r="W67">
+        <v>0.06383999999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>1.502917321348834</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1380749740892558</v>
+      </c>
+      <c r="C68">
+        <v>-548.109888815879</v>
+      </c>
+      <c r="D68">
+        <v>2114.518111184121</v>
+      </c>
+      <c r="E68">
+        <v>1316.128</v>
+      </c>
+      <c r="F68">
+        <v>2690.028</v>
+      </c>
+      <c r="G68">
+        <v>27.4</v>
+      </c>
+      <c r="H68">
+        <v>2701.9</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>452.625</v>
+      </c>
+      <c r="K68">
+        <v>89.5</v>
+      </c>
+      <c r="L68">
+        <v>363.125</v>
+      </c>
+      <c r="M68">
+        <v>421.2583848000001</v>
+      </c>
+      <c r="N68">
+        <v>-58.1333848000001</v>
+      </c>
+      <c r="O68">
+        <v>-17.44001544000003</v>
+      </c>
+      <c r="P68">
+        <v>-40.69336936000008</v>
+      </c>
+      <c r="Q68">
+        <v>48.80663063999992</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1807260462709514</v>
+      </c>
+      <c r="T68">
+        <v>3.085348831977205</v>
+      </c>
+      <c r="U68">
+        <v>0.1566</v>
+      </c>
+      <c r="V68">
+        <v>0.2586001939206979</v>
+      </c>
+      <c r="W68">
+        <v>0.1161032096320187</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.8620006464023263</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1392529740892558</v>
+      </c>
+      <c r="C69">
+        <v>-613.6645895363736</v>
+      </c>
+      <c r="D69">
+        <v>2089.721410463626</v>
+      </c>
+      <c r="E69">
+        <v>1356.886</v>
+      </c>
+      <c r="F69">
+        <v>2730.786</v>
+      </c>
+      <c r="G69">
+        <v>27.4</v>
+      </c>
+      <c r="H69">
+        <v>2701.9</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>452.625</v>
+      </c>
+      <c r="K69">
+        <v>89.5</v>
+      </c>
+      <c r="L69">
+        <v>363.125</v>
+      </c>
+      <c r="M69">
+        <v>427.6410876</v>
+      </c>
+      <c r="N69">
+        <v>-64.51608760000005</v>
+      </c>
+      <c r="O69">
+        <v>-19.35482628000002</v>
+      </c>
+      <c r="P69">
+        <v>-45.16126132000004</v>
+      </c>
+      <c r="Q69">
+        <v>44.33873867999996</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.1850268355518893</v>
+      </c>
+      <c r="T69">
+        <v>3.178844251128029</v>
+      </c>
+      <c r="U69">
+        <v>0.1566</v>
+      </c>
+      <c r="V69">
+        <v>0.2547404895338218</v>
+      </c>
+      <c r="W69">
+        <v>0.1167076393390035</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.8491349651127394</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1404309740892558</v>
+      </c>
+      <c r="C70">
+        <v>-678.6444553955384</v>
+      </c>
+      <c r="D70">
+        <v>2065.499544604462</v>
+      </c>
+      <c r="E70">
+        <v>1397.644</v>
+      </c>
+      <c r="F70">
+        <v>2771.544</v>
+      </c>
+      <c r="G70">
+        <v>27.4</v>
+      </c>
+      <c r="H70">
+        <v>2701.9</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>452.625</v>
+      </c>
+      <c r="K70">
+        <v>89.5</v>
+      </c>
+      <c r="L70">
+        <v>363.125</v>
+      </c>
+      <c r="M70">
+        <v>434.0237904000001</v>
+      </c>
+      <c r="N70">
+        <v>-70.89879040000011</v>
+      </c>
+      <c r="O70">
+        <v>-21.26963712000003</v>
+      </c>
+      <c r="P70">
+        <v>-49.62915328000008</v>
+      </c>
+      <c r="Q70">
+        <v>39.87084671999992</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.1895964241628859</v>
+      </c>
+      <c r="T70">
+        <v>3.27818313397578</v>
+      </c>
+      <c r="U70">
+        <v>0.1566</v>
+      </c>
+      <c r="V70">
+        <v>0.2509943058642068</v>
+      </c>
+      <c r="W70">
+        <v>0.1172942917016652</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.8366476862140226</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1416089740892558</v>
+      </c>
+      <c r="C71">
+        <v>-743.069246014727</v>
+      </c>
+      <c r="D71">
+        <v>2041.832753985273</v>
+      </c>
+      <c r="E71">
+        <v>1438.402</v>
+      </c>
+      <c r="F71">
+        <v>2812.302</v>
+      </c>
+      <c r="G71">
+        <v>27.4</v>
+      </c>
+      <c r="H71">
+        <v>2701.9</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>452.625</v>
+      </c>
+      <c r="K71">
+        <v>89.5</v>
+      </c>
+      <c r="L71">
+        <v>363.125</v>
+      </c>
+      <c r="M71">
+        <v>440.4064932000001</v>
+      </c>
+      <c r="N71">
+        <v>-77.28149320000006</v>
+      </c>
+      <c r="O71">
+        <v>-23.18444796000002</v>
+      </c>
+      <c r="P71">
+        <v>-54.09704524000004</v>
+      </c>
+      <c r="Q71">
+        <v>35.40295475999996</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.1944608249423338</v>
+      </c>
+      <c r="T71">
+        <v>3.383930977007257</v>
+      </c>
+      <c r="U71">
+        <v>0.1566</v>
+      </c>
+      <c r="V71">
+        <v>0.2473567072284937</v>
+      </c>
+      <c r="W71">
+        <v>0.1178639396480179</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.8245223574283123</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1427869740892558</v>
+      </c>
+      <c r="C72">
+        <v>-806.9578256403074</v>
+      </c>
+      <c r="D72">
+        <v>2018.702174359693</v>
+      </c>
+      <c r="E72">
+        <v>1479.16</v>
+      </c>
+      <c r="F72">
+        <v>2853.06</v>
+      </c>
+      <c r="G72">
+        <v>27.4</v>
+      </c>
+      <c r="H72">
+        <v>2701.9</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>452.625</v>
+      </c>
+      <c r="K72">
+        <v>89.5</v>
+      </c>
+      <c r="L72">
+        <v>363.125</v>
+      </c>
+      <c r="M72">
+        <v>446.7891960000001</v>
+      </c>
+      <c r="N72">
+        <v>-83.66419600000012</v>
+      </c>
+      <c r="O72">
+        <v>-25.09925880000003</v>
+      </c>
+      <c r="P72">
+        <v>-58.56493720000009</v>
+      </c>
+      <c r="Q72">
+        <v>30.93506279999991</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.1996495191070783</v>
+      </c>
+      <c r="T72">
+        <v>3.496728676240833</v>
+      </c>
+      <c r="U72">
+        <v>0.1566</v>
+      </c>
+      <c r="V72">
+        <v>0.2438230399823723</v>
+      </c>
+      <c r="W72">
+        <v>0.1184173119387605</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.8127434666079076</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1439649740892558</v>
+      </c>
+      <c r="C73">
+        <v>-870.3282132911372</v>
+      </c>
+      <c r="D73">
+        <v>1996.089786708863</v>
+      </c>
+      <c r="E73">
+        <v>1519.918</v>
+      </c>
+      <c r="F73">
+        <v>2893.818</v>
+      </c>
+      <c r="G73">
+        <v>27.4</v>
+      </c>
+      <c r="H73">
+        <v>2701.9</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>452.625</v>
+      </c>
+      <c r="K73">
+        <v>89.5</v>
+      </c>
+      <c r="L73">
+        <v>363.125</v>
+      </c>
+      <c r="M73">
+        <v>453.1718988000001</v>
+      </c>
+      <c r="N73">
+        <v>-90.04689880000006</v>
+      </c>
+      <c r="O73">
+        <v>-27.01406964000002</v>
+      </c>
+      <c r="P73">
+        <v>-63.03282916000005</v>
+      </c>
+      <c r="Q73">
+        <v>26.46717083999995</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2051960542487017</v>
+      </c>
+      <c r="T73">
+        <v>3.617305527145688</v>
+      </c>
+      <c r="U73">
+        <v>0.1566</v>
+      </c>
+      <c r="V73">
+        <v>0.2403889126586769</v>
+      </c>
+      <c r="W73">
+        <v>0.1189550962776512</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.8012963755289231</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1852097049652457</v>
+      </c>
+      <c r="C74">
+        <v>-1473.399934752852</v>
+      </c>
+      <c r="D74">
+        <v>1433.776065247148</v>
+      </c>
+      <c r="E74">
+        <v>1560.676</v>
+      </c>
+      <c r="F74">
+        <v>2934.576</v>
+      </c>
+      <c r="G74">
+        <v>27.4</v>
+      </c>
+      <c r="H74">
+        <v>2701.9</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>452.625</v>
+      </c>
+      <c r="K74">
+        <v>89.5</v>
+      </c>
+      <c r="L74">
+        <v>363.125</v>
+      </c>
+      <c r="M74">
+        <v>612.7394688000001</v>
+      </c>
+      <c r="N74">
+        <v>-249.6144688000001</v>
+      </c>
+      <c r="O74">
+        <v>-74.88434064000002</v>
+      </c>
+      <c r="P74">
+        <v>-174.73012816</v>
+      </c>
+      <c r="Q74">
+        <v>-85.23012816000005</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2200056664575476</v>
+      </c>
+      <c r="T74">
+        <v>3.93925361864234</v>
+      </c>
+      <c r="U74">
+        <v>0.2088</v>
+      </c>
+      <c r="V74">
+        <v>0.1777876333204798</v>
+      </c>
+      <c r="W74">
+        <v>0.1716779421626838</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5926254444015995</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1869097049652457</v>
+      </c>
+      <c r="C75">
+        <v>-1530.614785514199</v>
+      </c>
+      <c r="D75">
+        <v>1417.319214485801</v>
+      </c>
+      <c r="E75">
+        <v>1601.434</v>
+      </c>
+      <c r="F75">
+        <v>2975.334</v>
+      </c>
+      <c r="G75">
+        <v>27.4</v>
+      </c>
+      <c r="H75">
+        <v>2701.9</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>452.625</v>
+      </c>
+      <c r="K75">
+        <v>89.5</v>
+      </c>
+      <c r="L75">
+        <v>363.125</v>
+      </c>
+      <c r="M75">
+        <v>621.2497392000001</v>
+      </c>
+      <c r="N75">
+        <v>-258.1247392000001</v>
+      </c>
+      <c r="O75">
+        <v>-77.43742176000003</v>
+      </c>
+      <c r="P75">
+        <v>-180.6873174400001</v>
+      </c>
+      <c r="Q75">
+        <v>-91.1873174400001</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2267169874374568</v>
+      </c>
+      <c r="T75">
+        <v>4.085151900814278</v>
+      </c>
+      <c r="U75">
+        <v>0.2088</v>
+      </c>
+      <c r="V75">
+        <v>0.1753521862886924</v>
+      </c>
+      <c r="W75">
+        <v>0.172186463502921</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5845072876289747</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1886097049652457</v>
+      </c>
+      <c r="C76">
+        <v>-1587.456140495673</v>
+      </c>
+      <c r="D76">
+        <v>1401.235859504327</v>
+      </c>
+      <c r="E76">
+        <v>1642.192</v>
+      </c>
+      <c r="F76">
+        <v>3016.092</v>
+      </c>
+      <c r="G76">
+        <v>27.4</v>
+      </c>
+      <c r="H76">
+        <v>2701.9</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>452.625</v>
+      </c>
+      <c r="K76">
+        <v>89.5</v>
+      </c>
+      <c r="L76">
+        <v>363.125</v>
+      </c>
+      <c r="M76">
+        <v>629.7600096000001</v>
+      </c>
+      <c r="N76">
+        <v>-266.6350096000001</v>
+      </c>
+      <c r="O76">
+        <v>-79.99050288000002</v>
+      </c>
+      <c r="P76">
+        <v>-186.6445067200001</v>
+      </c>
+      <c r="Q76">
+        <v>-97.14450672000009</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.233944563877359</v>
+      </c>
+      <c r="T76">
+        <v>4.242273127768674</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.172982562149656</v>
+      </c>
+      <c r="W76">
+        <v>0.1726812410231518</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5766085404988535</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.1903097049652457</v>
+      </c>
+      <c r="C77">
+        <v>-1643.936572017163</v>
+      </c>
+      <c r="D77">
+        <v>1385.513427982837</v>
+      </c>
+      <c r="E77">
+        <v>1682.95</v>
+      </c>
+      <c r="F77">
+        <v>3056.85</v>
+      </c>
+      <c r="G77">
+        <v>27.4</v>
+      </c>
+      <c r="H77">
+        <v>2701.9</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>452.625</v>
+      </c>
+      <c r="K77">
+        <v>89.5</v>
+      </c>
+      <c r="L77">
+        <v>363.125</v>
+      </c>
+      <c r="M77">
+        <v>638.2702800000001</v>
+      </c>
+      <c r="N77">
+        <v>-275.1452800000001</v>
+      </c>
+      <c r="O77">
+        <v>-82.54358400000002</v>
+      </c>
+      <c r="P77">
+        <v>-192.6016960000001</v>
+      </c>
+      <c r="Q77">
+        <v>-103.1016960000001</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2417503464324534</v>
+      </c>
+      <c r="T77">
+        <v>4.411964052879421</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.1706761279876606</v>
+      </c>
+      <c r="W77">
+        <v>0.1731628244761765</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5689204266255354</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1920097049652457</v>
+      </c>
+      <c r="C78">
+        <v>-1700.068094393602</v>
+      </c>
+      <c r="D78">
+        <v>1370.139905606398</v>
+      </c>
+      <c r="E78">
+        <v>1723.708</v>
+      </c>
+      <c r="F78">
+        <v>3097.608</v>
+      </c>
+      <c r="G78">
+        <v>27.4</v>
+      </c>
+      <c r="H78">
+        <v>2701.9</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>452.625</v>
+      </c>
+      <c r="K78">
+        <v>89.5</v>
+      </c>
+      <c r="L78">
+        <v>363.125</v>
+      </c>
+      <c r="M78">
+        <v>646.7805504</v>
+      </c>
+      <c r="N78">
+        <v>-283.6555504</v>
+      </c>
+      <c r="O78">
+        <v>-85.09666512000001</v>
+      </c>
+      <c r="P78">
+        <v>-198.55888528</v>
+      </c>
+      <c r="Q78">
+        <v>-109.05888528</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2502066108671389</v>
+      </c>
+      <c r="T78">
+        <v>4.595795888416064</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.1684303894615072</v>
+      </c>
+      <c r="W78">
+        <v>0.1736317346804373</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5614346315383574</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1937097049652457</v>
+      </c>
+      <c r="C79">
+        <v>-1755.862194553069</v>
+      </c>
+      <c r="D79">
+        <v>1355.103805446931</v>
+      </c>
+      <c r="E79">
+        <v>1764.466</v>
+      </c>
+      <c r="F79">
+        <v>3138.366</v>
+      </c>
+      <c r="G79">
+        <v>27.4</v>
+      </c>
+      <c r="H79">
+        <v>2701.9</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>452.625</v>
+      </c>
+      <c r="K79">
+        <v>89.5</v>
+      </c>
+      <c r="L79">
+        <v>363.125</v>
+      </c>
+      <c r="M79">
+        <v>655.2908208</v>
+      </c>
+      <c r="N79">
+        <v>-292.1658208</v>
+      </c>
+      <c r="O79">
+        <v>-87.64974624</v>
+      </c>
+      <c r="P79">
+        <v>-204.51607456</v>
+      </c>
+      <c r="Q79">
+        <v>-115.01607456</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2593982026439711</v>
+      </c>
+      <c r="T79">
+        <v>4.795613100955893</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.166242981806163</v>
+      </c>
+      <c r="W79">
+        <v>0.1740884653988732</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.55414327268721</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1954097049652457</v>
+      </c>
+      <c r="C80">
+        <v>-1811.329860660741</v>
+      </c>
+      <c r="D80">
+        <v>1340.394139339259</v>
+      </c>
+      <c r="E80">
+        <v>1805.224</v>
+      </c>
+      <c r="F80">
+        <v>3179.124</v>
+      </c>
+      <c r="G80">
+        <v>27.4</v>
+      </c>
+      <c r="H80">
+        <v>2701.9</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>452.625</v>
+      </c>
+      <c r="K80">
+        <v>89.5</v>
+      </c>
+      <c r="L80">
+        <v>363.125</v>
+      </c>
+      <c r="M80">
+        <v>663.8010912000001</v>
+      </c>
+      <c r="N80">
+        <v>-300.6760912000001</v>
+      </c>
+      <c r="O80">
+        <v>-90.20282736000003</v>
+      </c>
+      <c r="P80">
+        <v>-210.4732638400001</v>
+      </c>
+      <c r="Q80">
+        <v>-120.9732638400001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2694253936732425</v>
+      </c>
+      <c r="T80">
+        <v>5.013595514635706</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.1641116615265968</v>
+      </c>
+      <c r="W80">
+        <v>0.1745334850732466</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5470388717553225</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1971097049652457</v>
+      </c>
+      <c r="C81">
+        <v>-1866.481608898582</v>
+      </c>
+      <c r="D81">
+        <v>1326.000391101418</v>
+      </c>
+      <c r="E81">
+        <v>1845.982</v>
+      </c>
+      <c r="F81">
+        <v>3219.882</v>
+      </c>
+      <c r="G81">
+        <v>27.4</v>
+      </c>
+      <c r="H81">
+        <v>2701.9</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>452.625</v>
+      </c>
+      <c r="K81">
+        <v>89.5</v>
+      </c>
+      <c r="L81">
+        <v>363.125</v>
+      </c>
+      <c r="M81">
+        <v>672.3113616000001</v>
+      </c>
+      <c r="N81">
+        <v>-309.1863616000001</v>
+      </c>
+      <c r="O81">
+        <v>-92.75590848000002</v>
+      </c>
+      <c r="P81">
+        <v>-216.43045312</v>
+      </c>
+      <c r="Q81">
+        <v>-126.93045312</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2804075552767302</v>
+      </c>
+      <c r="T81">
+        <v>5.252338158189787</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.1620342987224626</v>
+      </c>
+      <c r="W81">
+        <v>0.1749672384267498</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5401143290748754</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1988097049652457</v>
+      </c>
+      <c r="C82">
+        <v>-1921.327508537933</v>
+      </c>
+      <c r="D82">
+        <v>1311.912491462067</v>
+      </c>
+      <c r="E82">
+        <v>1886.74</v>
+      </c>
+      <c r="F82">
+        <v>3260.64</v>
+      </c>
+      <c r="G82">
+        <v>27.4</v>
+      </c>
+      <c r="H82">
+        <v>2701.9</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>452.625</v>
+      </c>
+      <c r="K82">
+        <v>89.5</v>
+      </c>
+      <c r="L82">
+        <v>363.125</v>
+      </c>
+      <c r="M82">
+        <v>680.8216320000001</v>
+      </c>
+      <c r="N82">
+        <v>-317.6966320000001</v>
+      </c>
+      <c r="O82">
+        <v>-95.30898960000003</v>
+      </c>
+      <c r="P82">
+        <v>-222.3876424000001</v>
+      </c>
+      <c r="Q82">
+        <v>-132.8876424000001</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.2924879330405667</v>
+      </c>
+      <c r="T82">
+        <v>5.514955066099278</v>
+      </c>
+      <c r="U82">
+        <v>0.2088</v>
+      </c>
+      <c r="V82">
+        <v>0.1600088699884318</v>
+      </c>
+      <c r="W82">
+        <v>0.1753901479464154</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.5333628999614395</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2005097049652457</v>
+      </c>
+      <c r="C83">
+        <v>-1975.877205430614</v>
+      </c>
+      <c r="D83">
+        <v>1298.120794569386</v>
+      </c>
+      <c r="E83">
+        <v>1927.498</v>
+      </c>
+      <c r="F83">
+        <v>3301.398</v>
+      </c>
+      <c r="G83">
+        <v>27.4</v>
+      </c>
+      <c r="H83">
+        <v>2701.9</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>452.625</v>
+      </c>
+      <c r="K83">
+        <v>89.5</v>
+      </c>
+      <c r="L83">
+        <v>363.125</v>
+      </c>
+      <c r="M83">
+        <v>689.3319024000001</v>
+      </c>
+      <c r="N83">
+        <v>-326.2069024000001</v>
+      </c>
+      <c r="O83">
+        <v>-97.86207072000003</v>
+      </c>
+      <c r="P83">
+        <v>-228.3448316800001</v>
+      </c>
+      <c r="Q83">
+        <v>-138.8448316800001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3058399295163861</v>
+      </c>
+      <c r="T83">
+        <v>5.805215859051872</v>
+      </c>
+      <c r="U83">
+        <v>0.2088</v>
+      </c>
+      <c r="V83">
+        <v>0.1580334518404265</v>
+      </c>
+      <c r="W83">
+        <v>0.175802615255719</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.5267781728014217</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2022097049652457</v>
+      </c>
+      <c r="C84">
+        <v>-2030.13994403373</v>
+      </c>
+      <c r="D84">
+        <v>1284.616055966271</v>
+      </c>
+      <c r="E84">
+        <v>1968.256</v>
+      </c>
+      <c r="F84">
+        <v>3342.156</v>
+      </c>
+      <c r="G84">
+        <v>27.4</v>
+      </c>
+      <c r="H84">
+        <v>2701.9</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>452.625</v>
+      </c>
+      <c r="K84">
+        <v>89.5</v>
+      </c>
+      <c r="L84">
+        <v>363.125</v>
+      </c>
+      <c r="M84">
+        <v>697.8421728000002</v>
+      </c>
+      <c r="N84">
+        <v>-334.7171728000002</v>
+      </c>
+      <c r="O84">
+        <v>-100.41515184</v>
+      </c>
+      <c r="P84">
+        <v>-234.3020209600001</v>
+      </c>
+      <c r="Q84">
+        <v>-144.8020209600001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3206754811561853</v>
+      </c>
+      <c r="T84">
+        <v>6.127727851221419</v>
+      </c>
+      <c r="U84">
+        <v>0.2088</v>
+      </c>
+      <c r="V84">
+        <v>0.1561062146228603</v>
+      </c>
+      <c r="W84">
+        <v>0.1762050223867468</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.5203540487428677</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2039097049652457</v>
+      </c>
+      <c r="C85">
+        <v>-2084.124588073839</v>
+      </c>
+      <c r="D85">
+        <v>1271.389411926162</v>
+      </c>
+      <c r="E85">
+        <v>2009.014</v>
+      </c>
+      <c r="F85">
+        <v>3382.914</v>
+      </c>
+      <c r="G85">
+        <v>27.4</v>
+      </c>
+      <c r="H85">
+        <v>2701.9</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>452.625</v>
+      </c>
+      <c r="K85">
+        <v>89.5</v>
+      </c>
+      <c r="L85">
+        <v>363.125</v>
+      </c>
+      <c r="M85">
+        <v>706.3524432</v>
+      </c>
+      <c r="N85">
+        <v>-343.2274432</v>
+      </c>
+      <c r="O85">
+        <v>-102.96823296</v>
+      </c>
+      <c r="P85">
+        <v>-240.25921024</v>
+      </c>
+      <c r="Q85">
+        <v>-150.75921024</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3372563918124315</v>
+      </c>
+      <c r="T85">
+        <v>6.488182430705033</v>
+      </c>
+      <c r="U85">
+        <v>0.2088</v>
+      </c>
+      <c r="V85">
+        <v>0.1542254168563199</v>
+      </c>
+      <c r="W85">
+        <v>0.1765977329604004</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.5140847228543995</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2056097049652457</v>
+      </c>
+      <c r="C86">
+        <v>-2137.839639947557</v>
+      </c>
+      <c r="D86">
+        <v>1258.432360052443</v>
+      </c>
+      <c r="E86">
+        <v>2049.772</v>
+      </c>
+      <c r="F86">
+        <v>3423.672</v>
+      </c>
+      <c r="G86">
+        <v>27.4</v>
+      </c>
+      <c r="H86">
+        <v>2701.9</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>452.625</v>
+      </c>
+      <c r="K86">
+        <v>89.5</v>
+      </c>
+      <c r="L86">
+        <v>363.125</v>
+      </c>
+      <c r="M86">
+        <v>714.8627136</v>
+      </c>
+      <c r="N86">
+        <v>-351.7377136</v>
+      </c>
+      <c r="O86">
+        <v>-105.52131408</v>
+      </c>
+      <c r="P86">
+        <v>-246.21639952</v>
+      </c>
+      <c r="Q86">
+        <v>-156.71639952</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3559099163007083</v>
+      </c>
+      <c r="T86">
+        <v>6.893693832624094</v>
+      </c>
+      <c r="U86">
+        <v>0.2088</v>
+      </c>
+      <c r="V86">
+        <v>0.1523893999889827</v>
+      </c>
+      <c r="W86">
+        <v>0.1769810932823004</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.5079646666299424</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2073097049652457</v>
+      </c>
+      <c r="C87">
+        <v>-2191.293258947842</v>
+      </c>
+      <c r="D87">
+        <v>1245.736741052158</v>
+      </c>
+      <c r="E87">
+        <v>2090.53</v>
+      </c>
+      <c r="F87">
+        <v>3464.43</v>
+      </c>
+      <c r="G87">
+        <v>27.4</v>
+      </c>
+      <c r="H87">
+        <v>2701.9</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>452.625</v>
+      </c>
+      <c r="K87">
+        <v>89.5</v>
+      </c>
+      <c r="L87">
+        <v>363.125</v>
+      </c>
+      <c r="M87">
+        <v>723.3729840000001</v>
+      </c>
+      <c r="N87">
+        <v>-360.2479840000001</v>
+      </c>
+      <c r="O87">
+        <v>-108.0743952</v>
+      </c>
+      <c r="P87">
+        <v>-252.1735888000001</v>
+      </c>
+      <c r="Q87">
+        <v>-162.6735888000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3770505773874223</v>
+      </c>
+      <c r="T87">
+        <v>7.353273421465701</v>
+      </c>
+      <c r="U87">
+        <v>0.2088</v>
+      </c>
+      <c r="V87">
+        <v>0.1505965835185241</v>
+      </c>
+      <c r="W87">
+        <v>0.1773554333613322</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.5019886117284136</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2357454075566991</v>
+      </c>
+      <c r="C88">
+        <v>-2411.91531323206</v>
+      </c>
+      <c r="D88">
+        <v>1065.87268676794</v>
+      </c>
+      <c r="E88">
+        <v>2131.288</v>
+      </c>
+      <c r="F88">
+        <v>3505.188</v>
+      </c>
+      <c r="G88">
+        <v>27.4</v>
+      </c>
+      <c r="H88">
+        <v>2701.9</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>452.625</v>
+      </c>
+      <c r="K88">
+        <v>89.5</v>
+      </c>
+      <c r="L88">
+        <v>363.125</v>
+      </c>
+      <c r="M88">
+        <v>837.0388944000001</v>
+      </c>
+      <c r="N88">
+        <v>-473.9138944000001</v>
+      </c>
+      <c r="O88">
+        <v>-142.17416832</v>
+      </c>
+      <c r="P88">
+        <v>-331.7397260800001</v>
+      </c>
+      <c r="Q88">
+        <v>-242.2397260800001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4078949228540486</v>
+      </c>
+      <c r="T88">
+        <v>8.023802670740187</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.1301462820053156</v>
+      </c>
+      <c r="W88">
+        <v>0.2077210678571306</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4338209400177186</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2377454075566992</v>
+      </c>
+      <c r="C89">
+        <v>-2463.388541091384</v>
+      </c>
+      <c r="D89">
+        <v>1055.157458908616</v>
+      </c>
+      <c r="E89">
+        <v>2172.046</v>
+      </c>
+      <c r="F89">
+        <v>3545.946</v>
+      </c>
+      <c r="G89">
+        <v>27.4</v>
+      </c>
+      <c r="H89">
+        <v>2701.9</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>452.625</v>
+      </c>
+      <c r="K89">
+        <v>89.5</v>
+      </c>
+      <c r="L89">
+        <v>363.125</v>
+      </c>
+      <c r="M89">
+        <v>846.7719048000001</v>
+      </c>
+      <c r="N89">
+        <v>-483.6469048000001</v>
+      </c>
+      <c r="O89">
+        <v>-145.09407144</v>
+      </c>
+      <c r="P89">
+        <v>-338.5528333600001</v>
+      </c>
+      <c r="Q89">
+        <v>-249.0528333600001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4362868399966677</v>
+      </c>
+      <c r="T89">
+        <v>8.641018260797125</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.1286503477293924</v>
+      </c>
+      <c r="W89">
+        <v>0.2080782969622211</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.4288344924313081</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2397454075566992</v>
+      </c>
+      <c r="C90">
+        <v>-2514.648472653178</v>
+      </c>
+      <c r="D90">
+        <v>1044.655527346822</v>
+      </c>
+      <c r="E90">
+        <v>2212.804</v>
+      </c>
+      <c r="F90">
+        <v>3586.704</v>
+      </c>
+      <c r="G90">
+        <v>27.4</v>
+      </c>
+      <c r="H90">
+        <v>2701.9</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>452.625</v>
+      </c>
+      <c r="K90">
+        <v>89.5</v>
+      </c>
+      <c r="L90">
+        <v>363.125</v>
+      </c>
+      <c r="M90">
+        <v>856.5049152000001</v>
+      </c>
+      <c r="N90">
+        <v>-493.3799152000001</v>
+      </c>
+      <c r="O90">
+        <v>-148.01397456</v>
+      </c>
+      <c r="P90">
+        <v>-345.3659406400001</v>
+      </c>
+      <c r="Q90">
+        <v>-255.8659406400001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4694107433297234</v>
+      </c>
+      <c r="T90">
+        <v>9.361103115863553</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.1271884119597402</v>
+      </c>
+      <c r="W90">
+        <v>0.2084274072240141</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.4239613731991342</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2417454075566992</v>
+      </c>
+      <c r="C91">
+        <v>-2565.701413937374</v>
+      </c>
+      <c r="D91">
+        <v>1034.360586062626</v>
+      </c>
+      <c r="E91">
+        <v>2253.562</v>
+      </c>
+      <c r="F91">
+        <v>3627.462</v>
+      </c>
+      <c r="G91">
+        <v>27.4</v>
+      </c>
+      <c r="H91">
+        <v>2701.9</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>452.625</v>
+      </c>
+      <c r="K91">
+        <v>89.5</v>
+      </c>
+      <c r="L91">
+        <v>363.125</v>
+      </c>
+      <c r="M91">
+        <v>866.2379256</v>
+      </c>
+      <c r="N91">
+        <v>-503.1129256</v>
+      </c>
+      <c r="O91">
+        <v>-150.93387768</v>
+      </c>
+      <c r="P91">
+        <v>-352.17904792</v>
+      </c>
+      <c r="Q91">
+        <v>-262.67904792</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5085571745415165</v>
+      </c>
+      <c r="T91">
+        <v>10.21211249003297</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.1257593286792937</v>
+      </c>
+      <c r="W91">
+        <v>0.2087686723113847</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.4191977622643125</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2437454075566992</v>
+      </c>
+      <c r="C92">
+        <v>-2616.553424809771</v>
+      </c>
+      <c r="D92">
+        <v>1024.266575190229</v>
+      </c>
+      <c r="E92">
+        <v>2294.32</v>
+      </c>
+      <c r="F92">
+        <v>3668.22</v>
+      </c>
+      <c r="G92">
+        <v>27.4</v>
+      </c>
+      <c r="H92">
+        <v>2701.9</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>452.625</v>
+      </c>
+      <c r="K92">
+        <v>89.5</v>
+      </c>
+      <c r="L92">
+        <v>363.125</v>
+      </c>
+      <c r="M92">
+        <v>875.9709360000001</v>
+      </c>
+      <c r="N92">
+        <v>-512.8459360000001</v>
+      </c>
+      <c r="O92">
+        <v>-153.8537808</v>
+      </c>
+      <c r="P92">
+        <v>-358.9921552000001</v>
+      </c>
+      <c r="Q92">
+        <v>-269.4921552000001</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5555328919956681</v>
+      </c>
+      <c r="T92">
+        <v>11.23332373903626</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.1243620028050793</v>
+      </c>
+      <c r="W92">
+        <v>0.2091023537301471</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.4145400093502646</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2457454075566992</v>
+      </c>
+      <c r="C93">
+        <v>-2667.210330876673</v>
+      </c>
+      <c r="D93">
+        <v>1014.367669123327</v>
+      </c>
+      <c r="E93">
+        <v>2335.078</v>
+      </c>
+      <c r="F93">
+        <v>3708.978</v>
+      </c>
+      <c r="G93">
+        <v>27.4</v>
+      </c>
+      <c r="H93">
+        <v>2701.9</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>452.625</v>
+      </c>
+      <c r="K93">
+        <v>89.5</v>
+      </c>
+      <c r="L93">
+        <v>363.125</v>
+      </c>
+      <c r="M93">
+        <v>885.7039464000001</v>
+      </c>
+      <c r="N93">
+        <v>-522.5789464000001</v>
+      </c>
+      <c r="O93">
+        <v>-156.77368392</v>
+      </c>
+      <c r="P93">
+        <v>-365.80526248</v>
+      </c>
+      <c r="Q93">
+        <v>-276.30526248</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6129476577729647</v>
+      </c>
+      <c r="T93">
+        <v>12.48147082115141</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.1229953873896389</v>
+      </c>
+      <c r="W93">
+        <v>0.2094287014913543</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.4099846246321297</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2477454075566992</v>
+      </c>
+      <c r="C94">
+        <v>-2717.677734696407</v>
+      </c>
+      <c r="D94">
+        <v>1004.658265303594</v>
+      </c>
+      <c r="E94">
+        <v>2375.836</v>
+      </c>
+      <c r="F94">
+        <v>3749.736</v>
+      </c>
+      <c r="G94">
+        <v>27.4</v>
+      </c>
+      <c r="H94">
+        <v>2701.9</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>452.625</v>
+      </c>
+      <c r="K94">
+        <v>89.5</v>
+      </c>
+      <c r="L94">
+        <v>363.125</v>
+      </c>
+      <c r="M94">
+        <v>895.4369568000001</v>
+      </c>
+      <c r="N94">
+        <v>-532.3119568000001</v>
+      </c>
+      <c r="O94">
+        <v>-159.69358704</v>
+      </c>
+      <c r="P94">
+        <v>-372.6183697600001</v>
+      </c>
+      <c r="Q94">
+        <v>-283.1183697600001</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.6847161149945855</v>
+      </c>
+      <c r="T94">
+        <v>14.04165467379534</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.1216584810049689</v>
+      </c>
+      <c r="W94">
+        <v>0.2097479547360134</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.4055282700165631</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2497454075566992</v>
+      </c>
+      <c r="C95">
+        <v>-2767.961026353051</v>
+      </c>
+      <c r="D95">
+        <v>995.1329736469494</v>
+      </c>
+      <c r="E95">
+        <v>2416.594</v>
+      </c>
+      <c r="F95">
+        <v>3790.494</v>
+      </c>
+      <c r="G95">
+        <v>27.4</v>
+      </c>
+      <c r="H95">
+        <v>2701.9</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>452.625</v>
+      </c>
+      <c r="K95">
+        <v>89.5</v>
+      </c>
+      <c r="L95">
+        <v>363.125</v>
+      </c>
+      <c r="M95">
+        <v>905.1699672000001</v>
+      </c>
+      <c r="N95">
+        <v>-542.0449672000001</v>
+      </c>
+      <c r="O95">
+        <v>-162.61349016</v>
+      </c>
+      <c r="P95">
+        <v>-379.4314770400001</v>
+      </c>
+      <c r="Q95">
+        <v>-289.9314770400001</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.7769898457080979</v>
+      </c>
+      <c r="T95">
+        <v>16.04760534148039</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.1203503252952381</v>
+      </c>
+      <c r="W95">
+        <v>0.2100603423194972</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.4011677509841269</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2517454075566992</v>
+      </c>
+      <c r="C96">
+        <v>-2818.065393434313</v>
+      </c>
+      <c r="D96">
+        <v>985.786606565688</v>
+      </c>
+      <c r="E96">
+        <v>2457.352</v>
+      </c>
+      <c r="F96">
+        <v>3831.252</v>
+      </c>
+      <c r="G96">
+        <v>27.4</v>
+      </c>
+      <c r="H96">
+        <v>2701.9</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>452.625</v>
+      </c>
+      <c r="K96">
+        <v>89.5</v>
+      </c>
+      <c r="L96">
+        <v>363.125</v>
+      </c>
+      <c r="M96">
+        <v>914.9029776000001</v>
+      </c>
+      <c r="N96">
+        <v>-551.7779776000001</v>
+      </c>
+      <c r="O96">
+        <v>-165.53339328</v>
+      </c>
+      <c r="P96">
+        <v>-386.2445843200001</v>
+      </c>
+      <c r="Q96">
+        <v>-296.7445843200001</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9000214866594476</v>
+      </c>
+      <c r="T96">
+        <v>18.72220623172712</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.1190700026857143</v>
+      </c>
+      <c r="W96">
+        <v>0.2103660833586514</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3969000089523809</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2537454075566992</v>
+      </c>
+      <c r="C97">
+        <v>-2867.995830452355</v>
+      </c>
+      <c r="D97">
+        <v>976.6141695476449</v>
+      </c>
+      <c r="E97">
+        <v>2498.11</v>
+      </c>
+      <c r="F97">
+        <v>3872.01</v>
+      </c>
+      <c r="G97">
+        <v>27.4</v>
+      </c>
+      <c r="H97">
+        <v>2701.9</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>452.625</v>
+      </c>
+      <c r="K97">
+        <v>89.5</v>
+      </c>
+      <c r="L97">
+        <v>363.125</v>
+      </c>
+      <c r="M97">
+        <v>924.6359880000001</v>
+      </c>
+      <c r="N97">
+        <v>-561.5109880000001</v>
+      </c>
+      <c r="O97">
+        <v>-168.4532964</v>
+      </c>
+      <c r="P97">
+        <v>-393.0576916000001</v>
+      </c>
+      <c r="Q97">
+        <v>-303.5576916000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.072265783991337</v>
+      </c>
+      <c r="T97">
+        <v>22.46664747807255</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.117816634236391</v>
+      </c>
+      <c r="W97">
+        <v>0.2106653877443498</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3927221141213032</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2557454075566991</v>
+      </c>
+      <c r="C98">
+        <v>-2917.757147743525</v>
+      </c>
+      <c r="D98">
+        <v>967.6108522564748</v>
+      </c>
+      <c r="E98">
+        <v>2538.868</v>
+      </c>
+      <c r="F98">
+        <v>3912.768</v>
+      </c>
+      <c r="G98">
+        <v>27.4</v>
+      </c>
+      <c r="H98">
+        <v>2701.9</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>452.625</v>
+      </c>
+      <c r="K98">
+        <v>89.5</v>
+      </c>
+      <c r="L98">
+        <v>363.125</v>
+      </c>
+      <c r="M98">
+        <v>934.3689984</v>
+      </c>
+      <c r="N98">
+        <v>-571.2439984</v>
+      </c>
+      <c r="O98">
+        <v>-171.37319952</v>
+      </c>
+      <c r="P98">
+        <v>-399.8707988800001</v>
+      </c>
+      <c r="Q98">
+        <v>-310.3707988800001</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.330632229989169</v>
+      </c>
+      <c r="T98">
+        <v>28.08330934759063</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.1165893776297619</v>
+      </c>
+      <c r="W98">
+        <v>0.2109584566220128</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.388631258765873</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2577454075566992</v>
+      </c>
+      <c r="C99">
+        <v>-2967.353979880308</v>
+      </c>
+      <c r="D99">
+        <v>958.7720201196925</v>
+      </c>
+      <c r="E99">
+        <v>2579.626</v>
+      </c>
+      <c r="F99">
+        <v>3953.526</v>
+      </c>
+      <c r="G99">
+        <v>27.4</v>
+      </c>
+      <c r="H99">
+        <v>2701.9</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>452.625</v>
+      </c>
+      <c r="K99">
+        <v>89.5</v>
+      </c>
+      <c r="L99">
+        <v>363.125</v>
+      </c>
+      <c r="M99">
+        <v>944.1020088000001</v>
+      </c>
+      <c r="N99">
+        <v>-580.9770088000001</v>
+      </c>
+      <c r="O99">
+        <v>-174.29310264</v>
+      </c>
+      <c r="P99">
+        <v>-406.6839061600001</v>
+      </c>
+      <c r="Q99">
+        <v>-317.1839061600001</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.761242973318892</v>
+      </c>
+      <c r="T99">
+        <v>37.44441246345418</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.1153874252830633</v>
+      </c>
+      <c r="W99">
+        <v>0.2112454828424045</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3846247509435444</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2597454075566992</v>
+      </c>
+      <c r="C100">
+        <v>-3016.790793626401</v>
+      </c>
+      <c r="D100">
+        <v>950.0932063735988</v>
+      </c>
+      <c r="E100">
+        <v>2620.384</v>
+      </c>
+      <c r="F100">
+        <v>3994.284</v>
+      </c>
+      <c r="G100">
+        <v>27.4</v>
+      </c>
+      <c r="H100">
+        <v>2701.9</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>452.625</v>
+      </c>
+      <c r="K100">
+        <v>89.5</v>
+      </c>
+      <c r="L100">
+        <v>363.125</v>
+      </c>
+      <c r="M100">
+        <v>953.8350192</v>
+      </c>
+      <c r="N100">
+        <v>-590.7100192</v>
+      </c>
+      <c r="O100">
+        <v>-177.21300576</v>
+      </c>
+      <c r="P100">
+        <v>-413.49701344</v>
+      </c>
+      <c r="Q100">
+        <v>-323.99701344</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.622464459978338</v>
+      </c>
+      <c r="T100">
+        <v>56.16661869518126</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.1142100025760933</v>
+      </c>
+      <c r="W100">
+        <v>0.2115266513848289</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3807000085869776</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2617454075566992</v>
+      </c>
+      <c r="C101">
+        <v>-3066.071895463626</v>
+      </c>
+      <c r="D101">
+        <v>941.5701045363745</v>
+      </c>
+      <c r="E101">
+        <v>2661.142</v>
+      </c>
+      <c r="F101">
+        <v>4035.042</v>
+      </c>
+      <c r="G101">
+        <v>27.4</v>
+      </c>
+      <c r="H101">
+        <v>2701.9</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>452.625</v>
+      </c>
+      <c r="K101">
+        <v>89.5</v>
+      </c>
+      <c r="L101">
+        <v>363.125</v>
+      </c>
+      <c r="M101">
+        <v>963.5680296000002</v>
+      </c>
+      <c r="N101">
+        <v>-600.4430296000002</v>
+      </c>
+      <c r="O101">
+        <v>-180.13290888</v>
+      </c>
+      <c r="P101">
+        <v>-420.3101207200001</v>
+      </c>
+      <c r="Q101">
+        <v>-330.8101207200001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.206128919956677</v>
+      </c>
+      <c r="T101">
+        <v>112.3332373903625</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.1130563661864358</v>
+      </c>
+      <c r="W101">
+        <v>0.2118021397546792</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.376854553954786</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/germany/germany_software_internet.xlsx
+++ b/research/traditional_assets/database/data/germany/germany_software_internet.xlsx
@@ -1380,7 +1380,7 @@
         <v>4.34045393858478</v>
       </c>
       <c r="F2">
-        <v>4.0194282824189</v>
+        <v>4.01942828241889</v>
       </c>
       <c r="G2">
         <v>3.07801754801992</v>
@@ -1525,7 +1525,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1662,22 +1662,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1005705269765737</v>
+        <v>0.100300315395644</v>
       </c>
       <c r="C2">
-        <v>3892.745248105122</v>
+        <v>3867.458871060472</v>
       </c>
       <c r="D2">
-        <v>3869.845248105122</v>
+        <v>3889.031871060472</v>
       </c>
       <c r="E2">
-        <v>-1298</v>
+        <v>-1253.527</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>44.47300000000001</v>
       </c>
       <c r="G2">
         <v>22.9</v>
@@ -1698,28 +1698,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>2.2369919</v>
       </c>
       <c r="N2">
-        <v>371.9555555555556</v>
+        <v>369.7185636555556</v>
       </c>
       <c r="O2">
-        <v>111.5866666666667</v>
+        <v>110.9155690966667</v>
       </c>
       <c r="P2">
-        <v>260.3688888888889</v>
+        <v>258.8029945588889</v>
       </c>
       <c r="Q2">
-        <v>356.9688888888889</v>
+        <v>355.4029945588888</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1005705269765737</v>
+        <v>0.1009577933289333</v>
       </c>
       <c r="T2">
-        <v>1.264908244262672</v>
+        <v>1.273852039929176</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>166.2748781323507</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1744,22 +1744,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.100300315395644</v>
+        <v>0.1000301038147142</v>
       </c>
       <c r="C3">
-        <v>3867.458871060472</v>
+        <v>3842.363695852322</v>
       </c>
       <c r="D3">
-        <v>3889.031871060472</v>
+        <v>3908.409695852322</v>
       </c>
       <c r="E3">
-        <v>-1253.527</v>
+        <v>-1209.054</v>
       </c>
       <c r="F3">
-        <v>44.47300000000001</v>
+        <v>88.94600000000001</v>
       </c>
       <c r="G3">
         <v>22.9</v>
@@ -1780,28 +1780,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M3">
-        <v>2.2369919</v>
+        <v>4.4739838</v>
       </c>
       <c r="N3">
-        <v>369.7185636555556</v>
+        <v>367.4815717555556</v>
       </c>
       <c r="O3">
-        <v>110.9155690966667</v>
+        <v>110.2444715266667</v>
       </c>
       <c r="P3">
-        <v>258.8029945588889</v>
+        <v>257.2371002288889</v>
       </c>
       <c r="Q3">
-        <v>355.4029945588888</v>
+        <v>353.8371002288889</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1009577933289333</v>
+        <v>0.101352963076239</v>
       </c>
       <c r="T3">
-        <v>1.273852039929176</v>
+        <v>1.282978362037853</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1818,7 +1818,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>166.2748781323507</v>
+        <v>83.13743906617533</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1826,22 +1826,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1000301038147142</v>
+        <v>0.09975989223378454</v>
       </c>
       <c r="C4">
-        <v>3842.363695852322</v>
+        <v>3817.462594889141</v>
       </c>
       <c r="D4">
-        <v>3908.409695852322</v>
+        <v>3927.981594889141</v>
       </c>
       <c r="E4">
-        <v>-1209.054</v>
+        <v>-1164.581</v>
       </c>
       <c r="F4">
-        <v>88.94600000000001</v>
+        <v>133.419</v>
       </c>
       <c r="G4">
         <v>22.9</v>
@@ -1862,28 +1862,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M4">
-        <v>4.4739838</v>
+        <v>6.710975700000001</v>
       </c>
       <c r="N4">
-        <v>367.4815717555556</v>
+        <v>365.2445798555556</v>
       </c>
       <c r="O4">
-        <v>110.2444715266667</v>
+        <v>109.5733739566667</v>
       </c>
       <c r="P4">
-        <v>257.2371002288889</v>
+        <v>255.6712058988889</v>
       </c>
       <c r="Q4">
-        <v>353.8371002288889</v>
+        <v>352.2712058988889</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.101352963076239</v>
+        <v>0.1017562806533861</v>
       </c>
       <c r="T4">
-        <v>1.282978362037853</v>
+        <v>1.2922928557364</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1900,7 +1900,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>83.13743906617533</v>
+        <v>55.42495937745022</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1908,22 +1908,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09975989223378454</v>
+        <v>0.09948968065285482</v>
       </c>
       <c r="C5">
-        <v>3817.462594889141</v>
+        <v>3792.758498404893</v>
       </c>
       <c r="D5">
-        <v>3927.981594889141</v>
+        <v>3947.750498404893</v>
       </c>
       <c r="E5">
-        <v>-1164.581</v>
+        <v>-1120.108</v>
       </c>
       <c r="F5">
-        <v>133.419</v>
+        <v>177.892</v>
       </c>
       <c r="G5">
         <v>22.9</v>
@@ -1944,28 +1944,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M5">
-        <v>6.710975700000001</v>
+        <v>8.9479676</v>
       </c>
       <c r="N5">
-        <v>365.2445798555556</v>
+        <v>363.0075879555556</v>
       </c>
       <c r="O5">
-        <v>109.5733739566667</v>
+        <v>108.9022763866667</v>
       </c>
       <c r="P5">
-        <v>255.6712058988889</v>
+        <v>254.1053115688889</v>
       </c>
       <c r="Q5">
-        <v>352.2712058988889</v>
+        <v>350.7053115688889</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1017562806533861</v>
+        <v>0.1021680006800571</v>
       </c>
       <c r="T5">
-        <v>1.2922928557364</v>
+        <v>1.301801401387</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1982,7 +1982,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>55.42495937745022</v>
+        <v>41.56871953308767</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1990,22 +1990,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09948968065285482</v>
+        <v>0.09921946907192508</v>
       </c>
       <c r="C6">
-        <v>3792.758498404893</v>
+        <v>3768.254395921525</v>
       </c>
       <c r="D6">
-        <v>3947.750498404893</v>
+        <v>3967.719395921525</v>
       </c>
       <c r="E6">
-        <v>-1120.108</v>
+        <v>-1075.635</v>
       </c>
       <c r="F6">
-        <v>177.892</v>
+        <v>222.365</v>
       </c>
       <c r="G6">
         <v>22.9</v>
@@ -2026,28 +2026,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M6">
-        <v>8.9479676</v>
+        <v>11.1849595</v>
       </c>
       <c r="N6">
-        <v>363.0075879555556</v>
+        <v>360.7705960555556</v>
       </c>
       <c r="O6">
-        <v>108.9022763866667</v>
+        <v>108.2311788166667</v>
       </c>
       <c r="P6">
-        <v>254.1053115688889</v>
+        <v>252.5394172388889</v>
       </c>
       <c r="Q6">
-        <v>350.7053115688889</v>
+        <v>349.1394172388889</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1021680006800571</v>
+        <v>0.1025883884967632</v>
       </c>
       <c r="T6">
-        <v>1.301801401387</v>
+        <v>1.311510126946034</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2064,7 +2064,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>41.56871953308767</v>
+        <v>33.25497562647013</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2072,22 +2072,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09921946907192508</v>
+        <v>0.09894925749099537</v>
       </c>
       <c r="C7">
-        <v>3768.254395921525</v>
+        <v>3743.953337756067</v>
       </c>
       <c r="D7">
-        <v>3967.719395921525</v>
+        <v>3987.891337756067</v>
       </c>
       <c r="E7">
-        <v>-1075.635</v>
+        <v>-1031.162</v>
       </c>
       <c r="F7">
-        <v>222.365</v>
+        <v>266.838</v>
       </c>
       <c r="G7">
         <v>22.9</v>
@@ -2108,28 +2108,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M7">
-        <v>11.1849595</v>
+        <v>13.4219514</v>
       </c>
       <c r="N7">
-        <v>360.7705960555556</v>
+        <v>358.5336041555556</v>
       </c>
       <c r="O7">
-        <v>108.2311788166667</v>
+        <v>107.5600812466667</v>
       </c>
       <c r="P7">
-        <v>252.5394172388889</v>
+        <v>250.9735229088889</v>
       </c>
       <c r="Q7">
-        <v>349.1394172388889</v>
+        <v>347.5735229088889</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1025883884967632</v>
+        <v>0.1030177207351015</v>
       </c>
       <c r="T7">
-        <v>1.311510126946034</v>
+        <v>1.321425421133983</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2146,7 +2146,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>33.25497562647013</v>
+        <v>27.71247968872511</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2154,22 +2154,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09894925749099537</v>
+        <v>0.09867904591006565</v>
       </c>
       <c r="C8">
-        <v>3743.953337756067</v>
+        <v>3719.858436573955</v>
       </c>
       <c r="D8">
-        <v>3987.891337756067</v>
+        <v>4008.269436573955</v>
       </c>
       <c r="E8">
-        <v>-1031.162</v>
+        <v>-986.6890000000001</v>
       </c>
       <c r="F8">
-        <v>266.838</v>
+        <v>311.311</v>
       </c>
       <c r="G8">
         <v>22.9</v>
@@ -2190,28 +2190,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M8">
-        <v>13.4219514</v>
+        <v>15.6589433</v>
       </c>
       <c r="N8">
-        <v>358.5336041555556</v>
+        <v>356.2966122555556</v>
       </c>
       <c r="O8">
-        <v>107.5600812466667</v>
+        <v>106.8889836766667</v>
       </c>
       <c r="P8">
-        <v>250.9735229088889</v>
+        <v>249.4076285788889</v>
       </c>
       <c r="Q8">
-        <v>347.5735229088889</v>
+        <v>346.0076285788889</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1030177207351015</v>
+        <v>0.1034562859248018</v>
       </c>
       <c r="T8">
-        <v>1.321425421133983</v>
+        <v>1.331553947455007</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2228,7 +2228,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>27.71247968872511</v>
+        <v>23.75355401890724</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2236,22 +2236,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09867904591006564</v>
+        <v>0.09840883432913594</v>
       </c>
       <c r="C9">
-        <v>3719.858436573956</v>
+        <v>3695.972868990207</v>
       </c>
       <c r="D9">
-        <v>4008.269436573956</v>
+        <v>4028.856868990207</v>
       </c>
       <c r="E9">
-        <v>-986.689</v>
+        <v>-942.2159999999999</v>
       </c>
       <c r="F9">
-        <v>311.311</v>
+        <v>355.784</v>
       </c>
       <c r="G9">
         <v>22.9</v>
@@ -2272,28 +2272,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M9">
-        <v>15.6589433</v>
+        <v>17.8959352</v>
       </c>
       <c r="N9">
-        <v>356.2966122555556</v>
+        <v>354.0596203555556</v>
       </c>
       <c r="O9">
-        <v>106.8889836766667</v>
+        <v>106.2178861066667</v>
       </c>
       <c r="P9">
-        <v>249.4076285788889</v>
+        <v>247.8417342488889</v>
       </c>
       <c r="Q9">
-        <v>346.0076285788889</v>
+        <v>344.4417342488889</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1034562859248018</v>
+        <v>0.1039043851403652</v>
       </c>
       <c r="T9">
-        <v>1.331553947455007</v>
+        <v>1.341902659130835</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2310,7 +2310,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>23.75355401890724</v>
+        <v>20.78435976654383</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2318,22 +2318,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09840883432913594</v>
+        <v>0.0981386227482062</v>
       </c>
       <c r="C10">
-        <v>3695.972868990207</v>
+        <v>3672.299877220206</v>
       </c>
       <c r="D10">
-        <v>4028.856868990207</v>
+        <v>4049.656877220206</v>
       </c>
       <c r="E10">
-        <v>-942.2159999999999</v>
+        <v>-897.7429999999999</v>
       </c>
       <c r="F10">
-        <v>355.784</v>
+        <v>400.257</v>
       </c>
       <c r="G10">
         <v>22.9</v>
@@ -2354,28 +2354,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M10">
-        <v>17.8959352</v>
+        <v>20.1329271</v>
       </c>
       <c r="N10">
-        <v>354.0596203555556</v>
+        <v>351.8226284555556</v>
       </c>
       <c r="O10">
-        <v>106.2178861066667</v>
+        <v>105.5467885366667</v>
       </c>
       <c r="P10">
-        <v>247.8417342488889</v>
+        <v>246.2758399188889</v>
       </c>
       <c r="Q10">
-        <v>344.4417342488889</v>
+        <v>342.8758399188889</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1039043851403652</v>
+        <v>0.1043623326903365</v>
       </c>
       <c r="T10">
-        <v>1.341902659130835</v>
+        <v>1.352478815019319</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>20.78435976654383</v>
+        <v>18.47498645915007</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2400,22 +2400,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.0981386227482062</v>
+        <v>0.09786841116727649</v>
       </c>
       <c r="C11">
-        <v>3672.299877220206</v>
+        <v>3648.842770781872</v>
       </c>
       <c r="D11">
-        <v>4049.656877220206</v>
+        <v>4070.672770781872</v>
       </c>
       <c r="E11">
-        <v>-897.7429999999999</v>
+        <v>-853.27</v>
       </c>
       <c r="F11">
-        <v>400.257</v>
+        <v>444.73</v>
       </c>
       <c r="G11">
         <v>22.9</v>
@@ -2436,28 +2436,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M11">
-        <v>20.1329271</v>
+        <v>22.369919</v>
       </c>
       <c r="N11">
-        <v>351.8226284555556</v>
+        <v>349.5856365555556</v>
       </c>
       <c r="O11">
-        <v>105.5467885366667</v>
+        <v>104.8756909666667</v>
       </c>
       <c r="P11">
-        <v>246.2758399188889</v>
+        <v>244.7099455888889</v>
       </c>
       <c r="Q11">
-        <v>342.8758399188889</v>
+        <v>341.3099455888889</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1043623326903365</v>
+        <v>0.1048304568525294</v>
       </c>
       <c r="T11">
-        <v>1.352478815019319</v>
+        <v>1.363289996594214</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2474,7 +2474,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>18.47498645915007</v>
+        <v>16.62748781323507</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2482,22 +2482,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09786841116727649</v>
+        <v>0.09759819958634677</v>
       </c>
       <c r="C12">
-        <v>3648.842770781872</v>
+        <v>3625.604928251137</v>
       </c>
       <c r="D12">
-        <v>4070.672770781872</v>
+        <v>4091.907928251137</v>
       </c>
       <c r="E12">
-        <v>-853.27</v>
+        <v>-808.797</v>
       </c>
       <c r="F12">
-        <v>444.73</v>
+        <v>489.203</v>
       </c>
       <c r="G12">
         <v>22.9</v>
@@ -2518,28 +2518,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M12">
-        <v>22.369919</v>
+        <v>24.6069109</v>
       </c>
       <c r="N12">
-        <v>349.5856365555556</v>
+        <v>347.3486446555556</v>
       </c>
       <c r="O12">
-        <v>104.8756909666667</v>
+        <v>104.2045933966667</v>
       </c>
       <c r="P12">
-        <v>244.7099455888889</v>
+        <v>243.1440512588889</v>
       </c>
       <c r="Q12">
-        <v>341.3099455888889</v>
+        <v>339.7440512588889</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1048304568525294</v>
+        <v>0.1053091006588166</v>
       </c>
       <c r="T12">
-        <v>1.363289996594214</v>
+        <v>1.374344126069668</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>16.62748781323507</v>
+        <v>15.11589801203188</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2564,22 +2564,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09759819958634677</v>
+        <v>0.09732798800541705</v>
       </c>
       <c r="C13">
-        <v>3625.604928251137</v>
+        <v>3602.589799072629</v>
       </c>
       <c r="D13">
-        <v>4091.907928251137</v>
+        <v>4113.36579907263</v>
       </c>
       <c r="E13">
-        <v>-808.797</v>
+        <v>-764.324</v>
       </c>
       <c r="F13">
-        <v>489.203</v>
+        <v>533.676</v>
       </c>
       <c r="G13">
         <v>22.9</v>
@@ -2600,28 +2600,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M13">
-        <v>24.6069109</v>
+        <v>26.8439028</v>
       </c>
       <c r="N13">
-        <v>347.3486446555556</v>
+        <v>345.1116527555556</v>
       </c>
       <c r="O13">
-        <v>104.2045933966667</v>
+        <v>103.5334958266667</v>
       </c>
       <c r="P13">
-        <v>243.1440512588889</v>
+        <v>241.5781569288889</v>
       </c>
       <c r="Q13">
-        <v>339.7440512588889</v>
+        <v>338.1781569288888</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1053091006588166</v>
+        <v>0.1057986227334285</v>
       </c>
       <c r="T13">
-        <v>1.374344126069668</v>
+        <v>1.385649485760473</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2638,7 +2638,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.11589801203188</v>
+        <v>13.85623984436255</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2646,22 +2646,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09732798800541705</v>
+        <v>0.09719427642448733</v>
       </c>
       <c r="C14">
-        <v>3602.589799072629</v>
+        <v>3568.818470196345</v>
       </c>
       <c r="D14">
-        <v>4113.36579907263</v>
+        <v>4124.067470196345</v>
       </c>
       <c r="E14">
-        <v>-764.324</v>
+        <v>-719.851</v>
       </c>
       <c r="F14">
-        <v>533.676</v>
+        <v>578.149</v>
       </c>
       <c r="G14">
         <v>22.9</v>
@@ -2682,45 +2682,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M14">
-        <v>26.8439028</v>
+        <v>29.9481182</v>
       </c>
       <c r="N14">
-        <v>345.1116527555556</v>
+        <v>342.0074373555556</v>
       </c>
       <c r="O14">
-        <v>103.5334958266667</v>
+        <v>102.6022312066667</v>
       </c>
       <c r="P14">
-        <v>241.5781569288889</v>
+        <v>239.4052061488889</v>
       </c>
       <c r="Q14">
-        <v>338.1781569288888</v>
+        <v>336.0052061488889</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1057986227334285</v>
+        <v>0.1062993981890659</v>
       </c>
       <c r="T14">
-        <v>1.385649485760473</v>
+        <v>1.397214738777504</v>
       </c>
       <c r="U14">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V14">
         <v>0.3</v>
       </c>
       <c r="W14">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y14">
-        <v>13.85623984436255</v>
+        <v>12.41999757953258</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2728,22 +2728,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09719427642448733</v>
+        <v>0.0969345648435576</v>
       </c>
       <c r="C15">
-        <v>3568.818470196345</v>
+        <v>3545.291538395467</v>
       </c>
       <c r="D15">
-        <v>4124.067470196345</v>
+        <v>4145.013538395468</v>
       </c>
       <c r="E15">
-        <v>-719.851</v>
+        <v>-675.3779999999999</v>
       </c>
       <c r="F15">
-        <v>578.149</v>
+        <v>622.6220000000001</v>
       </c>
       <c r="G15">
         <v>22.9</v>
@@ -2764,28 +2764,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M15">
-        <v>29.9481182</v>
+        <v>32.2518196</v>
       </c>
       <c r="N15">
-        <v>342.0074373555556</v>
+        <v>339.7037359555555</v>
       </c>
       <c r="O15">
-        <v>102.6022312066667</v>
+        <v>101.9111207866667</v>
       </c>
       <c r="P15">
-        <v>239.4052061488889</v>
+        <v>237.7926151688889</v>
       </c>
       <c r="Q15">
-        <v>336.0052061488889</v>
+        <v>334.3926151688888</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1062993981890659</v>
+        <v>0.1068118195855321</v>
       </c>
       <c r="T15">
-        <v>1.397214738777504</v>
+        <v>1.409048951167023</v>
       </c>
       <c r="U15">
         <v>0.0518</v>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>12.41999757953258</v>
+        <v>11.53285489528025</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2810,22 +2810,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0969345648435576</v>
+        <v>0.09667485326262788</v>
       </c>
       <c r="C16">
-        <v>3545.291538395467</v>
+        <v>3521.978462208408</v>
       </c>
       <c r="D16">
-        <v>4145.013538395468</v>
+        <v>4166.173462208409</v>
       </c>
       <c r="E16">
-        <v>-675.3779999999999</v>
+        <v>-630.9049999999999</v>
       </c>
       <c r="F16">
-        <v>622.6220000000001</v>
+        <v>667.0950000000001</v>
       </c>
       <c r="G16">
         <v>22.9</v>
@@ -2846,28 +2846,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M16">
-        <v>32.2518196</v>
+        <v>34.55552100000001</v>
       </c>
       <c r="N16">
-        <v>339.7037359555555</v>
+        <v>337.4000345555556</v>
       </c>
       <c r="O16">
-        <v>101.9111207866667</v>
+        <v>101.2200103666667</v>
       </c>
       <c r="P16">
-        <v>237.7926151688889</v>
+        <v>236.1800241888889</v>
       </c>
       <c r="Q16">
-        <v>334.3926151688888</v>
+        <v>332.7800241888889</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1068118195855321</v>
+        <v>0.1073362979560328</v>
       </c>
       <c r="T16">
-        <v>1.409048951167023</v>
+        <v>1.421161615612767</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2884,7 +2884,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>11.53285489528025</v>
+        <v>10.76399790226157</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2892,22 +2892,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09667485326262788</v>
+        <v>0.09641514168169817</v>
       </c>
       <c r="C17">
-        <v>3521.978462208408</v>
+        <v>3498.882533581674</v>
       </c>
       <c r="D17">
-        <v>4166.173462208409</v>
+        <v>4187.550533581674</v>
       </c>
       <c r="E17">
-        <v>-630.905</v>
+        <v>-586.4319999999999</v>
       </c>
       <c r="F17">
-        <v>667.095</v>
+        <v>711.5680000000001</v>
       </c>
       <c r="G17">
         <v>22.9</v>
@@ -2928,28 +2928,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M17">
-        <v>34.555521</v>
+        <v>36.85922240000001</v>
       </c>
       <c r="N17">
-        <v>337.4000345555556</v>
+        <v>335.0963331555556</v>
       </c>
       <c r="O17">
-        <v>101.2200103666667</v>
+        <v>100.5288999466667</v>
       </c>
       <c r="P17">
-        <v>236.1800241888889</v>
+        <v>234.5674332088889</v>
       </c>
       <c r="Q17">
-        <v>332.7800241888889</v>
+        <v>331.1674332088888</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1073362979560328</v>
+        <v>0.1078732639067835</v>
       </c>
       <c r="T17">
-        <v>1.421161615612767</v>
+        <v>1.433562676831029</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2966,7 +2966,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>10.76399790226157</v>
+        <v>10.09124803337022</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2974,22 +2974,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09641514168169817</v>
+        <v>0.09635773010076844</v>
       </c>
       <c r="C18">
-        <v>3498.882533581674</v>
+        <v>3459.164768752968</v>
       </c>
       <c r="D18">
-        <v>4187.550533581674</v>
+        <v>4192.305768752969</v>
       </c>
       <c r="E18">
-        <v>-586.4319999999999</v>
+        <v>-541.9589999999999</v>
       </c>
       <c r="F18">
-        <v>711.5680000000001</v>
+        <v>756.0410000000001</v>
       </c>
       <c r="G18">
         <v>22.9</v>
@@ -3010,45 +3010,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M18">
-        <v>36.85922240000001</v>
+        <v>40.4481935</v>
       </c>
       <c r="N18">
-        <v>335.0963331555556</v>
+        <v>331.5073620555556</v>
       </c>
       <c r="O18">
-        <v>100.5288999466667</v>
+        <v>99.45220861666667</v>
       </c>
       <c r="P18">
-        <v>234.5674332088889</v>
+        <v>232.0551534388889</v>
       </c>
       <c r="Q18">
-        <v>331.1674332088888</v>
+        <v>328.6551534388889</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1078732639067835</v>
+        <v>0.1084231687961066</v>
       </c>
       <c r="T18">
-        <v>1.433562676831029</v>
+        <v>1.446262558801538</v>
       </c>
       <c r="U18">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V18">
         <v>0.3</v>
       </c>
       <c r="W18">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y18">
-        <v>10.09124803337022</v>
+        <v>9.195850874169587</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3056,22 +3056,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09635773010076844</v>
+        <v>0.09610991851983872</v>
       </c>
       <c r="C19">
-        <v>3459.164768752968</v>
+        <v>3435.341810551105</v>
       </c>
       <c r="D19">
-        <v>4192.305768752969</v>
+        <v>4212.955810551105</v>
       </c>
       <c r="E19">
-        <v>-541.9589999999999</v>
+        <v>-497.4859999999999</v>
       </c>
       <c r="F19">
-        <v>756.0410000000001</v>
+        <v>800.5140000000001</v>
       </c>
       <c r="G19">
         <v>22.9</v>
@@ -3092,28 +3092,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M19">
-        <v>40.4481935</v>
+        <v>42.827499</v>
       </c>
       <c r="N19">
-        <v>331.5073620555556</v>
+        <v>329.1280565555556</v>
       </c>
       <c r="O19">
-        <v>99.45220861666667</v>
+        <v>98.73841696666668</v>
       </c>
       <c r="P19">
-        <v>232.0551534388889</v>
+        <v>230.3896395888889</v>
       </c>
       <c r="Q19">
-        <v>328.6551534388889</v>
+        <v>326.9896395888888</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1084231687961066</v>
+        <v>0.1089864859998033</v>
       </c>
       <c r="T19">
-        <v>1.446262558801538</v>
+        <v>1.459272193990839</v>
       </c>
       <c r="U19">
         <v>0.0535</v>
@@ -3130,7 +3130,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>9.195850874169587</v>
+        <v>8.684970270049053</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3138,22 +3138,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09610991851983873</v>
+        <v>0.09586210693890899</v>
       </c>
       <c r="C20">
-        <v>3435.341810551104</v>
+        <v>3411.723291188001</v>
       </c>
       <c r="D20">
-        <v>4212.955810551104</v>
+        <v>4233.810291188001</v>
       </c>
       <c r="E20">
-        <v>-497.486</v>
+        <v>-453.0129999999999</v>
       </c>
       <c r="F20">
-        <v>800.514</v>
+        <v>844.9870000000001</v>
       </c>
       <c r="G20">
         <v>22.9</v>
@@ -3174,28 +3174,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M20">
-        <v>42.827499</v>
+        <v>45.2068045</v>
       </c>
       <c r="N20">
-        <v>329.1280565555556</v>
+        <v>326.7487510555555</v>
       </c>
       <c r="O20">
-        <v>98.73841696666668</v>
+        <v>98.02462531666666</v>
       </c>
       <c r="P20">
-        <v>230.3896395888889</v>
+        <v>228.7241257388889</v>
       </c>
       <c r="Q20">
-        <v>326.9896395888888</v>
+        <v>325.3241257388888</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1089864859998033</v>
+        <v>0.109563712270258</v>
       </c>
       <c r="T20">
-        <v>1.459272193990839</v>
+        <v>1.47260305474037</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>8.684970270049053</v>
+        <v>8.227866571625418</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3220,22 +3220,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09586210693890899</v>
+        <v>0.09561429535797927</v>
       </c>
       <c r="C21">
-        <v>3411.723291188001</v>
+        <v>3388.312261734329</v>
       </c>
       <c r="D21">
-        <v>4233.810291188001</v>
+        <v>4254.872261734329</v>
       </c>
       <c r="E21">
-        <v>-453.0129999999999</v>
+        <v>-408.54</v>
       </c>
       <c r="F21">
-        <v>844.9870000000001</v>
+        <v>889.46</v>
       </c>
       <c r="G21">
         <v>22.9</v>
@@ -3256,28 +3256,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M21">
-        <v>45.2068045</v>
+        <v>47.58611</v>
       </c>
       <c r="N21">
-        <v>326.7487510555555</v>
+        <v>324.3694455555556</v>
       </c>
       <c r="O21">
-        <v>98.02462531666666</v>
+        <v>97.31083366666667</v>
       </c>
       <c r="P21">
-        <v>228.7241257388889</v>
+        <v>227.0586118888889</v>
       </c>
       <c r="Q21">
-        <v>325.3241257388888</v>
+        <v>323.6586118888889</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.109563712270258</v>
+        <v>0.1101553691974741</v>
       </c>
       <c r="T21">
-        <v>1.47260305474037</v>
+        <v>1.48626718700864</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.227866571625418</v>
+        <v>7.816473243044149</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3302,22 +3302,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09561429535797927</v>
+        <v>0.09548408377704956</v>
       </c>
       <c r="C22">
-        <v>3388.312261734329</v>
+        <v>3354.99039106461</v>
       </c>
       <c r="D22">
-        <v>4254.872261734329</v>
+        <v>4266.02339106461</v>
       </c>
       <c r="E22">
-        <v>-408.54</v>
+        <v>-364.0669999999999</v>
       </c>
       <c r="F22">
-        <v>889.46</v>
+        <v>933.9330000000001</v>
       </c>
       <c r="G22">
         <v>22.9</v>
@@ -3338,45 +3338,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M22">
-        <v>47.58611</v>
+        <v>50.7125619</v>
       </c>
       <c r="N22">
-        <v>324.3694455555556</v>
+        <v>321.2429936555556</v>
       </c>
       <c r="O22">
-        <v>97.31083366666667</v>
+        <v>96.37289809666666</v>
       </c>
       <c r="P22">
-        <v>227.0586118888889</v>
+        <v>224.8700955588889</v>
       </c>
       <c r="Q22">
-        <v>323.6586118888889</v>
+        <v>321.4700955588888</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1101553691974741</v>
+        <v>0.1107620047810754</v>
       </c>
       <c r="T22">
-        <v>1.48626718700864</v>
+        <v>1.500277246676107</v>
       </c>
       <c r="U22">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V22">
         <v>0.3</v>
       </c>
       <c r="W22">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y22">
-        <v>7.816473243044149</v>
+        <v>7.334584205960921</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3384,22 +3384,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09548408377704953</v>
+        <v>0.09524187219611983</v>
       </c>
       <c r="C23">
-        <v>3354.990391064613</v>
+        <v>3331.416281497688</v>
       </c>
       <c r="D23">
-        <v>4266.023391064613</v>
+        <v>4286.922281497688</v>
       </c>
       <c r="E23">
-        <v>-364.067</v>
+        <v>-319.5939999999999</v>
       </c>
       <c r="F23">
-        <v>933.933</v>
+        <v>978.4060000000001</v>
       </c>
       <c r="G23">
         <v>22.9</v>
@@ -3420,28 +3420,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M23">
-        <v>50.7125619</v>
+        <v>53.1274458</v>
       </c>
       <c r="N23">
-        <v>321.2429936555556</v>
+        <v>318.8281097555556</v>
       </c>
       <c r="O23">
-        <v>96.37289809666666</v>
+        <v>95.64843292666667</v>
       </c>
       <c r="P23">
-        <v>224.8700955588889</v>
+        <v>223.1796768288889</v>
       </c>
       <c r="Q23">
-        <v>321.4700955588888</v>
+        <v>319.7796768288889</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1107620047810754</v>
+        <v>0.1113841951232306</v>
       </c>
       <c r="T23">
-        <v>1.500277246676106</v>
+        <v>1.514646538642739</v>
       </c>
       <c r="U23">
         <v>0.0543</v>
@@ -3458,7 +3458,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>7.334584205960922</v>
+        <v>7.00119401478088</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3466,22 +3466,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09524187219611983</v>
+        <v>0.09499966061519011</v>
       </c>
       <c r="C24">
-        <v>3331.416281497688</v>
+        <v>3308.047943809197</v>
       </c>
       <c r="D24">
-        <v>4286.922281497688</v>
+        <v>4308.026943809197</v>
       </c>
       <c r="E24">
-        <v>-319.5939999999999</v>
+        <v>-275.1209999999999</v>
       </c>
       <c r="F24">
-        <v>978.4060000000001</v>
+        <v>1022.879</v>
       </c>
       <c r="G24">
         <v>22.9</v>
@@ -3502,28 +3502,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M24">
-        <v>53.1274458</v>
+        <v>55.54232970000001</v>
       </c>
       <c r="N24">
-        <v>318.8281097555556</v>
+        <v>316.4132258555555</v>
       </c>
       <c r="O24">
-        <v>95.64843292666667</v>
+        <v>94.92396775666666</v>
       </c>
       <c r="P24">
-        <v>223.1796768288889</v>
+        <v>221.4892580988889</v>
       </c>
       <c r="Q24">
-        <v>319.7796768288889</v>
+        <v>318.0892580988889</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1113841951232306</v>
+        <v>0.1120225462534936</v>
       </c>
       <c r="T24">
-        <v>1.514646538642739</v>
+        <v>1.52938905897214</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.00119401478088</v>
+        <v>6.696794275007796</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3548,22 +3548,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09499966061519011</v>
+        <v>0.09475744903426041</v>
       </c>
       <c r="C25">
-        <v>3308.047943809197</v>
+        <v>3284.888432100172</v>
       </c>
       <c r="D25">
-        <v>4308.026943809197</v>
+        <v>4329.340432100173</v>
       </c>
       <c r="E25">
-        <v>-275.1209999999999</v>
+        <v>-230.6479999999999</v>
       </c>
       <c r="F25">
-        <v>1022.879</v>
+        <v>1067.352</v>
       </c>
       <c r="G25">
         <v>22.9</v>
@@ -3584,28 +3584,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M25">
-        <v>55.54232970000001</v>
+        <v>57.9572136</v>
       </c>
       <c r="N25">
-        <v>316.4132258555555</v>
+        <v>313.9983419555556</v>
       </c>
       <c r="O25">
-        <v>94.92396775666666</v>
+        <v>94.19950258666667</v>
       </c>
       <c r="P25">
-        <v>221.4892580988889</v>
+        <v>219.7988393688889</v>
       </c>
       <c r="Q25">
-        <v>318.0892580988889</v>
+        <v>316.3988393688889</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1120225462534936</v>
+        <v>0.1126776960977111</v>
       </c>
       <c r="T25">
-        <v>1.52938905897214</v>
+        <v>1.544519540362842</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3622,7 +3622,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>6.696794275007796</v>
+        <v>6.417761180215806</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3630,22 +3630,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09475744903426041</v>
+        <v>0.09451523745333067</v>
       </c>
       <c r="C26">
-        <v>3284.888432100172</v>
+        <v>3261.940861211478</v>
       </c>
       <c r="D26">
-        <v>4329.340432100173</v>
+        <v>4350.865861211478</v>
       </c>
       <c r="E26">
-        <v>-230.6479999999999</v>
+        <v>-186.175</v>
       </c>
       <c r="F26">
-        <v>1067.352</v>
+        <v>1111.825</v>
       </c>
       <c r="G26">
         <v>22.9</v>
@@ -3666,28 +3666,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M26">
-        <v>57.9572136</v>
+        <v>60.3720975</v>
       </c>
       <c r="N26">
-        <v>313.9983419555556</v>
+        <v>311.5834580555556</v>
       </c>
       <c r="O26">
-        <v>94.19950258666667</v>
+        <v>93.47503741666667</v>
       </c>
       <c r="P26">
-        <v>219.7988393688889</v>
+        <v>218.1084206388889</v>
       </c>
       <c r="Q26">
-        <v>316.3988393688889</v>
+        <v>314.7084206388889</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1126776960977111</v>
+        <v>0.1133503166044409</v>
       </c>
       <c r="T26">
-        <v>1.544519540362842</v>
+        <v>1.560053501257296</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3704,7 +3704,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.417761180215806</v>
+        <v>6.161050733007174</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3712,22 +3712,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09451523745333067</v>
+        <v>0.09445502587240093</v>
       </c>
       <c r="C27">
-        <v>3261.940861211478</v>
+        <v>3222.852145922451</v>
       </c>
       <c r="D27">
-        <v>4350.865861211478</v>
+        <v>4356.250145922451</v>
       </c>
       <c r="E27">
-        <v>-186.175</v>
+        <v>-141.702</v>
       </c>
       <c r="F27">
-        <v>1111.825</v>
+        <v>1156.298</v>
       </c>
       <c r="G27">
         <v>22.9</v>
@@ -3748,45 +3748,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M27">
-        <v>60.3720975</v>
+        <v>63.9432794</v>
       </c>
       <c r="N27">
-        <v>311.5834580555556</v>
+        <v>308.0122761555556</v>
       </c>
       <c r="O27">
-        <v>93.47503741666667</v>
+        <v>92.40368284666667</v>
       </c>
       <c r="P27">
-        <v>218.1084206388889</v>
+        <v>215.6085933088889</v>
       </c>
       <c r="Q27">
-        <v>314.7084206388889</v>
+        <v>312.2085933088889</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1133503166044409</v>
+        <v>0.1140411160437851</v>
       </c>
       <c r="T27">
-        <v>1.560053501257296</v>
+        <v>1.576007298932681</v>
       </c>
       <c r="U27">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V27">
         <v>0.3</v>
       </c>
       <c r="W27">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y27">
-        <v>6.161050733007174</v>
+        <v>5.816960891679815</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3794,22 +3794,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09445502587240093</v>
+        <v>0.09421981429147122</v>
       </c>
       <c r="C28">
-        <v>3222.852145922451</v>
+        <v>3199.540740586562</v>
       </c>
       <c r="D28">
-        <v>4356.250145922451</v>
+        <v>4377.411740586563</v>
       </c>
       <c r="E28">
-        <v>-141.702</v>
+        <v>-97.22899999999981</v>
       </c>
       <c r="F28">
-        <v>1156.298</v>
+        <v>1200.771</v>
       </c>
       <c r="G28">
         <v>22.9</v>
@@ -3830,28 +3830,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M28">
-        <v>63.9432794</v>
+        <v>66.40263630000001</v>
       </c>
       <c r="N28">
-        <v>308.0122761555556</v>
+        <v>305.5529192555556</v>
       </c>
       <c r="O28">
-        <v>92.40368284666667</v>
+        <v>91.66587577666668</v>
       </c>
       <c r="P28">
-        <v>215.6085933088889</v>
+        <v>213.8870434788889</v>
       </c>
       <c r="Q28">
-        <v>312.2085933088889</v>
+        <v>310.4870434788889</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1140411160437851</v>
+        <v>0.1147508414951661</v>
       </c>
       <c r="T28">
-        <v>1.576007298932681</v>
+        <v>1.592398186955337</v>
       </c>
       <c r="U28">
         <v>0.0553</v>
@@ -3868,7 +3868,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.816960891679815</v>
+        <v>5.601517895691674</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3876,22 +3876,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09421981429147122</v>
+        <v>0.0939846027105415</v>
       </c>
       <c r="C29">
-        <v>3199.540740586562</v>
+        <v>3176.435934531605</v>
       </c>
       <c r="D29">
-        <v>4377.411740586563</v>
+        <v>4398.779934531605</v>
       </c>
       <c r="E29">
-        <v>-97.22899999999981</v>
+        <v>-52.75599999999986</v>
       </c>
       <c r="F29">
-        <v>1200.771</v>
+        <v>1245.244</v>
       </c>
       <c r="G29">
         <v>22.9</v>
@@ -3912,28 +3912,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M29">
-        <v>66.40263630000001</v>
+        <v>68.86199320000001</v>
       </c>
       <c r="N29">
-        <v>305.5529192555556</v>
+        <v>303.0935623555555</v>
       </c>
       <c r="O29">
-        <v>91.66587577666668</v>
+        <v>90.92806870666666</v>
       </c>
       <c r="P29">
-        <v>213.8870434788889</v>
+        <v>212.1654936488889</v>
       </c>
       <c r="Q29">
-        <v>310.4870434788889</v>
+        <v>308.7654936488889</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1147508414951661</v>
+        <v>0.1154802815424188</v>
       </c>
       <c r="T29">
-        <v>1.592398186955337</v>
+        <v>1.609244377423066</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3950,7 +3950,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.601517895691674</v>
+        <v>5.401463685131256</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3958,22 +3958,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.0939846027105415</v>
+        <v>0.09374939112961178</v>
       </c>
       <c r="C30">
-        <v>3176.435934531605</v>
+        <v>3153.540768122158</v>
       </c>
       <c r="D30">
-        <v>4398.779934531605</v>
+        <v>4420.357768122159</v>
       </c>
       <c r="E30">
-        <v>-52.75599999999986</v>
+        <v>-8.282999999999902</v>
       </c>
       <c r="F30">
-        <v>1245.244</v>
+        <v>1289.717</v>
       </c>
       <c r="G30">
         <v>22.9</v>
@@ -3994,28 +3994,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M30">
-        <v>68.86199320000001</v>
+        <v>71.3213501</v>
       </c>
       <c r="N30">
-        <v>303.0935623555555</v>
+        <v>300.6342054555556</v>
       </c>
       <c r="O30">
-        <v>90.92806870666666</v>
+        <v>90.19026163666666</v>
       </c>
       <c r="P30">
-        <v>212.1654936488889</v>
+        <v>210.4439438188889</v>
       </c>
       <c r="Q30">
-        <v>308.7654936488889</v>
+        <v>307.0439438188889</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1154802815424188</v>
+        <v>0.1162302691966363</v>
       </c>
       <c r="T30">
-        <v>1.609244377423066</v>
+        <v>1.626565108467352</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -4032,7 +4032,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.401463685131256</v>
+        <v>5.215206316678454</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4040,22 +4040,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09374939112961178</v>
+        <v>0.09351417954868206</v>
       </c>
       <c r="C31">
-        <v>3153.540768122159</v>
+        <v>3130.858341673866</v>
       </c>
       <c r="D31">
-        <v>4420.357768122159</v>
+        <v>4442.148341673867</v>
       </c>
       <c r="E31">
-        <v>-8.283000000000129</v>
+        <v>36.19000000000005</v>
       </c>
       <c r="F31">
-        <v>1289.717</v>
+        <v>1334.19</v>
       </c>
       <c r="G31">
         <v>22.9</v>
@@ -4076,28 +4076,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M31">
-        <v>71.32135009999999</v>
+        <v>73.78070700000001</v>
       </c>
       <c r="N31">
-        <v>300.6342054555556</v>
+        <v>298.1748485555556</v>
       </c>
       <c r="O31">
-        <v>90.19026163666668</v>
+        <v>89.45245456666667</v>
       </c>
       <c r="P31">
-        <v>210.443943818889</v>
+        <v>208.7223939888889</v>
       </c>
       <c r="Q31">
-        <v>307.0439438188889</v>
+        <v>305.3223939888888</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1162302691966363</v>
+        <v>0.1170016850695458</v>
       </c>
       <c r="T31">
-        <v>1.626565108467352</v>
+        <v>1.644380717541474</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -4114,7 +4114,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.215206316678456</v>
+        <v>5.041366106122506</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4122,22 +4122,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09351417954868206</v>
+        <v>0.09327896796775233</v>
       </c>
       <c r="C32">
-        <v>3130.858341673866</v>
+        <v>3108.391816938434</v>
       </c>
       <c r="D32">
-        <v>4442.148341673867</v>
+        <v>4464.154816938434</v>
       </c>
       <c r="E32">
-        <v>36.19000000000005</v>
+        <v>80.66300000000001</v>
       </c>
       <c r="F32">
-        <v>1334.19</v>
+        <v>1378.663</v>
       </c>
       <c r="G32">
         <v>22.9</v>
@@ -4158,28 +4158,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M32">
-        <v>73.78070700000001</v>
+        <v>76.24006390000001</v>
       </c>
       <c r="N32">
-        <v>298.1748485555556</v>
+        <v>295.7154916555556</v>
       </c>
       <c r="O32">
-        <v>89.45245456666667</v>
+        <v>88.71464749666667</v>
       </c>
       <c r="P32">
-        <v>208.7223939888889</v>
+        <v>207.0008441588889</v>
       </c>
       <c r="Q32">
-        <v>305.3223939888888</v>
+        <v>303.6008441588889</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1170016850695458</v>
+        <v>0.1177954608228295</v>
       </c>
       <c r="T32">
-        <v>1.644380717541474</v>
+        <v>1.662712721081513</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.041366106122506</v>
+        <v>4.87874139302178</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4204,22 +4204,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09327896796775233</v>
+        <v>0.09304375638682261</v>
       </c>
       <c r="C33">
-        <v>3108.391816938434</v>
+        <v>3086.144418632967</v>
       </c>
       <c r="D33">
-        <v>4464.154816938434</v>
+        <v>4486.380418632968</v>
       </c>
       <c r="E33">
-        <v>80.66300000000001</v>
+        <v>125.1360000000002</v>
       </c>
       <c r="F33">
-        <v>1378.663</v>
+        <v>1423.136</v>
       </c>
       <c r="G33">
         <v>22.9</v>
@@ -4240,28 +4240,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M33">
-        <v>76.24006390000001</v>
+        <v>78.69942080000001</v>
       </c>
       <c r="N33">
-        <v>295.7154916555556</v>
+        <v>293.2561347555555</v>
       </c>
       <c r="O33">
-        <v>88.71464749666667</v>
+        <v>87.97684042666666</v>
       </c>
       <c r="P33">
-        <v>207.0008441588889</v>
+        <v>205.2792943288889</v>
       </c>
       <c r="Q33">
-        <v>303.6008441588889</v>
+        <v>301.8792943288888</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1177954608228295</v>
+        <v>0.118612582921798</v>
       </c>
       <c r="T33">
-        <v>1.662712721081513</v>
+        <v>1.681583901196259</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>4.87874139302178</v>
+        <v>4.726280724489849</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4286,22 +4286,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09304375638682261</v>
+        <v>0.0928085448058929</v>
       </c>
       <c r="C34">
-        <v>3086.144418632967</v>
+        <v>3064.119436015255</v>
       </c>
       <c r="D34">
-        <v>4486.380418632968</v>
+        <v>4508.828436015256</v>
       </c>
       <c r="E34">
-        <v>125.1360000000002</v>
+        <v>169.6090000000002</v>
       </c>
       <c r="F34">
-        <v>1423.136</v>
+        <v>1467.609</v>
       </c>
       <c r="G34">
         <v>22.9</v>
@@ -4322,28 +4322,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M34">
-        <v>78.69942080000001</v>
+        <v>81.15877770000002</v>
       </c>
       <c r="N34">
-        <v>293.2561347555555</v>
+        <v>290.7967778555555</v>
       </c>
       <c r="O34">
-        <v>87.97684042666666</v>
+        <v>87.23903335666667</v>
       </c>
       <c r="P34">
-        <v>205.2792943288889</v>
+        <v>203.5577444988889</v>
       </c>
       <c r="Q34">
-        <v>301.8792943288888</v>
+        <v>300.1577444988889</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.118612582921798</v>
+        <v>0.1194540967252133</v>
       </c>
       <c r="T34">
-        <v>1.681583901196259</v>
+        <v>1.7010184001204</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4360,7 +4360,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.726280724489849</v>
+        <v>4.583060096475005</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4368,22 +4368,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.0928085448058929</v>
+        <v>0.09316833322496318</v>
       </c>
       <c r="C35">
-        <v>3064.119436015255</v>
+        <v>2985.399416025155</v>
       </c>
       <c r="D35">
-        <v>4508.828436015256</v>
+        <v>4474.581416025156</v>
       </c>
       <c r="E35">
-        <v>169.6090000000002</v>
+        <v>214.0820000000001</v>
       </c>
       <c r="F35">
-        <v>1467.609</v>
+        <v>1512.082</v>
       </c>
       <c r="G35">
         <v>22.9</v>
@@ -4404,45 +4404,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M35">
-        <v>81.15877770000002</v>
+        <v>87.39833960000001</v>
       </c>
       <c r="N35">
-        <v>290.7967778555555</v>
+        <v>284.5572159555555</v>
       </c>
       <c r="O35">
-        <v>87.23903335666667</v>
+        <v>85.36716478666666</v>
       </c>
       <c r="P35">
-        <v>203.5577444988889</v>
+        <v>199.1900511688889</v>
       </c>
       <c r="Q35">
-        <v>300.1577444988889</v>
+        <v>295.7900511688889</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1194540967252133</v>
+        <v>0.1203211109469139</v>
       </c>
       <c r="T35">
-        <v>1.7010184001204</v>
+        <v>1.721041823254363</v>
       </c>
       <c r="U35">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V35">
         <v>0.3</v>
       </c>
       <c r="W35">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y35">
-        <v>4.583060096475005</v>
+        <v>4.255865240208242</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4450,22 +4450,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09316833322496318</v>
+        <v>0.09295062164403345</v>
       </c>
       <c r="C36">
-        <v>2985.399416025155</v>
+        <v>2961.587186978212</v>
       </c>
       <c r="D36">
-        <v>4474.581416025156</v>
+        <v>4495.242186978213</v>
       </c>
       <c r="E36">
-        <v>214.0820000000001</v>
+        <v>258.5550000000003</v>
       </c>
       <c r="F36">
-        <v>1512.082</v>
+        <v>1556.555</v>
       </c>
       <c r="G36">
         <v>22.9</v>
@@ -4486,28 +4486,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M36">
-        <v>87.39833960000001</v>
+        <v>89.96887900000003</v>
       </c>
       <c r="N36">
-        <v>284.5572159555555</v>
+        <v>281.9866765555556</v>
       </c>
       <c r="O36">
-        <v>85.36716478666666</v>
+        <v>84.59600296666666</v>
       </c>
       <c r="P36">
-        <v>199.1900511688889</v>
+        <v>197.3906735888889</v>
       </c>
       <c r="Q36">
-        <v>295.7900511688889</v>
+        <v>293.9906735888889</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1203211109469139</v>
+        <v>0.1212148025292822</v>
       </c>
       <c r="T36">
-        <v>1.721041823254363</v>
+        <v>1.741681351715526</v>
       </c>
       <c r="U36">
         <v>0.0578</v>
@@ -4524,7 +4524,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.255865240208242</v>
+        <v>4.134269090488006</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4532,22 +4532,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09295062164403345</v>
+        <v>0.09273291006310372</v>
       </c>
       <c r="C37">
-        <v>2961.587186978212</v>
+        <v>2937.966639593512</v>
       </c>
       <c r="D37">
-        <v>4495.242186978213</v>
+        <v>4516.094639593513</v>
       </c>
       <c r="E37">
-        <v>258.5550000000003</v>
+        <v>303.0280000000002</v>
       </c>
       <c r="F37">
-        <v>1556.555</v>
+        <v>1601.028</v>
       </c>
       <c r="G37">
         <v>22.9</v>
@@ -4568,28 +4568,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M37">
-        <v>89.96887900000003</v>
+        <v>92.53941840000002</v>
       </c>
       <c r="N37">
-        <v>281.9866765555556</v>
+        <v>279.4161371555556</v>
       </c>
       <c r="O37">
-        <v>84.59600296666666</v>
+        <v>83.82484114666667</v>
       </c>
       <c r="P37">
-        <v>197.3906735888889</v>
+        <v>195.5912960088889</v>
       </c>
       <c r="Q37">
-        <v>293.9906735888889</v>
+        <v>292.1912960088889</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1212148025292822</v>
+        <v>0.1221364219735996</v>
       </c>
       <c r="T37">
-        <v>1.741681351715526</v>
+        <v>1.7629658654411</v>
       </c>
       <c r="U37">
         <v>0.0578</v>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.134269090488006</v>
+        <v>4.019428282418895</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4614,22 +4614,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09273291006310373</v>
+        <v>0.09342169848217402</v>
       </c>
       <c r="C38">
-        <v>2937.966639593511</v>
+        <v>2828.17396838645</v>
       </c>
       <c r="D38">
-        <v>4516.094639593512</v>
+        <v>4450.77496838645</v>
       </c>
       <c r="E38">
-        <v>303.028</v>
+        <v>347.501</v>
       </c>
       <c r="F38">
-        <v>1601.028</v>
+        <v>1645.501</v>
       </c>
       <c r="G38">
         <v>22.9</v>
@@ -4650,45 +4650,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M38">
-        <v>92.5394184</v>
+        <v>100.8692113</v>
       </c>
       <c r="N38">
-        <v>279.4161371555556</v>
+        <v>271.0863442555556</v>
       </c>
       <c r="O38">
-        <v>83.82484114666667</v>
+        <v>81.32590327666666</v>
       </c>
       <c r="P38">
-        <v>195.5912960088889</v>
+        <v>189.7604409788889</v>
       </c>
       <c r="Q38">
-        <v>292.1912960088889</v>
+        <v>286.3604409788888</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1221364219735996</v>
+        <v>0.123087299178054</v>
       </c>
       <c r="T38">
-        <v>1.7629658654411</v>
+        <v>1.784926078015104</v>
       </c>
       <c r="U38">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V38">
         <v>0.3</v>
       </c>
       <c r="W38">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y38">
-        <v>4.019428282418896</v>
+        <v>3.687503359665464</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4696,22 +4696,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09342169848217402</v>
+        <v>0.09322848690124427</v>
       </c>
       <c r="C39">
-        <v>2828.17396838645</v>
+        <v>2801.83229249542</v>
       </c>
       <c r="D39">
-        <v>4450.77496838645</v>
+        <v>4468.906292495421</v>
       </c>
       <c r="E39">
-        <v>347.501</v>
+        <v>391.9740000000002</v>
       </c>
       <c r="F39">
-        <v>1645.501</v>
+        <v>1689.974</v>
       </c>
       <c r="G39">
         <v>22.9</v>
@@ -4732,28 +4732,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M39">
-        <v>100.8692113</v>
+        <v>103.5954062</v>
       </c>
       <c r="N39">
-        <v>271.0863442555556</v>
+        <v>268.3601493555556</v>
       </c>
       <c r="O39">
-        <v>81.32590327666666</v>
+        <v>80.50804480666666</v>
       </c>
       <c r="P39">
-        <v>189.7604409788889</v>
+        <v>187.8521045488889</v>
       </c>
       <c r="Q39">
-        <v>286.3604409788888</v>
+        <v>284.4521045488889</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.123087299178054</v>
+        <v>0.1240688498407166</v>
       </c>
       <c r="T39">
-        <v>1.784926078015104</v>
+        <v>1.807594684543109</v>
       </c>
       <c r="U39">
         <v>0.0613</v>
@@ -4770,7 +4770,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.687503359665464</v>
+        <v>3.590463797569004</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4778,22 +4778,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09322848690124427</v>
+        <v>0.09379967532031458</v>
       </c>
       <c r="C40">
-        <v>2801.83229249542</v>
+        <v>2704.180026111851</v>
       </c>
       <c r="D40">
-        <v>4468.906292495421</v>
+        <v>4415.727026111852</v>
       </c>
       <c r="E40">
-        <v>391.9740000000002</v>
+        <v>436.4470000000001</v>
       </c>
       <c r="F40">
-        <v>1689.974</v>
+        <v>1734.447</v>
       </c>
       <c r="G40">
         <v>22.9</v>
@@ -4814,45 +4814,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M40">
-        <v>103.5954062</v>
+        <v>111.1780527</v>
       </c>
       <c r="N40">
-        <v>268.3601493555556</v>
+        <v>260.7775028555556</v>
       </c>
       <c r="O40">
-        <v>80.50804480666666</v>
+        <v>78.23325085666666</v>
       </c>
       <c r="P40">
-        <v>187.8521045488889</v>
+        <v>182.5442519988889</v>
       </c>
       <c r="Q40">
-        <v>284.4521045488889</v>
+        <v>279.1442519988889</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1240688498407166</v>
+        <v>0.125082582492319</v>
       </c>
       <c r="T40">
-        <v>1.807594684543109</v>
+        <v>1.831006524072032</v>
       </c>
       <c r="U40">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V40">
         <v>0.3</v>
       </c>
       <c r="W40">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>3.590463797569004</v>
+        <v>3.345584371397751</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4860,22 +4860,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09379967532031458</v>
+        <v>0.09362606373938487</v>
       </c>
       <c r="C41">
-        <v>2704.180026111851</v>
+        <v>2675.736389392401</v>
       </c>
       <c r="D41">
-        <v>4415.727026111852</v>
+        <v>4431.756389392402</v>
       </c>
       <c r="E41">
-        <v>436.4470000000001</v>
+        <v>480.9200000000001</v>
       </c>
       <c r="F41">
-        <v>1734.447</v>
+        <v>1778.92</v>
       </c>
       <c r="G41">
         <v>22.9</v>
@@ -4896,28 +4896,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M41">
-        <v>111.1780527</v>
+        <v>114.028772</v>
       </c>
       <c r="N41">
-        <v>260.7775028555556</v>
+        <v>257.9267835555556</v>
       </c>
       <c r="O41">
-        <v>78.23325085666666</v>
+        <v>77.37803506666667</v>
       </c>
       <c r="P41">
-        <v>182.5442519988889</v>
+        <v>180.5487484888889</v>
       </c>
       <c r="Q41">
-        <v>279.1442519988889</v>
+        <v>277.1487484888889</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.125082582492319</v>
+        <v>0.1261301062323081</v>
       </c>
       <c r="T41">
-        <v>1.831006524072032</v>
+        <v>1.85519875825192</v>
       </c>
       <c r="U41">
         <v>0.0641</v>
@@ -4934,7 +4934,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.345584371397751</v>
+        <v>3.261944762112807</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4942,22 +4942,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09362606373938487</v>
+        <v>0.09345245215845513</v>
       </c>
       <c r="C42">
-        <v>2675.736389392401</v>
+        <v>2647.40955182911</v>
       </c>
       <c r="D42">
-        <v>4431.756389392402</v>
+        <v>4447.90255182911</v>
       </c>
       <c r="E42">
-        <v>480.9200000000001</v>
+        <v>525.3930000000003</v>
       </c>
       <c r="F42">
-        <v>1778.92</v>
+        <v>1823.393</v>
       </c>
       <c r="G42">
         <v>22.9</v>
@@ -4978,28 +4978,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M42">
-        <v>114.028772</v>
+        <v>116.8794913</v>
       </c>
       <c r="N42">
-        <v>257.9267835555556</v>
+        <v>255.0760642555555</v>
       </c>
       <c r="O42">
-        <v>77.37803506666667</v>
+        <v>76.52281927666665</v>
       </c>
       <c r="P42">
-        <v>180.5487484888889</v>
+        <v>178.5532449788889</v>
       </c>
       <c r="Q42">
-        <v>277.1487484888889</v>
+        <v>275.1532449788888</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1261301062323081</v>
+        <v>0.1272131392516189</v>
       </c>
       <c r="T42">
-        <v>1.85519875825192</v>
+        <v>1.880211068166718</v>
       </c>
       <c r="U42">
         <v>0.0641</v>
@@ -5016,7 +5016,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.261944762112807</v>
+        <v>3.182385133768592</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5024,22 +5024,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09345245215845513</v>
+        <v>0.0932788405775254</v>
       </c>
       <c r="C43">
-        <v>2647.40955182911</v>
+        <v>2619.200794688695</v>
       </c>
       <c r="D43">
-        <v>4447.90255182911</v>
+        <v>4464.166794688696</v>
       </c>
       <c r="E43">
-        <v>525.3930000000003</v>
+        <v>569.8660000000002</v>
       </c>
       <c r="F43">
-        <v>1823.393</v>
+        <v>1867.866</v>
       </c>
       <c r="G43">
         <v>22.9</v>
@@ -5060,28 +5060,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M43">
-        <v>116.8794913</v>
+        <v>119.7302106</v>
       </c>
       <c r="N43">
-        <v>255.0760642555555</v>
+        <v>252.2253449555556</v>
       </c>
       <c r="O43">
-        <v>76.52281927666665</v>
+        <v>75.66760348666666</v>
       </c>
       <c r="P43">
-        <v>178.5532449788889</v>
+        <v>176.5577414688889</v>
       </c>
       <c r="Q43">
-        <v>275.1532449788888</v>
+        <v>273.1577414688888</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1272131392516189</v>
+        <v>0.1283335182371128</v>
       </c>
       <c r="T43">
-        <v>1.880211068166718</v>
+        <v>1.906085871526855</v>
       </c>
       <c r="U43">
         <v>0.0641</v>
@@ -5098,7 +5098,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.182385133768592</v>
+        <v>3.106614059155054</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5106,22 +5106,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09327884057752542</v>
+        <v>0.09310522899659569</v>
       </c>
       <c r="C44">
-        <v>2619.200794688694</v>
+        <v>2591.111418047027</v>
       </c>
       <c r="D44">
-        <v>4464.166794688695</v>
+        <v>4480.550418047027</v>
       </c>
       <c r="E44">
-        <v>569.866</v>
+        <v>614.3389999999999</v>
       </c>
       <c r="F44">
-        <v>1867.866</v>
+        <v>1912.339</v>
       </c>
       <c r="G44">
         <v>22.9</v>
@@ -5142,28 +5142,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M44">
-        <v>119.7302106</v>
+        <v>122.5809299</v>
       </c>
       <c r="N44">
-        <v>252.2253449555556</v>
+        <v>249.3746256555556</v>
       </c>
       <c r="O44">
-        <v>75.66760348666666</v>
+        <v>74.81238769666668</v>
       </c>
       <c r="P44">
-        <v>176.5577414688889</v>
+        <v>174.5622379588889</v>
       </c>
       <c r="Q44">
-        <v>273.1577414688888</v>
+        <v>271.1622379588889</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1283335182371128</v>
+        <v>0.1294932087659574</v>
       </c>
       <c r="T44">
-        <v>1.906085871526854</v>
+        <v>1.932868562724189</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -5180,7 +5180,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.106614059155055</v>
+        <v>3.034367220570053</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5188,22 +5188,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09310522899659569</v>
+        <v>0.09533401741566598</v>
       </c>
       <c r="C45">
-        <v>2591.111418047027</v>
+        <v>2345.035572087566</v>
       </c>
       <c r="D45">
-        <v>4480.550418047027</v>
+        <v>4278.947572087566</v>
       </c>
       <c r="E45">
-        <v>614.3389999999999</v>
+        <v>658.8120000000001</v>
       </c>
       <c r="F45">
-        <v>1912.339</v>
+        <v>1956.812</v>
       </c>
       <c r="G45">
         <v>22.9</v>
@@ -5224,45 +5224,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M45">
-        <v>122.5809299</v>
+        <v>140.6947828</v>
       </c>
       <c r="N45">
-        <v>249.3746256555556</v>
+        <v>231.2607727555556</v>
       </c>
       <c r="O45">
-        <v>74.81238769666668</v>
+        <v>69.37823182666666</v>
       </c>
       <c r="P45">
-        <v>174.5622379588889</v>
+        <v>161.8825409288889</v>
       </c>
       <c r="Q45">
-        <v>271.1622379588889</v>
+        <v>258.4825409288889</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1294932087659574</v>
+        <v>0.1306943168136892</v>
       </c>
       <c r="T45">
-        <v>1.932868562724189</v>
+        <v>1.960607778607142</v>
       </c>
       <c r="U45">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V45">
         <v>0.3</v>
       </c>
       <c r="W45">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y45">
-        <v>3.034367220570053</v>
+        <v>2.643705389447856</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5270,22 +5270,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09533401741566598</v>
+        <v>0.09521500583473626</v>
       </c>
       <c r="C46">
-        <v>2345.035572087566</v>
+        <v>2310.868031060346</v>
       </c>
       <c r="D46">
-        <v>4278.947572087566</v>
+        <v>4289.253031060346</v>
       </c>
       <c r="E46">
-        <v>658.8120000000001</v>
+        <v>703.2850000000001</v>
       </c>
       <c r="F46">
-        <v>1956.812</v>
+        <v>2001.285</v>
       </c>
       <c r="G46">
         <v>22.9</v>
@@ -5306,28 +5306,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M46">
-        <v>140.6947828</v>
+        <v>143.8923915</v>
       </c>
       <c r="N46">
-        <v>231.2607727555556</v>
+        <v>228.0631640555555</v>
       </c>
       <c r="O46">
-        <v>69.37823182666666</v>
+        <v>68.41894921666666</v>
       </c>
       <c r="P46">
-        <v>161.8825409288889</v>
+        <v>159.6442148388889</v>
       </c>
       <c r="Q46">
-        <v>258.4825409288889</v>
+        <v>256.2442148388889</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1306943168136892</v>
+        <v>0.1319391015177023</v>
       </c>
       <c r="T46">
-        <v>1.960607778607142</v>
+        <v>1.989355693249476</v>
       </c>
       <c r="U46">
         <v>0.07190000000000001</v>
@@ -5344,7 +5344,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>2.643705389447856</v>
+        <v>2.584956380793459</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5352,22 +5352,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09521500583473626</v>
+        <v>0.09509599425380653</v>
       </c>
       <c r="C47">
-        <v>2310.868031060346</v>
+        <v>2276.750249409445</v>
       </c>
       <c r="D47">
-        <v>4289.253031060346</v>
+        <v>4299.608249409445</v>
       </c>
       <c r="E47">
-        <v>703.2850000000001</v>
+        <v>747.7580000000003</v>
       </c>
       <c r="F47">
-        <v>2001.285</v>
+        <v>2045.758</v>
       </c>
       <c r="G47">
         <v>22.9</v>
@@ -5388,28 +5388,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M47">
-        <v>143.8923915</v>
+        <v>147.0900002</v>
       </c>
       <c r="N47">
-        <v>228.0631640555555</v>
+        <v>224.8655553555556</v>
       </c>
       <c r="O47">
-        <v>68.41894921666666</v>
+        <v>67.45966660666666</v>
       </c>
       <c r="P47">
-        <v>159.6442148388889</v>
+        <v>157.4058887488889</v>
       </c>
       <c r="Q47">
-        <v>256.2442148388889</v>
+        <v>254.0058887488889</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1319391015177023</v>
+        <v>0.133229989358901</v>
       </c>
       <c r="T47">
-        <v>1.989355693249476</v>
+        <v>2.019168345471155</v>
       </c>
       <c r="U47">
         <v>0.07190000000000001</v>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.584956380793459</v>
+        <v>2.528761676863167</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5434,22 +5434,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09509599425380653</v>
+        <v>0.09626008267287682</v>
       </c>
       <c r="C48">
-        <v>2276.750249409445</v>
+        <v>2133.087475937929</v>
       </c>
       <c r="D48">
-        <v>4299.608249409445</v>
+        <v>4200.41847593793</v>
       </c>
       <c r="E48">
-        <v>747.7580000000003</v>
+        <v>792.2310000000002</v>
       </c>
       <c r="F48">
-        <v>2045.758</v>
+        <v>2090.231</v>
       </c>
       <c r="G48">
         <v>22.9</v>
@@ -5470,45 +5470,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M48">
-        <v>147.0900002</v>
+        <v>158.4395098</v>
       </c>
       <c r="N48">
-        <v>224.8655553555556</v>
+        <v>213.5160457555556</v>
       </c>
       <c r="O48">
-        <v>67.45966660666666</v>
+        <v>64.05481372666667</v>
       </c>
       <c r="P48">
-        <v>157.4058887488889</v>
+        <v>149.4612320288889</v>
       </c>
       <c r="Q48">
-        <v>254.0058887488889</v>
+        <v>246.0612320288889</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.133229989358901</v>
+        <v>0.1345695899488242</v>
       </c>
       <c r="T48">
-        <v>2.019168345471155</v>
+        <v>2.050106003437048</v>
       </c>
       <c r="U48">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y48">
-        <v>2.528761676863167</v>
+        <v>2.347618697035097</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5516,22 +5516,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09626008267287682</v>
+        <v>0.09616837109194708</v>
       </c>
       <c r="C49">
-        <v>2133.087475937929</v>
+        <v>2096.262668854304</v>
       </c>
       <c r="D49">
-        <v>4200.41847593793</v>
+        <v>4208.066668854304</v>
       </c>
       <c r="E49">
-        <v>792.2310000000002</v>
+        <v>836.7040000000002</v>
       </c>
       <c r="F49">
-        <v>2090.231</v>
+        <v>2134.704</v>
       </c>
       <c r="G49">
         <v>22.9</v>
@@ -5552,28 +5552,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M49">
-        <v>158.4395098</v>
+        <v>161.8105632</v>
       </c>
       <c r="N49">
-        <v>213.5160457555556</v>
+        <v>210.1449923555556</v>
       </c>
       <c r="O49">
-        <v>64.05481372666667</v>
+        <v>63.04349770666666</v>
       </c>
       <c r="P49">
-        <v>149.4612320288889</v>
+        <v>147.1014946488889</v>
       </c>
       <c r="Q49">
-        <v>246.0612320288889</v>
+        <v>243.7014946488889</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1345695899488242</v>
+        <v>0.1359607136383598</v>
       </c>
       <c r="T49">
-        <v>2.050106003437048</v>
+        <v>2.082233571324707</v>
       </c>
       <c r="U49">
         <v>0.07580000000000001</v>
@@ -5590,7 +5590,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.347618697035097</v>
+        <v>2.298709974180199</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5598,22 +5598,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09616837109194708</v>
+        <v>0.09607665951101738</v>
       </c>
       <c r="C50">
-        <v>2096.262668854304</v>
+        <v>2059.465764494143</v>
       </c>
       <c r="D50">
-        <v>4208.066668854304</v>
+        <v>4215.742764494144</v>
       </c>
       <c r="E50">
-        <v>836.7040000000002</v>
+        <v>881.1770000000001</v>
       </c>
       <c r="F50">
-        <v>2134.704</v>
+        <v>2179.177</v>
       </c>
       <c r="G50">
         <v>22.9</v>
@@ -5634,28 +5634,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M50">
-        <v>161.8105632</v>
+        <v>165.1816166</v>
       </c>
       <c r="N50">
-        <v>210.1449923555556</v>
+        <v>206.7739389555556</v>
       </c>
       <c r="O50">
-        <v>63.04349770666666</v>
+        <v>62.03218168666667</v>
       </c>
       <c r="P50">
-        <v>147.1014946488889</v>
+        <v>144.7417572688889</v>
       </c>
       <c r="Q50">
-        <v>243.7014946488889</v>
+        <v>241.3417572688889</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1359607136383598</v>
+        <v>0.1374063911980733</v>
       </c>
       <c r="T50">
-        <v>2.082233571324707</v>
+        <v>2.115621043835411</v>
       </c>
       <c r="U50">
         <v>0.07580000000000001</v>
@@ -5672,7 +5672,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.298709974180199</v>
+        <v>2.251797525727542</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5680,22 +5680,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09607665951101738</v>
+        <v>0.09598494793008765</v>
       </c>
       <c r="C51">
-        <v>2059.465764494143</v>
+        <v>2022.696915831779</v>
       </c>
       <c r="D51">
-        <v>4215.742764494144</v>
+        <v>4223.44691583178</v>
       </c>
       <c r="E51">
-        <v>881.1770000000001</v>
+        <v>925.6500000000001</v>
       </c>
       <c r="F51">
-        <v>2179.177</v>
+        <v>2223.65</v>
       </c>
       <c r="G51">
         <v>22.9</v>
@@ -5716,28 +5716,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M51">
-        <v>165.1816166</v>
+        <v>168.55267</v>
       </c>
       <c r="N51">
-        <v>206.7739389555556</v>
+        <v>203.4028855555555</v>
       </c>
       <c r="O51">
-        <v>62.03218168666667</v>
+        <v>61.02086566666666</v>
       </c>
       <c r="P51">
-        <v>144.7417572688889</v>
+        <v>142.3820198888889</v>
       </c>
       <c r="Q51">
-        <v>241.3417572688889</v>
+        <v>238.9820198888889</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1374063911980733</v>
+        <v>0.1389098958601753</v>
       </c>
       <c r="T51">
-        <v>2.115621043835411</v>
+        <v>2.150344015246543</v>
       </c>
       <c r="U51">
         <v>0.07580000000000001</v>
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.251797525727542</v>
+        <v>2.206761575212991</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5762,22 +5762,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09598494793008765</v>
+        <v>0.09589323634915793</v>
       </c>
       <c r="C52">
-        <v>2022.696915831779</v>
+        <v>1985.95627696181</v>
       </c>
       <c r="D52">
-        <v>4223.44691583178</v>
+        <v>4231.179276961811</v>
       </c>
       <c r="E52">
-        <v>925.6500000000001</v>
+        <v>970.123</v>
       </c>
       <c r="F52">
-        <v>2223.65</v>
+        <v>2268.123</v>
       </c>
       <c r="G52">
         <v>22.9</v>
@@ -5798,28 +5798,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M52">
-        <v>168.55267</v>
+        <v>171.9237234</v>
       </c>
       <c r="N52">
-        <v>203.4028855555555</v>
+        <v>200.0318321555555</v>
       </c>
       <c r="O52">
-        <v>61.02086566666666</v>
+        <v>60.00954964666666</v>
       </c>
       <c r="P52">
-        <v>142.3820198888889</v>
+        <v>140.0222825088889</v>
       </c>
       <c r="Q52">
-        <v>238.9820198888889</v>
+        <v>236.6222825088888</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1389098958601753</v>
+        <v>0.140474768059506</v>
       </c>
       <c r="T52">
-        <v>2.150344015246543</v>
+        <v>2.186484250796906</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5836,7 +5836,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.206761575212991</v>
+        <v>2.163491740404893</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5844,22 +5844,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09589323634915793</v>
+        <v>0.0958015247682282</v>
       </c>
       <c r="C53">
-        <v>1985.95627696181</v>
+        <v>1949.244003109383</v>
       </c>
       <c r="D53">
-        <v>4231.179276961811</v>
+        <v>4238.940003109384</v>
       </c>
       <c r="E53">
-        <v>970.123</v>
+        <v>1014.596</v>
       </c>
       <c r="F53">
-        <v>2268.123</v>
+        <v>2312.596</v>
       </c>
       <c r="G53">
         <v>22.9</v>
@@ -5880,28 +5880,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M53">
-        <v>171.9237234</v>
+        <v>175.2947768</v>
       </c>
       <c r="N53">
-        <v>200.0318321555555</v>
+        <v>196.6607787555556</v>
       </c>
       <c r="O53">
-        <v>60.00954964666666</v>
+        <v>58.99823362666666</v>
       </c>
       <c r="P53">
-        <v>140.0222825088889</v>
+        <v>137.6625451288889</v>
       </c>
       <c r="Q53">
-        <v>236.6222825088888</v>
+        <v>234.2625451288889</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.140474768059506</v>
+        <v>0.1421048432671421</v>
       </c>
       <c r="T53">
-        <v>2.186484250796906</v>
+        <v>2.224130329495199</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5918,7 +5918,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.163491740404893</v>
+        <v>2.121886130012492</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5926,22 +5926,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.0958015247682282</v>
+        <v>0.09570981318729847</v>
       </c>
       <c r="C54">
-        <v>1949.244003109383</v>
+        <v>1912.560250640575</v>
       </c>
       <c r="D54">
-        <v>4238.940003109384</v>
+        <v>4246.729250640576</v>
       </c>
       <c r="E54">
-        <v>1014.596</v>
+        <v>1059.069</v>
       </c>
       <c r="F54">
-        <v>2312.596</v>
+        <v>2357.069</v>
       </c>
       <c r="G54">
         <v>22.9</v>
@@ -5962,28 +5962,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M54">
-        <v>175.2947768</v>
+        <v>178.6658302</v>
       </c>
       <c r="N54">
-        <v>196.6607787555556</v>
+        <v>193.2897253555555</v>
       </c>
       <c r="O54">
-        <v>58.99823362666666</v>
+        <v>57.98691760666666</v>
       </c>
       <c r="P54">
-        <v>137.6625451288889</v>
+        <v>135.3028077488889</v>
       </c>
       <c r="Q54">
-        <v>234.2625451288889</v>
+        <v>231.9028077488888</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1421048432671421</v>
+        <v>0.1438042833772308</v>
       </c>
       <c r="T54">
-        <v>2.224130329495199</v>
+        <v>2.263378368989165</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -6000,7 +6000,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.121886130012492</v>
+        <v>2.081850542653765</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6008,22 +6008,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09570981318729847</v>
+        <v>0.09561810160636876</v>
       </c>
       <c r="C55">
-        <v>1912.560250640575</v>
+        <v>1875.9051770729</v>
       </c>
       <c r="D55">
-        <v>4246.729250640576</v>
+        <v>4254.547177072901</v>
       </c>
       <c r="E55">
-        <v>1059.069</v>
+        <v>1103.542</v>
       </c>
       <c r="F55">
-        <v>2357.069</v>
+        <v>2401.542</v>
       </c>
       <c r="G55">
         <v>22.9</v>
@@ -6044,28 +6044,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M55">
-        <v>178.6658302</v>
+        <v>182.0368836</v>
       </c>
       <c r="N55">
-        <v>193.2897253555555</v>
+        <v>189.9186719555555</v>
       </c>
       <c r="O55">
-        <v>57.98691760666666</v>
+        <v>56.97560158666666</v>
       </c>
       <c r="P55">
-        <v>135.3028077488889</v>
+        <v>132.9430703688889</v>
       </c>
       <c r="Q55">
-        <v>231.9028077488888</v>
+        <v>229.5430703688888</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1438042833772308</v>
+        <v>0.1455776121877582</v>
       </c>
       <c r="T55">
-        <v>2.263378368989165</v>
+        <v>2.304332844982869</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.081850542653765</v>
+        <v>2.043297754826844</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6090,22 +6090,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09561810160636876</v>
+        <v>0.09552639002543904</v>
       </c>
       <c r="C56">
-        <v>1875.9051770729</v>
+        <v>1839.278941085929</v>
       </c>
       <c r="D56">
-        <v>4254.547177072901</v>
+        <v>4262.393941085929</v>
       </c>
       <c r="E56">
-        <v>1103.542</v>
+        <v>1148.015</v>
       </c>
       <c r="F56">
-        <v>2401.542</v>
+        <v>2446.015</v>
       </c>
       <c r="G56">
         <v>22.9</v>
@@ -6126,28 +6126,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M56">
-        <v>182.0368836</v>
+        <v>185.407937</v>
       </c>
       <c r="N56">
-        <v>189.9186719555555</v>
+        <v>186.5476185555555</v>
       </c>
       <c r="O56">
-        <v>56.97560158666666</v>
+        <v>55.96428556666666</v>
       </c>
       <c r="P56">
-        <v>132.9430703688889</v>
+        <v>130.5833329888889</v>
       </c>
       <c r="Q56">
-        <v>229.5430703688888</v>
+        <v>227.1833329888888</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1455776121877582</v>
+        <v>0.1474297556120868</v>
       </c>
       <c r="T56">
-        <v>2.304332844982869</v>
+        <v>2.347107519909626</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -6164,7 +6164,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.043297754826844</v>
+        <v>2.006146886557265</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6172,22 +6172,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09552639002543904</v>
+        <v>0.1010010784445093</v>
       </c>
       <c r="C57">
-        <v>1839.278941085929</v>
+        <v>1372.073643016135</v>
       </c>
       <c r="D57">
-        <v>4262.393941085929</v>
+        <v>3839.661643016135</v>
       </c>
       <c r="E57">
-        <v>1148.015</v>
+        <v>1192.488</v>
       </c>
       <c r="F57">
-        <v>2446.015</v>
+        <v>2490.488</v>
       </c>
       <c r="G57">
         <v>22.9</v>
@@ -6208,45 +6208,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M57">
-        <v>185.407937</v>
+        <v>224.14392</v>
       </c>
       <c r="N57">
-        <v>186.5476185555555</v>
+        <v>147.8116355555556</v>
       </c>
       <c r="O57">
-        <v>55.96428556666666</v>
+        <v>44.34349066666667</v>
       </c>
       <c r="P57">
-        <v>130.5833329888889</v>
+        <v>103.4681448888889</v>
       </c>
       <c r="Q57">
-        <v>227.1833329888888</v>
+        <v>200.0681448888889</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1474297556120868</v>
+        <v>0.1493660873738848</v>
       </c>
       <c r="T57">
-        <v>2.347107519909626</v>
+        <v>2.391826498242144</v>
       </c>
       <c r="U57">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y57">
-        <v>2.006146886557265</v>
+        <v>1.659449676598658</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6254,22 +6254,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1010010784445093</v>
+        <v>0.1010087668635796</v>
       </c>
       <c r="C58">
-        <v>1372.073643016135</v>
+        <v>1327.065928522827</v>
       </c>
       <c r="D58">
-        <v>3839.661643016135</v>
+        <v>3839.126928522827</v>
       </c>
       <c r="E58">
-        <v>1192.488</v>
+        <v>1236.961</v>
       </c>
       <c r="F58">
-        <v>2490.488</v>
+        <v>2534.961</v>
       </c>
       <c r="G58">
         <v>22.9</v>
@@ -6290,28 +6290,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M58">
-        <v>224.14392</v>
+        <v>228.14649</v>
       </c>
       <c r="N58">
-        <v>147.8116355555556</v>
+        <v>143.8090655555556</v>
       </c>
       <c r="O58">
-        <v>44.34349066666667</v>
+        <v>43.14271966666667</v>
       </c>
       <c r="P58">
-        <v>103.4681448888889</v>
+        <v>100.6663458888889</v>
       </c>
       <c r="Q58">
-        <v>200.0681448888889</v>
+        <v>197.2663458888889</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1493660873738848</v>
+        <v>0.1513924810780921</v>
       </c>
       <c r="T58">
-        <v>2.391826498242144</v>
+        <v>2.438625429055245</v>
       </c>
       <c r="U58">
         <v>0.09</v>
@@ -6328,7 +6328,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>1.659449676598658</v>
+        <v>1.630336524377629</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6336,22 +6336,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1010087668635796</v>
+        <v>0.1010164552826499</v>
       </c>
       <c r="C59">
-        <v>1327.065928522827</v>
+        <v>1282.058362938358</v>
       </c>
       <c r="D59">
-        <v>3839.126928522827</v>
+        <v>3838.592362938358</v>
       </c>
       <c r="E59">
-        <v>1236.961</v>
+        <v>1281.434</v>
       </c>
       <c r="F59">
-        <v>2534.961</v>
+        <v>2579.434</v>
       </c>
       <c r="G59">
         <v>22.9</v>
@@ -6372,28 +6372,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M59">
-        <v>228.14649</v>
+        <v>232.14906</v>
       </c>
       <c r="N59">
-        <v>143.8090655555556</v>
+        <v>139.8064955555556</v>
       </c>
       <c r="O59">
-        <v>43.14271966666667</v>
+        <v>41.94194866666667</v>
       </c>
       <c r="P59">
-        <v>100.6663458888889</v>
+        <v>97.8645468888889</v>
       </c>
       <c r="Q59">
-        <v>197.2663458888889</v>
+        <v>194.4645468888889</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1513924810780921</v>
+        <v>0.1535153697205949</v>
       </c>
       <c r="T59">
-        <v>2.438625429055245</v>
+        <v>2.487652880383256</v>
       </c>
       <c r="U59">
         <v>0.09</v>
@@ -6410,7 +6410,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>1.630336524377629</v>
+        <v>1.602227273957325</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6418,22 +6418,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1010164552826499</v>
+        <v>0.1010241437017201</v>
       </c>
       <c r="C60">
-        <v>1282.058362938358</v>
+        <v>1237.050946200534</v>
       </c>
       <c r="D60">
-        <v>3838.592362938358</v>
+        <v>3838.057946200534</v>
       </c>
       <c r="E60">
-        <v>1281.434</v>
+        <v>1325.907</v>
       </c>
       <c r="F60">
-        <v>2579.434</v>
+        <v>2623.907</v>
       </c>
       <c r="G60">
         <v>22.9</v>
@@ -6454,28 +6454,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M60">
-        <v>232.14906</v>
+        <v>236.15163</v>
       </c>
       <c r="N60">
-        <v>139.8064955555556</v>
+        <v>135.8039255555556</v>
       </c>
       <c r="O60">
-        <v>41.94194866666668</v>
+        <v>40.74117766666667</v>
       </c>
       <c r="P60">
-        <v>97.86454688888892</v>
+        <v>95.06274788888891</v>
       </c>
       <c r="Q60">
-        <v>194.4645468888889</v>
+        <v>191.6627478888889</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1535153697205949</v>
+        <v>0.1557418139066345</v>
       </c>
       <c r="T60">
-        <v>2.487652880383255</v>
+        <v>2.539071914702876</v>
       </c>
       <c r="U60">
         <v>0.09</v>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>1.602227273957326</v>
+        <v>1.575070879483472</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6500,22 +6500,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1010241437017201</v>
+        <v>0.1010318321207904</v>
       </c>
       <c r="C61">
-        <v>1237.050946200534</v>
+        <v>1192.043678247194</v>
       </c>
       <c r="D61">
-        <v>3838.057946200534</v>
+        <v>3837.523678247194</v>
       </c>
       <c r="E61">
-        <v>1325.907</v>
+        <v>1370.38</v>
       </c>
       <c r="F61">
-        <v>2623.907</v>
+        <v>2668.38</v>
       </c>
       <c r="G61">
         <v>22.9</v>
@@ -6536,28 +6536,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M61">
-        <v>236.15163</v>
+        <v>240.1542</v>
       </c>
       <c r="N61">
-        <v>135.8039255555556</v>
+        <v>131.8013555555556</v>
       </c>
       <c r="O61">
-        <v>40.74117766666667</v>
+        <v>39.54040666666667</v>
       </c>
       <c r="P61">
-        <v>95.06274788888891</v>
+        <v>92.2609488888889</v>
       </c>
       <c r="Q61">
-        <v>191.6627478888889</v>
+        <v>188.8609488888889</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1557418139066345</v>
+        <v>0.1580795803019761</v>
       </c>
       <c r="T61">
-        <v>2.539071914702876</v>
+        <v>2.593061900738478</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6574,7 +6574,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.575070879483472</v>
+        <v>1.548819698158748</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6582,22 +6582,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1010318321207904</v>
+        <v>0.1010395205398607</v>
       </c>
       <c r="C62">
-        <v>1192.043678247194</v>
+        <v>1147.036559016213</v>
       </c>
       <c r="D62">
-        <v>3837.523678247194</v>
+        <v>3836.989559016213</v>
       </c>
       <c r="E62">
-        <v>1370.38</v>
+        <v>1414.853</v>
       </c>
       <c r="F62">
-        <v>2668.38</v>
+        <v>2712.853</v>
       </c>
       <c r="G62">
         <v>22.9</v>
@@ -6618,28 +6618,28 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M62">
-        <v>240.1542</v>
+        <v>244.15677</v>
       </c>
       <c r="N62">
-        <v>131.8013555555556</v>
+        <v>127.7987855555556</v>
       </c>
       <c r="O62">
-        <v>39.54040666666667</v>
+        <v>38.33963566666667</v>
       </c>
       <c r="P62">
-        <v>92.2609488888889</v>
+        <v>89.4591498888889</v>
       </c>
       <c r="Q62">
-        <v>188.8609488888889</v>
+        <v>186.0591498888889</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1580795803019761</v>
+        <v>0.160537232153489</v>
       </c>
       <c r="T62">
-        <v>2.593061900738478</v>
+        <v>2.649820604006675</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6656,7 +6656,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.548819698158748</v>
+        <v>1.523429211303686</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6664,22 +6664,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1010395205398607</v>
+        <v>0.1287383353924946</v>
       </c>
       <c r="C63">
-        <v>1147.036559016213</v>
+        <v>-178.8711705780474</v>
       </c>
       <c r="D63">
-        <v>3836.989559016213</v>
+        <v>2555.554829421952</v>
       </c>
       <c r="E63">
-        <v>1414.853</v>
+        <v>1459.326</v>
       </c>
       <c r="F63">
-        <v>2712.853</v>
+        <v>2757.326</v>
       </c>
       <c r="G63">
         <v>22.9</v>
@@ -6700,45 +6700,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M63">
-        <v>244.15677</v>
+        <v>404.7754568</v>
       </c>
       <c r="N63">
-        <v>127.7987855555556</v>
+        <v>-32.81990124444445</v>
       </c>
       <c r="O63">
-        <v>38.33963566666667</v>
+        <v>-9.845970373333335</v>
       </c>
       <c r="P63">
-        <v>89.4591498888889</v>
+        <v>-22.97393087111111</v>
       </c>
       <c r="Q63">
-        <v>186.0591498888889</v>
+        <v>73.62606912888884</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.160537232153489</v>
+        <v>0.1652979329017533</v>
       </c>
       <c r="T63">
-        <v>2.649820604006675</v>
+        <v>2.759767503504697</v>
       </c>
       <c r="U63">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V63">
-        <v>0.3</v>
+        <v>0.2756754758522865</v>
       </c>
       <c r="W63">
-        <v>0.063</v>
+        <v>0.1063308401448843</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y63">
-        <v>1.523429211303686</v>
+        <v>0.9189182528409552</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6746,22 +6746,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1287383353924946</v>
+        <v>0.1297483353924946</v>
       </c>
       <c r="C64">
-        <v>-178.8711705780474</v>
+        <v>-254.090585806513</v>
       </c>
       <c r="D64">
-        <v>2555.554829421952</v>
+        <v>2524.808414193487</v>
       </c>
       <c r="E64">
-        <v>1459.326</v>
+        <v>1503.799</v>
       </c>
       <c r="F64">
-        <v>2757.326</v>
+        <v>2801.799</v>
       </c>
       <c r="G64">
         <v>22.9</v>
@@ -6782,37 +6782,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M64">
-        <v>404.7754568</v>
+        <v>411.3040932</v>
       </c>
       <c r="N64">
-        <v>-32.81990124444445</v>
+        <v>-39.34853764444443</v>
       </c>
       <c r="O64">
-        <v>-9.845970373333335</v>
+        <v>-11.80456129333333</v>
       </c>
       <c r="P64">
-        <v>-22.97393087111111</v>
+        <v>-27.54397635111111</v>
       </c>
       <c r="Q64">
-        <v>73.62606912888884</v>
+        <v>69.05602364888887</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1652979329017533</v>
+        <v>0.1685276067639629</v>
       </c>
       <c r="T64">
-        <v>2.759767503504697</v>
+        <v>2.834355814410229</v>
       </c>
       <c r="U64">
         <v>0.1468</v>
       </c>
       <c r="V64">
-        <v>0.2756754758522865</v>
+        <v>0.271299674648282</v>
       </c>
       <c r="W64">
-        <v>0.1063308401448843</v>
+        <v>0.1069732077616322</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.9189182528409552</v>
+        <v>0.9043322488276068</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6828,22 +6828,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1297483353924946</v>
+        <v>0.1307583353924946</v>
       </c>
       <c r="C65">
-        <v>-254.090585806513</v>
+        <v>-328.5789631859625</v>
       </c>
       <c r="D65">
-        <v>2524.808414193487</v>
+        <v>2494.793036814038</v>
       </c>
       <c r="E65">
-        <v>1503.799</v>
+        <v>1548.272</v>
       </c>
       <c r="F65">
-        <v>2801.799</v>
+        <v>2846.272</v>
       </c>
       <c r="G65">
         <v>22.9</v>
@@ -6864,37 +6864,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M65">
-        <v>411.3040932</v>
+        <v>417.8327296000001</v>
       </c>
       <c r="N65">
-        <v>-39.34853764444443</v>
+        <v>-45.87717404444453</v>
       </c>
       <c r="O65">
-        <v>-11.80456129333333</v>
+        <v>-13.76315221333336</v>
       </c>
       <c r="P65">
-        <v>-27.54397635111111</v>
+        <v>-32.11402183111117</v>
       </c>
       <c r="Q65">
-        <v>69.05602364888887</v>
+        <v>64.48597816888879</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1685276067639629</v>
+        <v>0.1719367069518508</v>
       </c>
       <c r="T65">
-        <v>2.834355814410229</v>
+        <v>2.91308792036607</v>
       </c>
       <c r="U65">
         <v>0.1468</v>
       </c>
       <c r="V65">
-        <v>0.271299674648282</v>
+        <v>0.2670606172319026</v>
       </c>
       <c r="W65">
-        <v>0.1069732077616322</v>
+        <v>0.1075955013903567</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.9043322488276068</v>
+        <v>0.8902020574396752</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6910,22 +6910,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1307583353924946</v>
+        <v>0.1317683353924946</v>
       </c>
       <c r="C66">
-        <v>-328.5789631859625</v>
+        <v>-402.3620685367077</v>
       </c>
       <c r="D66">
-        <v>2494.793036814038</v>
+        <v>2465.482931463293</v>
       </c>
       <c r="E66">
-        <v>1548.272</v>
+        <v>1592.745</v>
       </c>
       <c r="F66">
-        <v>2846.272</v>
+        <v>2890.745</v>
       </c>
       <c r="G66">
         <v>22.9</v>
@@ -6946,37 +6946,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M66">
-        <v>417.8327296000001</v>
+        <v>424.3613660000001</v>
       </c>
       <c r="N66">
-        <v>-45.87717404444453</v>
+        <v>-52.40581044444451</v>
       </c>
       <c r="O66">
-        <v>-13.76315221333336</v>
+        <v>-15.72174313333335</v>
       </c>
       <c r="P66">
-        <v>-32.11402183111117</v>
+        <v>-36.68406731111116</v>
       </c>
       <c r="Q66">
-        <v>64.48597816888879</v>
+        <v>59.91593268888881</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1719367069518508</v>
+        <v>0.1755406128647608</v>
       </c>
       <c r="T66">
-        <v>2.91308792036607</v>
+        <v>2.996319003805101</v>
       </c>
       <c r="U66">
         <v>0.1468</v>
       </c>
       <c r="V66">
-        <v>0.2670606172319026</v>
+        <v>0.2629519923514118</v>
       </c>
       <c r="W66">
-        <v>0.1075955013903567</v>
+        <v>0.1081986475228128</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6984,7 +6984,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.8902020574396752</v>
+        <v>0.8765066411713726</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6992,22 +6992,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1317683353924946</v>
+        <v>0.1327783353924946</v>
       </c>
       <c r="C67">
-        <v>-402.3620685367077</v>
+        <v>-475.4644708992723</v>
       </c>
       <c r="D67">
-        <v>2465.482931463293</v>
+        <v>2436.853529100728</v>
       </c>
       <c r="E67">
-        <v>1592.745</v>
+        <v>1637.218</v>
       </c>
       <c r="F67">
-        <v>2890.745</v>
+        <v>2935.218</v>
       </c>
       <c r="G67">
         <v>22.9</v>
@@ -7028,37 +7028,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M67">
-        <v>424.3613660000001</v>
+        <v>430.8900024000001</v>
       </c>
       <c r="N67">
-        <v>-52.40581044444451</v>
+        <v>-58.93444684444449</v>
       </c>
       <c r="O67">
-        <v>-15.72174313333335</v>
+        <v>-17.68033405333335</v>
       </c>
       <c r="P67">
-        <v>-36.68406731111116</v>
+        <v>-41.25411279111115</v>
       </c>
       <c r="Q67">
-        <v>59.91593268888881</v>
+        <v>55.34588720888882</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1755406128647608</v>
+        <v>0.1793565132431361</v>
       </c>
       <c r="T67">
-        <v>2.996319003805101</v>
+        <v>3.08444603332878</v>
       </c>
       <c r="U67">
         <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.2629519923514118</v>
+        <v>0.2589678712551783</v>
       </c>
       <c r="W67">
-        <v>0.1081986475228128</v>
+        <v>0.1087835164997398</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -7066,7 +7066,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.8765066411713726</v>
+        <v>0.8632262375172609</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7074,22 +7074,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1327783353924946</v>
+        <v>0.1337883353924946</v>
       </c>
       <c r="C68">
-        <v>-475.4644708992723</v>
+        <v>-547.9096112223369</v>
       </c>
       <c r="D68">
-        <v>2436.853529100728</v>
+        <v>2408.881388777663</v>
       </c>
       <c r="E68">
-        <v>1637.218</v>
+        <v>1681.691</v>
       </c>
       <c r="F68">
-        <v>2935.218</v>
+        <v>2979.691</v>
       </c>
       <c r="G68">
         <v>22.9</v>
@@ -7110,37 +7110,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M68">
-        <v>430.8900024000001</v>
+        <v>437.4186388000001</v>
       </c>
       <c r="N68">
-        <v>-58.93444684444449</v>
+        <v>-65.46308324444448</v>
       </c>
       <c r="O68">
-        <v>-17.68033405333335</v>
+        <v>-19.63892497333334</v>
       </c>
       <c r="P68">
-        <v>-41.25411279111115</v>
+        <v>-45.82415827111113</v>
       </c>
       <c r="Q68">
-        <v>55.34588720888882</v>
+        <v>50.77584172888884</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1793565132431361</v>
+        <v>0.18340368031111</v>
       </c>
       <c r="T68">
-        <v>3.08444603332878</v>
+        <v>3.177914094944804</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.2589678712551783</v>
+        <v>0.255102679146892</v>
       </c>
       <c r="W68">
-        <v>0.1087835164997398</v>
+        <v>0.1093509267012363</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7148,7 +7148,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.8632262375172609</v>
+        <v>0.8503422638229734</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7156,22 +7156,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1337883353924946</v>
+        <v>0.1347983353924946</v>
       </c>
       <c r="C69">
-        <v>-547.9096112223369</v>
+        <v>-619.7198663736353</v>
       </c>
       <c r="D69">
-        <v>2408.881388777663</v>
+        <v>2381.544133626365</v>
       </c>
       <c r="E69">
-        <v>1681.691</v>
+        <v>1726.164</v>
       </c>
       <c r="F69">
-        <v>2979.691</v>
+        <v>3024.164</v>
       </c>
       <c r="G69">
         <v>22.9</v>
@@ -7192,37 +7192,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M69">
-        <v>437.4186388000001</v>
+        <v>443.9472752000001</v>
       </c>
       <c r="N69">
-        <v>-65.46308324444448</v>
+        <v>-71.99171964444452</v>
       </c>
       <c r="O69">
-        <v>-19.63892497333334</v>
+        <v>-21.59751589333336</v>
       </c>
       <c r="P69">
-        <v>-45.82415827111113</v>
+        <v>-50.39420375111116</v>
       </c>
       <c r="Q69">
-        <v>50.77584172888884</v>
+        <v>46.2057962488888</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.18340368031111</v>
+        <v>0.1877037953208322</v>
       </c>
       <c r="T69">
-        <v>3.177914094944804</v>
+        <v>3.277223910411829</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.255102679146892</v>
+        <v>0.2513511691594377</v>
       </c>
       <c r="W69">
-        <v>0.1093509267012363</v>
+        <v>0.1099016483673946</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -7230,7 +7230,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.8503422638229734</v>
+        <v>0.8378372305314591</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7238,22 +7238,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1347983353924946</v>
+        <v>0.1358083353924946</v>
       </c>
       <c r="C70">
-        <v>-619.7198663736353</v>
+        <v>-690.9166088411939</v>
       </c>
       <c r="D70">
-        <v>2381.544133626365</v>
+        <v>2354.820391158806</v>
       </c>
       <c r="E70">
-        <v>1726.164</v>
+        <v>1770.637</v>
       </c>
       <c r="F70">
-        <v>3024.164</v>
+        <v>3068.637</v>
       </c>
       <c r="G70">
         <v>22.9</v>
@@ -7274,37 +7274,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M70">
-        <v>443.9472752000001</v>
+        <v>450.4759116000001</v>
       </c>
       <c r="N70">
-        <v>-71.99171964444452</v>
+        <v>-78.5203560444445</v>
       </c>
       <c r="O70">
-        <v>-21.59751589333336</v>
+        <v>-23.55610681333335</v>
       </c>
       <c r="P70">
-        <v>-50.39420375111116</v>
+        <v>-54.96424923111115</v>
       </c>
       <c r="Q70">
-        <v>46.2057962488888</v>
+        <v>41.63575076888881</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1877037953208322</v>
+        <v>0.1922813371053751</v>
       </c>
       <c r="T70">
-        <v>3.277223910411829</v>
+        <v>3.382940810747695</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.2513511691594377</v>
+        <v>0.2477083985919097</v>
       </c>
       <c r="W70">
-        <v>0.1099016483673946</v>
+        <v>0.1104364070867077</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8378372305314591</v>
+        <v>0.8256946619730321</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7320,22 +7320,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1358083353924946</v>
+        <v>0.1368183353924946</v>
       </c>
       <c r="C71">
-        <v>-690.9166088411939</v>
+        <v>-761.5202624596573</v>
       </c>
       <c r="D71">
-        <v>2354.820391158806</v>
+        <v>2328.689737540343</v>
       </c>
       <c r="E71">
-        <v>1770.637</v>
+        <v>1815.110000000001</v>
       </c>
       <c r="F71">
-        <v>3068.637</v>
+        <v>3113.110000000001</v>
       </c>
       <c r="G71">
         <v>22.9</v>
@@ -7356,37 +7356,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M71">
-        <v>450.4759116000001</v>
+        <v>457.0045480000001</v>
       </c>
       <c r="N71">
-        <v>-78.5203560444445</v>
+        <v>-85.04899244444454</v>
       </c>
       <c r="O71">
-        <v>-23.55610681333335</v>
+        <v>-25.51469773333336</v>
       </c>
       <c r="P71">
-        <v>-54.96424923111115</v>
+        <v>-59.53429471111117</v>
       </c>
       <c r="Q71">
-        <v>41.63575076888881</v>
+        <v>37.06570528888879</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1922813371053751</v>
+        <v>0.197164048342221</v>
       </c>
       <c r="T71">
-        <v>3.382940810747695</v>
+        <v>3.495705504439285</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2477083985919097</v>
+        <v>0.2441697071834538</v>
       </c>
       <c r="W71">
-        <v>0.1104364070867077</v>
+        <v>0.110955886985469</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8256946619730321</v>
+        <v>0.8138990239448459</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7402,22 +7402,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1368183353924946</v>
+        <v>0.1378283353924946</v>
       </c>
       <c r="C72">
-        <v>-761.5202624596573</v>
+        <v>-831.5503544670773</v>
       </c>
       <c r="D72">
-        <v>2328.689737540343</v>
+        <v>2303.132645532923</v>
       </c>
       <c r="E72">
-        <v>1815.110000000001</v>
+        <v>1859.583000000001</v>
       </c>
       <c r="F72">
-        <v>3113.110000000001</v>
+        <v>3157.583000000001</v>
       </c>
       <c r="G72">
         <v>22.9</v>
@@ -7438,37 +7438,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M72">
-        <v>457.0045480000001</v>
+        <v>463.5331844000001</v>
       </c>
       <c r="N72">
-        <v>-85.04899244444454</v>
+        <v>-91.57762884444452</v>
       </c>
       <c r="O72">
-        <v>-25.51469773333336</v>
+        <v>-27.47328865333336</v>
       </c>
       <c r="P72">
-        <v>-59.53429471111117</v>
+        <v>-64.10434019111116</v>
       </c>
       <c r="Q72">
-        <v>37.06570528888879</v>
+        <v>32.4956598088888</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.197164048342221</v>
+        <v>0.2023834982850562</v>
       </c>
       <c r="T72">
-        <v>3.495705504439285</v>
+        <v>3.61624707355788</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2441697071834538</v>
+        <v>0.2407306972231234</v>
       </c>
       <c r="W72">
-        <v>0.110955886985469</v>
+        <v>0.1114607336476455</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8138990239448459</v>
+        <v>0.8024356574104115</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7484,22 +7484,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1378283353924946</v>
+        <v>0.1802358198227287</v>
       </c>
       <c r="C73">
-        <v>-831.5503544670769</v>
+        <v>-1602.541494758795</v>
       </c>
       <c r="D73">
-        <v>2303.132645532923</v>
+        <v>1576.614505241205</v>
       </c>
       <c r="E73">
-        <v>1859.583</v>
+        <v>1904.056</v>
       </c>
       <c r="F73">
-        <v>3157.583</v>
+        <v>3202.056</v>
       </c>
       <c r="G73">
         <v>22.9</v>
@@ -7520,45 +7520,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M73">
-        <v>463.5331844</v>
+        <v>642.9728448000001</v>
       </c>
       <c r="N73">
-        <v>-91.57762884444446</v>
+        <v>-271.0172892444445</v>
       </c>
       <c r="O73">
-        <v>-27.47328865333334</v>
+        <v>-81.30518677333335</v>
       </c>
       <c r="P73">
-        <v>-64.10434019111112</v>
+        <v>-189.7121024711112</v>
       </c>
       <c r="Q73">
-        <v>32.49565980888885</v>
+        <v>-93.1121024711112</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2023834982850561</v>
+        <v>0.2169667819032155</v>
       </c>
       <c r="T73">
-        <v>3.616247073557879</v>
+        <v>3.953043461968027</v>
       </c>
       <c r="U73">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V73">
-        <v>0.2407306972231235</v>
+        <v>0.1735480239470708</v>
       </c>
       <c r="W73">
-        <v>0.1114607336476455</v>
+        <v>0.1659515567914282</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y73">
-        <v>0.8024356574104116</v>
+        <v>0.5784934131569028</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7566,22 +7566,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1802358198227287</v>
+        <v>0.1817858198227286</v>
       </c>
       <c r="C74">
-        <v>-1602.541494758795</v>
+        <v>-1664.985136744183</v>
       </c>
       <c r="D74">
-        <v>1576.614505241205</v>
+        <v>1558.643863255817</v>
       </c>
       <c r="E74">
-        <v>1904.056</v>
+        <v>1948.529</v>
       </c>
       <c r="F74">
-        <v>3202.056</v>
+        <v>3246.529</v>
       </c>
       <c r="G74">
         <v>22.9</v>
@@ -7602,37 +7602,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M74">
-        <v>642.9728448000001</v>
+        <v>651.9030232</v>
       </c>
       <c r="N74">
-        <v>-271.0172892444445</v>
+        <v>-279.9474676444444</v>
       </c>
       <c r="O74">
-        <v>-81.30518677333335</v>
+        <v>-83.98424029333333</v>
       </c>
       <c r="P74">
-        <v>-189.7121024711112</v>
+        <v>-195.9632273511111</v>
       </c>
       <c r="Q74">
-        <v>-93.1121024711112</v>
+        <v>-99.36322735111114</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2169667819032155</v>
+        <v>0.2233062923440753</v>
       </c>
       <c r="T74">
-        <v>3.953043461968027</v>
+        <v>4.099452479077954</v>
       </c>
       <c r="U74">
         <v>0.2008</v>
       </c>
       <c r="V74">
-        <v>0.1735480239470708</v>
+        <v>0.1711706537560151</v>
       </c>
       <c r="W74">
-        <v>0.1659515567914282</v>
+        <v>0.1664289327257922</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.5784934131569028</v>
+        <v>0.5705688458533836</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7648,22 +7648,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1817858198227286</v>
+        <v>0.1833358198227286</v>
       </c>
       <c r="C75">
-        <v>-1664.985136744183</v>
+        <v>-1727.023727956425</v>
       </c>
       <c r="D75">
-        <v>1558.643863255817</v>
+        <v>1541.078272043575</v>
       </c>
       <c r="E75">
-        <v>1948.529</v>
+        <v>1993.002</v>
       </c>
       <c r="F75">
-        <v>3246.529</v>
+        <v>3291.002</v>
       </c>
       <c r="G75">
         <v>22.9</v>
@@ -7684,37 +7684,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M75">
-        <v>651.9030232</v>
+        <v>660.8332016000001</v>
       </c>
       <c r="N75">
-        <v>-279.9474676444444</v>
+        <v>-288.8776460444445</v>
       </c>
       <c r="O75">
-        <v>-83.98424029333333</v>
+        <v>-86.66329381333334</v>
       </c>
       <c r="P75">
-        <v>-195.9632273511111</v>
+        <v>-202.2143522311111</v>
       </c>
       <c r="Q75">
-        <v>-99.36322735111114</v>
+        <v>-105.6143522311112</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2233062923440753</v>
+        <v>0.2301334574342321</v>
       </c>
       <c r="T75">
-        <v>4.099452479077954</v>
+        <v>4.25712372827326</v>
       </c>
       <c r="U75">
         <v>0.2008</v>
       </c>
       <c r="V75">
-        <v>0.1711706537560151</v>
+        <v>0.1688575368133662</v>
       </c>
       <c r="W75">
-        <v>0.1664289327257922</v>
+        <v>0.1668934066078761</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7722,7 +7722,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.5705688458533836</v>
+        <v>0.5628584560445541</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7730,22 +7730,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1833358198227286</v>
+        <v>0.1848858198227286</v>
       </c>
       <c r="C76">
-        <v>-1727.023727956425</v>
+        <v>-1788.670810294308</v>
       </c>
       <c r="D76">
-        <v>1541.078272043575</v>
+        <v>1523.904189705692</v>
       </c>
       <c r="E76">
-        <v>1993.002</v>
+        <v>2037.475</v>
       </c>
       <c r="F76">
-        <v>3291.002</v>
+        <v>3335.475</v>
       </c>
       <c r="G76">
         <v>22.9</v>
@@ -7766,37 +7766,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M76">
-        <v>660.8332016000001</v>
+        <v>669.7633800000001</v>
       </c>
       <c r="N76">
-        <v>-288.8776460444445</v>
+        <v>-297.8078244444445</v>
       </c>
       <c r="O76">
-        <v>-86.66329381333334</v>
+        <v>-89.34234733333335</v>
       </c>
       <c r="P76">
-        <v>-202.2143522311111</v>
+        <v>-208.4654771111112</v>
       </c>
       <c r="Q76">
-        <v>-105.6143522311112</v>
+        <v>-111.8654771111112</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2301334574342321</v>
+        <v>0.2375067957316014</v>
       </c>
       <c r="T76">
-        <v>4.25712372827326</v>
+        <v>4.42740867740419</v>
       </c>
       <c r="U76">
         <v>0.2008</v>
       </c>
       <c r="V76">
-        <v>0.1688575368133662</v>
+        <v>0.166606102989188</v>
       </c>
       <c r="W76">
-        <v>0.1668934066078761</v>
+        <v>0.1673454945197711</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7804,7 +7804,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.5628584560445541</v>
+        <v>0.5553536766306266</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7812,22 +7812,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1848858198227286</v>
+        <v>0.1864358198227286</v>
       </c>
       <c r="C77">
-        <v>-1788.670810294308</v>
+        <v>-1849.939328655286</v>
       </c>
       <c r="D77">
-        <v>1523.904189705692</v>
+        <v>1507.108671344714</v>
       </c>
       <c r="E77">
-        <v>2037.475</v>
+        <v>2081.948</v>
       </c>
       <c r="F77">
-        <v>3335.475</v>
+        <v>3379.948</v>
       </c>
       <c r="G77">
         <v>22.9</v>
@@ -7848,37 +7848,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M77">
-        <v>669.7633800000001</v>
+        <v>678.6935584</v>
       </c>
       <c r="N77">
-        <v>-297.8078244444445</v>
+        <v>-306.7380028444445</v>
       </c>
       <c r="O77">
-        <v>-89.34234733333335</v>
+        <v>-92.02140085333333</v>
       </c>
       <c r="P77">
-        <v>-208.4654771111112</v>
+        <v>-214.7166019911111</v>
       </c>
       <c r="Q77">
-        <v>-111.8654771111112</v>
+        <v>-118.1166019911112</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2375067957316014</v>
+        <v>0.2454945788870848</v>
       </c>
       <c r="T77">
-        <v>4.42740867740419</v>
+        <v>4.611884038962699</v>
       </c>
       <c r="U77">
         <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.166606102989188</v>
+        <v>0.1644139174235408</v>
       </c>
       <c r="W77">
-        <v>0.1673454945197711</v>
+        <v>0.167785685381353</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7886,7 +7886,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.5553536766306266</v>
+        <v>0.5480463914118027</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7894,22 +7894,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1864358198227286</v>
+        <v>0.1879858198227286</v>
       </c>
       <c r="C78">
-        <v>-1849.939328655286</v>
+        <v>-1910.841663475712</v>
       </c>
       <c r="D78">
-        <v>1507.108671344714</v>
+        <v>1490.679336524289</v>
       </c>
       <c r="E78">
-        <v>2081.948</v>
+        <v>2126.421</v>
       </c>
       <c r="F78">
-        <v>3379.948</v>
+        <v>3424.421</v>
       </c>
       <c r="G78">
         <v>22.9</v>
@@ -7930,37 +7930,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M78">
-        <v>678.6935584</v>
+        <v>687.6237368000001</v>
       </c>
       <c r="N78">
-        <v>-306.7380028444445</v>
+        <v>-315.6681812444445</v>
       </c>
       <c r="O78">
-        <v>-92.02140085333333</v>
+        <v>-94.70045437333334</v>
       </c>
       <c r="P78">
-        <v>-214.7166019911111</v>
+        <v>-220.9677268711112</v>
       </c>
       <c r="Q78">
-        <v>-118.1166019911112</v>
+        <v>-124.3677268711112</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2454945788870848</v>
+        <v>0.2541769518821754</v>
       </c>
       <c r="T78">
-        <v>4.611884038962699</v>
+        <v>4.812400736308903</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1644139174235408</v>
+        <v>0.1622786717427156</v>
       </c>
       <c r="W78">
-        <v>0.167785685381353</v>
+        <v>0.1682144427140627</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5480463914118027</v>
+        <v>0.540928905809052</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7976,22 +7976,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1879858198227286</v>
+        <v>0.1895358198227287</v>
       </c>
       <c r="C79">
-        <v>-1910.841663475712</v>
+        <v>-1971.389661165657</v>
       </c>
       <c r="D79">
-        <v>1490.679336524289</v>
+        <v>1474.604338834343</v>
       </c>
       <c r="E79">
-        <v>2126.421</v>
+        <v>2170.894</v>
       </c>
       <c r="F79">
-        <v>3424.421</v>
+        <v>3468.894</v>
       </c>
       <c r="G79">
         <v>22.9</v>
@@ -8012,37 +8012,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M79">
-        <v>687.6237368000001</v>
+        <v>696.5539152000001</v>
       </c>
       <c r="N79">
-        <v>-315.6681812444445</v>
+        <v>-324.5983596444445</v>
       </c>
       <c r="O79">
-        <v>-94.70045437333334</v>
+        <v>-97.37950789333335</v>
       </c>
       <c r="P79">
-        <v>-220.9677268711112</v>
+        <v>-227.2188517511112</v>
       </c>
       <c r="Q79">
-        <v>-124.3677268711112</v>
+        <v>-130.6188517511112</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2541769518821754</v>
+        <v>0.2636486315131834</v>
       </c>
       <c r="T79">
-        <v>4.812400736308903</v>
+        <v>5.031146224322944</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1622786717427156</v>
+        <v>0.1601981759511423</v>
       </c>
       <c r="W79">
-        <v>0.1682144427140627</v>
+        <v>0.1686322062690106</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -8050,7 +8050,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.540928905809052</v>
+        <v>0.5339939198371411</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8058,22 +8058,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1895358198227287</v>
+        <v>0.1910858198227287</v>
       </c>
       <c r="C80">
-        <v>-1971.389661165657</v>
+        <v>-2031.594662595542</v>
       </c>
       <c r="D80">
-        <v>1474.604338834343</v>
+        <v>1458.872337404458</v>
       </c>
       <c r="E80">
-        <v>2170.894</v>
+        <v>2215.367</v>
       </c>
       <c r="F80">
-        <v>3468.894</v>
+        <v>3513.367</v>
       </c>
       <c r="G80">
         <v>22.9</v>
@@ -8094,37 +8094,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M80">
-        <v>696.5539152000001</v>
+        <v>705.4840936000001</v>
       </c>
       <c r="N80">
-        <v>-324.5983596444445</v>
+        <v>-333.5285380444445</v>
       </c>
       <c r="O80">
-        <v>-97.37950789333335</v>
+        <v>-100.0585614133333</v>
       </c>
       <c r="P80">
-        <v>-227.2188517511112</v>
+        <v>-233.4699766311111</v>
       </c>
       <c r="Q80">
-        <v>-130.6188517511112</v>
+        <v>-136.8699766311112</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2636486315131834</v>
+        <v>0.274022375870954</v>
       </c>
       <c r="T80">
-        <v>5.031146224322944</v>
+        <v>5.27072461595737</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1601981759511423</v>
+        <v>0.1581703509391025</v>
       </c>
       <c r="W80">
-        <v>0.1686322062690106</v>
+        <v>0.1690393935314282</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5339939198371411</v>
+        <v>0.5272345031303418</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8140,22 +8140,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1910858198227287</v>
+        <v>0.1926358198227286</v>
       </c>
       <c r="C81">
-        <v>-2031.594662595542</v>
+        <v>-2091.467529778541</v>
       </c>
       <c r="D81">
-        <v>1458.872337404458</v>
+        <v>1443.472470221459</v>
       </c>
       <c r="E81">
-        <v>2215.367</v>
+        <v>2259.84</v>
       </c>
       <c r="F81">
-        <v>3513.367</v>
+        <v>3557.84</v>
       </c>
       <c r="G81">
         <v>22.9</v>
@@ -8176,37 +8176,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M81">
-        <v>705.4840936000001</v>
+        <v>714.4142720000001</v>
       </c>
       <c r="N81">
-        <v>-333.5285380444445</v>
+        <v>-342.4587164444445</v>
       </c>
       <c r="O81">
-        <v>-100.0585614133333</v>
+        <v>-102.7376149333333</v>
       </c>
       <c r="P81">
-        <v>-233.4699766311111</v>
+        <v>-239.7211015111112</v>
       </c>
       <c r="Q81">
-        <v>-136.8699766311112</v>
+        <v>-143.1211015111112</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.274022375870954</v>
+        <v>0.2854334946645017</v>
       </c>
       <c r="T81">
-        <v>5.27072461595737</v>
+        <v>5.534260846755239</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1581703509391025</v>
+        <v>0.1561932215523638</v>
       </c>
       <c r="W81">
-        <v>0.1690393935314282</v>
+        <v>0.1694364011122854</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -8214,7 +8214,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5272345031303418</v>
+        <v>0.5206440718412124</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8222,22 +8222,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1926358198227286</v>
+        <v>0.1941858198227286</v>
       </c>
       <c r="C82">
-        <v>-2091.467529778541</v>
+        <v>-2151.018670880678</v>
       </c>
       <c r="D82">
-        <v>1443.472470221459</v>
+        <v>1428.394329119322</v>
       </c>
       <c r="E82">
-        <v>2259.84</v>
+        <v>2304.313000000001</v>
       </c>
       <c r="F82">
-        <v>3557.84</v>
+        <v>3602.313000000001</v>
       </c>
       <c r="G82">
         <v>22.9</v>
@@ -8258,37 +8258,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M82">
-        <v>714.4142720000001</v>
+        <v>723.3444504000001</v>
       </c>
       <c r="N82">
-        <v>-342.4587164444445</v>
+        <v>-351.3888948444446</v>
       </c>
       <c r="O82">
-        <v>-102.7376149333333</v>
+        <v>-105.4166684533334</v>
       </c>
       <c r="P82">
-        <v>-239.7211015111112</v>
+        <v>-245.9722263911112</v>
       </c>
       <c r="Q82">
-        <v>-143.1211015111112</v>
+        <v>-149.3722263911112</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2854334946645017</v>
+        <v>0.2980457838573703</v>
       </c>
       <c r="T82">
-        <v>5.534260846755239</v>
+        <v>5.825537733426568</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1561932215523638</v>
+        <v>0.154264910175174</v>
       </c>
       <c r="W82">
-        <v>0.1694364011122854</v>
+        <v>0.1698236060368251</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5206440718412124</v>
+        <v>0.5142163672505802</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8304,22 +8304,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1941858198227286</v>
+        <v>0.1957358198227286</v>
       </c>
       <c r="C83">
-        <v>-2151.018670880678</v>
+        <v>-2210.258063679627</v>
       </c>
       <c r="D83">
-        <v>1428.394329119322</v>
+        <v>1413.627936320373</v>
       </c>
       <c r="E83">
-        <v>2304.313000000001</v>
+        <v>2348.786000000001</v>
       </c>
       <c r="F83">
-        <v>3602.313000000001</v>
+        <v>3646.786000000001</v>
       </c>
       <c r="G83">
         <v>22.9</v>
@@ -8340,37 +8340,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M83">
-        <v>723.3444504000001</v>
+        <v>732.2746288000001</v>
       </c>
       <c r="N83">
-        <v>-351.3888948444446</v>
+        <v>-360.3190732444445</v>
       </c>
       <c r="O83">
-        <v>-105.4166684533334</v>
+        <v>-108.0957219733333</v>
       </c>
       <c r="P83">
-        <v>-245.9722263911112</v>
+        <v>-252.2233512711111</v>
       </c>
       <c r="Q83">
-        <v>-149.3722263911112</v>
+        <v>-155.6233512711112</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2980457838573703</v>
+        <v>0.3120594385161131</v>
       </c>
       <c r="T83">
-        <v>5.825537733426568</v>
+        <v>6.149178718616933</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.154264910175174</v>
+        <v>0.1523836307827939</v>
       </c>
       <c r="W83">
-        <v>0.1698236060368251</v>
+        <v>0.170201366938815</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5142163672505802</v>
+        <v>0.5079454359426463</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8386,22 +8386,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1957358198227286</v>
+        <v>0.1972858198227286</v>
       </c>
       <c r="C84">
-        <v>-2210.258063679627</v>
+        <v>-2269.195277583349</v>
       </c>
       <c r="D84">
-        <v>1413.627936320373</v>
+        <v>1399.163722416651</v>
       </c>
       <c r="E84">
-        <v>2348.786000000001</v>
+        <v>2393.259</v>
       </c>
       <c r="F84">
-        <v>3646.786000000001</v>
+        <v>3691.259</v>
       </c>
       <c r="G84">
         <v>22.9</v>
@@ -8422,37 +8422,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M84">
-        <v>732.2746288000001</v>
+        <v>741.2048072000001</v>
       </c>
       <c r="N84">
-        <v>-360.3190732444445</v>
+        <v>-369.2492516444445</v>
       </c>
       <c r="O84">
-        <v>-108.0957219733333</v>
+        <v>-110.7747754933334</v>
       </c>
       <c r="P84">
-        <v>-252.2233512711111</v>
+        <v>-258.4744761511112</v>
       </c>
       <c r="Q84">
-        <v>-155.6233512711112</v>
+        <v>-161.8744761511112</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3120594385161131</v>
+        <v>0.3277217584288257</v>
       </c>
       <c r="T84">
-        <v>6.149178718616933</v>
+        <v>6.510895113829695</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1523836307827939</v>
+        <v>0.150547683423965</v>
       </c>
       <c r="W84">
-        <v>0.170201366938815</v>
+        <v>0.1705700251684678</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5079454359426463</v>
+        <v>0.5018256114132169</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8468,22 +8468,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1972858198227286</v>
+        <v>0.2292516551981678</v>
       </c>
       <c r="C85">
-        <v>-2269.195277583349</v>
+        <v>-2557.467861543189</v>
       </c>
       <c r="D85">
-        <v>1399.163722416651</v>
+        <v>1155.364138456811</v>
       </c>
       <c r="E85">
-        <v>2393.259</v>
+        <v>2437.732</v>
       </c>
       <c r="F85">
-        <v>3691.259</v>
+        <v>3735.732</v>
       </c>
       <c r="G85">
         <v>22.9</v>
@@ -8504,45 +8504,45 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M85">
-        <v>741.2048072000001</v>
+        <v>880.8856056000002</v>
       </c>
       <c r="N85">
-        <v>-369.2492516444445</v>
+        <v>-508.9300500444446</v>
       </c>
       <c r="O85">
-        <v>-110.7747754933334</v>
+        <v>-152.6790150133334</v>
       </c>
       <c r="P85">
-        <v>-258.4744761511112</v>
+        <v>-356.2510350311112</v>
       </c>
       <c r="Q85">
-        <v>-161.8744761511112</v>
+        <v>-259.6510350311112</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3277217584288257</v>
+        <v>0.3516908394271224</v>
       </c>
       <c r="T85">
-        <v>6.510895113829695</v>
+        <v>7.064453566446248</v>
       </c>
       <c r="U85">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.150547683423965</v>
+        <v>0.1266755478319586</v>
       </c>
       <c r="W85">
-        <v>0.1705700251684678</v>
+        <v>0.2059299058212241</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y85">
-        <v>0.5018256114132169</v>
+        <v>0.4222518261065288</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8550,22 +8550,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2292516551981678</v>
+        <v>0.2311516551981679</v>
       </c>
       <c r="C86">
-        <v>-2557.467861543189</v>
+        <v>-2613.784251129977</v>
       </c>
       <c r="D86">
-        <v>1155.364138456811</v>
+        <v>1143.520748870023</v>
       </c>
       <c r="E86">
-        <v>2437.732</v>
+        <v>2482.205</v>
       </c>
       <c r="F86">
-        <v>3735.732</v>
+        <v>3780.205</v>
       </c>
       <c r="G86">
         <v>22.9</v>
@@ -8586,37 +8586,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M86">
-        <v>880.8856056000001</v>
+        <v>891.372339</v>
       </c>
       <c r="N86">
-        <v>-508.9300500444445</v>
+        <v>-519.4167834444445</v>
       </c>
       <c r="O86">
-        <v>-152.6790150133334</v>
+        <v>-155.8250350333333</v>
       </c>
       <c r="P86">
-        <v>-356.2510350311111</v>
+        <v>-363.5917484111112</v>
       </c>
       <c r="Q86">
-        <v>-259.6510350311112</v>
+        <v>-266.9917484111112</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3516908394271222</v>
+        <v>0.3720835620555971</v>
       </c>
       <c r="T86">
-        <v>7.064453566446243</v>
+        <v>7.53541713754266</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.1266755478319586</v>
+        <v>0.1251852472692297</v>
       </c>
       <c r="W86">
-        <v>0.2059299058212241</v>
+        <v>0.2062813186939156</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8624,7 +8624,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4222518261065288</v>
+        <v>0.4172841575640991</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8632,22 +8632,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2311516551981679</v>
+        <v>0.2330516551981678</v>
       </c>
       <c r="C87">
-        <v>-2613.784251129977</v>
+        <v>-2669.860296350344</v>
       </c>
       <c r="D87">
-        <v>1143.520748870023</v>
+        <v>1131.917703649655</v>
       </c>
       <c r="E87">
-        <v>2482.205</v>
+        <v>2526.678</v>
       </c>
       <c r="F87">
-        <v>3780.205</v>
+        <v>3824.678</v>
       </c>
       <c r="G87">
         <v>22.9</v>
@@ -8668,37 +8668,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M87">
-        <v>891.372339</v>
+        <v>901.8590724000001</v>
       </c>
       <c r="N87">
-        <v>-519.4167834444445</v>
+        <v>-529.9035168444445</v>
       </c>
       <c r="O87">
-        <v>-155.8250350333333</v>
+        <v>-158.9710550533333</v>
       </c>
       <c r="P87">
-        <v>-363.5917484111112</v>
+        <v>-370.9324617911112</v>
       </c>
       <c r="Q87">
-        <v>-266.9917484111112</v>
+        <v>-274.3324617911113</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3720835620555971</v>
+        <v>0.395389530773854</v>
       </c>
       <c r="T87">
-        <v>7.53541713754266</v>
+        <v>8.073661218795706</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1251852472692297</v>
+        <v>0.1237296048591224</v>
       </c>
       <c r="W87">
-        <v>0.2062813186939156</v>
+        <v>0.2066245591742189</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4172841575640991</v>
+        <v>0.4124320161970746</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8714,22 +8714,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2330516551981678</v>
+        <v>0.2349516551981679</v>
       </c>
       <c r="C88">
-        <v>-2669.860296350344</v>
+        <v>-2725.703239873606</v>
       </c>
       <c r="D88">
-        <v>1131.917703649655</v>
+        <v>1120.547760126395</v>
       </c>
       <c r="E88">
-        <v>2526.678</v>
+        <v>2571.151</v>
       </c>
       <c r="F88">
-        <v>3824.678</v>
+        <v>3869.151</v>
       </c>
       <c r="G88">
         <v>22.9</v>
@@ -8750,37 +8750,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M88">
-        <v>901.8590724000001</v>
+        <v>912.3458058000001</v>
       </c>
       <c r="N88">
-        <v>-529.9035168444445</v>
+        <v>-540.3902502444446</v>
       </c>
       <c r="O88">
-        <v>-158.9710550533333</v>
+        <v>-162.1170750733334</v>
       </c>
       <c r="P88">
-        <v>-370.9324617911112</v>
+        <v>-378.2731751711112</v>
       </c>
       <c r="Q88">
-        <v>-274.3324617911113</v>
+        <v>-281.6731751711113</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.395389530773854</v>
+        <v>0.4222810331410735</v>
       </c>
       <c r="T88">
-        <v>8.073661218795706</v>
+        <v>8.694712081779992</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1237296048591224</v>
+        <v>0.1223074254929256</v>
       </c>
       <c r="W88">
-        <v>0.2066245591742189</v>
+        <v>0.2069599090687682</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8788,7 +8788,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4124320161970746</v>
+        <v>0.4076914183097519</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8796,22 +8796,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2349516551981679</v>
+        <v>0.2368516551981679</v>
       </c>
       <c r="C89">
-        <v>-2725.703239873606</v>
+        <v>-2781.320036257006</v>
       </c>
       <c r="D89">
-        <v>1120.547760126395</v>
+        <v>1109.403963742994</v>
       </c>
       <c r="E89">
-        <v>2571.151</v>
+        <v>2615.624</v>
       </c>
       <c r="F89">
-        <v>3869.151</v>
+        <v>3913.624</v>
       </c>
       <c r="G89">
         <v>22.9</v>
@@ -8832,37 +8832,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M89">
-        <v>912.3458058000001</v>
+        <v>922.8325392</v>
       </c>
       <c r="N89">
-        <v>-540.3902502444446</v>
+        <v>-550.8769836444444</v>
       </c>
       <c r="O89">
-        <v>-162.1170750733334</v>
+        <v>-165.2630950933333</v>
       </c>
       <c r="P89">
-        <v>-378.2731751711112</v>
+        <v>-385.6138885511111</v>
       </c>
       <c r="Q89">
-        <v>-281.6731751711113</v>
+        <v>-289.0138885511112</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4222810331410735</v>
+        <v>0.4536544525694964</v>
       </c>
       <c r="T89">
-        <v>8.694712081779992</v>
+        <v>9.419271421928327</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1223074254929256</v>
+        <v>0.1209175683850514</v>
       </c>
       <c r="W89">
-        <v>0.2069599090687682</v>
+        <v>0.2072876373748049</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4076914183097519</v>
+        <v>0.4030585612835049</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8878,22 +8878,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2368516551981679</v>
+        <v>0.2387516551981679</v>
       </c>
       <c r="C90">
-        <v>-2781.320036257006</v>
+        <v>-2836.717366130968</v>
       </c>
       <c r="D90">
-        <v>1109.403963742994</v>
+        <v>1098.479633869032</v>
       </c>
       <c r="E90">
-        <v>2615.624</v>
+        <v>2660.097</v>
       </c>
       <c r="F90">
-        <v>3913.624</v>
+        <v>3958.097</v>
       </c>
       <c r="G90">
         <v>22.9</v>
@@ -8914,37 +8914,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M90">
-        <v>922.8325392</v>
+        <v>933.3192726000001</v>
       </c>
       <c r="N90">
-        <v>-550.8769836444444</v>
+        <v>-561.3637170444445</v>
       </c>
       <c r="O90">
-        <v>-165.2630950933333</v>
+        <v>-168.4091151133333</v>
       </c>
       <c r="P90">
-        <v>-385.6138885511111</v>
+        <v>-392.9546019311111</v>
       </c>
       <c r="Q90">
-        <v>-289.0138885511112</v>
+        <v>-296.3546019311112</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4536544525694964</v>
+        <v>0.4907321300758142</v>
       </c>
       <c r="T90">
-        <v>9.419271421928327</v>
+        <v>10.27556882392181</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1209175683850514</v>
+        <v>0.1195589440211745</v>
       </c>
       <c r="W90">
-        <v>0.2072876373748049</v>
+        <v>0.2076080009998071</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4030585612835049</v>
+        <v>0.3985298134039149</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8960,22 +8960,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2387516551981679</v>
+        <v>0.2406516551981679</v>
       </c>
       <c r="C91">
-        <v>-2836.717366130968</v>
+        <v>-2891.901649554394</v>
       </c>
       <c r="D91">
-        <v>1098.479633869032</v>
+        <v>1087.768350445606</v>
       </c>
       <c r="E91">
-        <v>2660.097</v>
+        <v>2704.57</v>
       </c>
       <c r="F91">
-        <v>3958.097</v>
+        <v>4002.57</v>
       </c>
       <c r="G91">
         <v>22.9</v>
@@ -8996,37 +8996,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M91">
-        <v>933.3192726000001</v>
+        <v>943.806006</v>
       </c>
       <c r="N91">
-        <v>-561.3637170444445</v>
+        <v>-571.8504504444445</v>
       </c>
       <c r="O91">
-        <v>-168.4091151133333</v>
+        <v>-171.5551351333334</v>
       </c>
       <c r="P91">
-        <v>-392.9546019311111</v>
+        <v>-400.2953153111112</v>
       </c>
       <c r="Q91">
-        <v>-296.3546019311112</v>
+        <v>-303.6953153111112</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4907321300758142</v>
+        <v>0.5352253430833956</v>
       </c>
       <c r="T91">
-        <v>10.27556882392181</v>
+        <v>11.30312570631399</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1195589440211745</v>
+        <v>0.1182305113098281</v>
       </c>
       <c r="W91">
-        <v>0.2076080009998071</v>
+        <v>0.2079212454331426</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.3985298134039149</v>
+        <v>0.3941017043660936</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9042,22 +9042,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2406516551981679</v>
+        <v>0.2425516551981678</v>
       </c>
       <c r="C92">
-        <v>-2891.901649554394</v>
+        <v>-2946.879058596162</v>
       </c>
       <c r="D92">
-        <v>1087.768350445606</v>
+        <v>1077.263941403838</v>
       </c>
       <c r="E92">
-        <v>2704.57</v>
+        <v>2749.043</v>
       </c>
       <c r="F92">
-        <v>4002.57</v>
+        <v>4047.043</v>
       </c>
       <c r="G92">
         <v>22.9</v>
@@ -9078,37 +9078,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M92">
-        <v>943.806006</v>
+        <v>954.2927394000001</v>
       </c>
       <c r="N92">
-        <v>-571.8504504444445</v>
+        <v>-582.3371838444446</v>
       </c>
       <c r="O92">
-        <v>-171.5551351333334</v>
+        <v>-174.7011551533334</v>
       </c>
       <c r="P92">
-        <v>-400.2953153111112</v>
+        <v>-407.6360286911112</v>
       </c>
       <c r="Q92">
-        <v>-303.6953153111112</v>
+        <v>-311.0360286911112</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5352253430833956</v>
+        <v>0.5896059367593286</v>
       </c>
       <c r="T92">
-        <v>11.30312570631399</v>
+        <v>12.55902856257111</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1182305113098281</v>
+        <v>0.116931274921808</v>
       </c>
       <c r="W92">
-        <v>0.2079212454331426</v>
+        <v>0.2082276053734377</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9116,7 +9116,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.3941017043660936</v>
+        <v>0.3897709164060266</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9124,22 +9124,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2425516551981678</v>
+        <v>0.2444516551981679</v>
       </c>
       <c r="C93">
-        <v>-2946.879058596162</v>
+        <v>-3001.655529194611</v>
       </c>
       <c r="D93">
-        <v>1077.263941403838</v>
+        <v>1066.96047080539</v>
       </c>
       <c r="E93">
-        <v>2749.043</v>
+        <v>2793.516000000001</v>
       </c>
       <c r="F93">
-        <v>4047.043</v>
+        <v>4091.516000000001</v>
       </c>
       <c r="G93">
         <v>22.9</v>
@@ -9160,37 +9160,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M93">
-        <v>954.2927394000001</v>
+        <v>964.7794728000001</v>
       </c>
       <c r="N93">
-        <v>-582.3371838444446</v>
+        <v>-592.8239172444446</v>
       </c>
       <c r="O93">
-        <v>-174.7011551533334</v>
+        <v>-177.8471751733334</v>
       </c>
       <c r="P93">
-        <v>-407.6360286911112</v>
+        <v>-414.9767420711112</v>
       </c>
       <c r="Q93">
-        <v>-311.0360286911112</v>
+        <v>-318.3767420711113</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5896059367593286</v>
+        <v>0.6575816788542448</v>
       </c>
       <c r="T93">
-        <v>12.55902856257111</v>
+        <v>14.1289071328925</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.116931274921808</v>
+        <v>0.1156602828030927</v>
       </c>
       <c r="W93">
-        <v>0.2082276053734377</v>
+        <v>0.2085273053150307</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.3897709164060266</v>
+        <v>0.3855342760103089</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9206,22 +9206,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2444516551981679</v>
+        <v>0.2463516551981679</v>
       </c>
       <c r="C94">
-        <v>-3001.655529194611</v>
+        <v>-3056.236772342877</v>
       </c>
       <c r="D94">
-        <v>1066.96047080539</v>
+        <v>1056.852227657124</v>
       </c>
       <c r="E94">
-        <v>2793.516000000001</v>
+        <v>2837.989</v>
       </c>
       <c r="F94">
-        <v>4091.516000000001</v>
+        <v>4135.989</v>
       </c>
       <c r="G94">
         <v>22.9</v>
@@ -9242,37 +9242,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M94">
-        <v>964.7794728000001</v>
+        <v>975.2662062000002</v>
       </c>
       <c r="N94">
-        <v>-592.8239172444446</v>
+        <v>-603.3106506444446</v>
       </c>
       <c r="O94">
-        <v>-177.8471751733334</v>
+        <v>-180.9931951933334</v>
       </c>
       <c r="P94">
-        <v>-414.9767420711112</v>
+        <v>-422.3174554511113</v>
       </c>
       <c r="Q94">
-        <v>-318.3767420711113</v>
+        <v>-325.7174554511113</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6575816788542448</v>
+        <v>0.7449790615477085</v>
       </c>
       <c r="T94">
-        <v>14.1289071328925</v>
+        <v>16.14732243759143</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.1156602828030927</v>
+        <v>0.1144166238482207</v>
       </c>
       <c r="W94">
-        <v>0.2085273053150307</v>
+        <v>0.2088205600965896</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9280,7 +9280,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3855342760103089</v>
+        <v>0.3813887461607356</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9288,22 +9288,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2463516551981679</v>
+        <v>0.2482516551981679</v>
       </c>
       <c r="C95">
-        <v>-3056.236772342877</v>
+        <v>-3110.628284644408</v>
       </c>
       <c r="D95">
-        <v>1056.852227657124</v>
+        <v>1046.933715355592</v>
       </c>
       <c r="E95">
-        <v>2837.989</v>
+        <v>2882.462</v>
       </c>
       <c r="F95">
-        <v>4135.989</v>
+        <v>4180.462</v>
       </c>
       <c r="G95">
         <v>22.9</v>
@@ -9324,37 +9324,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M95">
-        <v>975.2662062000002</v>
+        <v>985.7529396000001</v>
       </c>
       <c r="N95">
-        <v>-603.3106506444446</v>
+        <v>-613.7973840444445</v>
       </c>
       <c r="O95">
-        <v>-180.9931951933334</v>
+        <v>-184.1392152133333</v>
       </c>
       <c r="P95">
-        <v>-422.3174554511113</v>
+        <v>-429.6581688311111</v>
       </c>
       <c r="Q95">
-        <v>-325.7174554511113</v>
+        <v>-333.0581688311112</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7449790615477085</v>
+        <v>0.8615089051389934</v>
       </c>
       <c r="T95">
-        <v>16.14732243759143</v>
+        <v>18.83854284385667</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.1144166238482207</v>
+        <v>0.1131994257221758</v>
       </c>
       <c r="W95">
-        <v>0.2088205600965896</v>
+        <v>0.209107575414711</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3813887461607356</v>
+        <v>0.3773314190739194</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9370,22 +9370,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2482516551981679</v>
+        <v>0.2501516551981678</v>
       </c>
       <c r="C96">
-        <v>-3110.628284644408</v>
+        <v>-3164.835358279616</v>
       </c>
       <c r="D96">
-        <v>1046.933715355592</v>
+        <v>1037.199641720384</v>
       </c>
       <c r="E96">
-        <v>2882.462</v>
+        <v>2926.935</v>
       </c>
       <c r="F96">
-        <v>4180.462</v>
+        <v>4224.935</v>
       </c>
       <c r="G96">
         <v>22.9</v>
@@ -9406,37 +9406,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M96">
-        <v>985.7529396000001</v>
+        <v>996.2396730000002</v>
       </c>
       <c r="N96">
-        <v>-613.7973840444445</v>
+        <v>-624.2841174444445</v>
       </c>
       <c r="O96">
-        <v>-184.1392152133333</v>
+        <v>-187.2852352333333</v>
       </c>
       <c r="P96">
-        <v>-429.6581688311111</v>
+        <v>-436.9988822111112</v>
       </c>
       <c r="Q96">
-        <v>-333.0581688311112</v>
+        <v>-340.3988822111112</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8615089051389934</v>
+        <v>1.024650686166793</v>
       </c>
       <c r="T96">
-        <v>18.83854284385667</v>
+        <v>22.60625141262801</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1131994257221758</v>
+        <v>0.1120078528198371</v>
       </c>
       <c r="W96">
-        <v>0.209107575414711</v>
+        <v>0.2093885483050824</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3773314190739194</v>
+        <v>0.3733595093994571</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9452,22 +9452,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2501516551981678</v>
+        <v>0.2520516551981679</v>
       </c>
       <c r="C97">
-        <v>-3164.835358279616</v>
+        <v>-3218.863090421646</v>
       </c>
       <c r="D97">
-        <v>1037.199641720384</v>
+        <v>1027.644909578354</v>
       </c>
       <c r="E97">
-        <v>2926.935</v>
+        <v>2971.408</v>
       </c>
       <c r="F97">
-        <v>4224.935</v>
+        <v>4269.408</v>
       </c>
       <c r="G97">
         <v>22.9</v>
@@ -9488,37 +9488,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M97">
-        <v>996.2396730000002</v>
+        <v>1006.7264064</v>
       </c>
       <c r="N97">
-        <v>-624.2841174444445</v>
+        <v>-634.7708508444446</v>
       </c>
       <c r="O97">
-        <v>-187.2852352333333</v>
+        <v>-190.4312552533334</v>
       </c>
       <c r="P97">
-        <v>-436.9988822111112</v>
+        <v>-444.3395955911112</v>
       </c>
       <c r="Q97">
-        <v>-340.3988822111112</v>
+        <v>-347.7395955911113</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.024650686166793</v>
+        <v>1.269363357708491</v>
       </c>
       <c r="T97">
-        <v>22.60625141262801</v>
+        <v>28.25781426578503</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.1120078528198371</v>
+        <v>0.1108411043529638</v>
       </c>
       <c r="W97">
-        <v>0.2093885483050824</v>
+        <v>0.2096636675935711</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9526,7 +9526,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3733595093994571</v>
+        <v>0.3694703478432126</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9534,22 +9534,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2520516551981679</v>
+        <v>0.2539516551981679</v>
       </c>
       <c r="C98">
-        <v>-3218.863090421646</v>
+        <v>-3272.71639213647</v>
       </c>
       <c r="D98">
-        <v>1027.644909578354</v>
+        <v>1018.26460786353</v>
       </c>
       <c r="E98">
-        <v>2971.408</v>
+        <v>3015.881</v>
       </c>
       <c r="F98">
-        <v>4269.408</v>
+        <v>4313.881</v>
       </c>
       <c r="G98">
         <v>22.9</v>
@@ -9570,37 +9570,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M98">
-        <v>1006.7264064</v>
+        <v>1017.2131398</v>
       </c>
       <c r="N98">
-        <v>-634.7708508444446</v>
+        <v>-645.2575842444446</v>
       </c>
       <c r="O98">
-        <v>-190.4312552533334</v>
+        <v>-193.5772752733334</v>
       </c>
       <c r="P98">
-        <v>-444.3395955911112</v>
+        <v>-451.6803089711112</v>
       </c>
       <c r="Q98">
-        <v>-347.7395955911113</v>
+        <v>-355.0803089711113</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.269363357708488</v>
+        <v>1.677217810277984</v>
       </c>
       <c r="T98">
-        <v>28.25781426578495</v>
+        <v>37.67708568771327</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1108411043529638</v>
+        <v>0.1096984125555106</v>
       </c>
       <c r="W98">
-        <v>0.2096636675935711</v>
+        <v>0.2099331143194106</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9608,7 +9608,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3694703478432126</v>
+        <v>0.3656613751850352</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9616,22 +9616,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2539516551981679</v>
+        <v>0.2558516551981679</v>
       </c>
       <c r="C99">
-        <v>-3272.71639213647</v>
+        <v>-3326.399996799953</v>
       </c>
       <c r="D99">
-        <v>1018.26460786353</v>
+        <v>1009.054003200047</v>
       </c>
       <c r="E99">
-        <v>3015.881</v>
+        <v>3060.354</v>
       </c>
       <c r="F99">
-        <v>4313.881</v>
+        <v>4358.354</v>
       </c>
       <c r="G99">
         <v>22.9</v>
@@ -9652,37 +9652,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M99">
-        <v>1017.2131398</v>
+        <v>1027.6998732</v>
       </c>
       <c r="N99">
-        <v>-645.2575842444446</v>
+        <v>-655.7443176444447</v>
       </c>
       <c r="O99">
-        <v>-193.5772752733334</v>
+        <v>-196.7232952933334</v>
       </c>
       <c r="P99">
-        <v>-451.6803089711112</v>
+        <v>-459.0210223511112</v>
       </c>
       <c r="Q99">
-        <v>-355.0803089711113</v>
+        <v>-362.4210223511113</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.677217810277984</v>
+        <v>2.492926715416976</v>
       </c>
       <c r="T99">
-        <v>37.67708568771327</v>
+        <v>56.51562853156991</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.1096984125555106</v>
+        <v>0.1085790409988217</v>
       </c>
       <c r="W99">
-        <v>0.2099331143194106</v>
+        <v>0.2101970621324779</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9690,7 +9690,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3656613751850352</v>
+        <v>0.3619301366627389</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9698,22 +9698,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2558516551981679</v>
+        <v>0.2577516551981678</v>
       </c>
       <c r="C100">
-        <v>-3326.399996799953</v>
+        <v>-3379.918468062197</v>
       </c>
       <c r="D100">
-        <v>1009.054003200047</v>
+        <v>1000.008531937803</v>
       </c>
       <c r="E100">
-        <v>3060.354</v>
+        <v>3104.827</v>
       </c>
       <c r="F100">
-        <v>4358.354</v>
+        <v>4402.827</v>
       </c>
       <c r="G100">
         <v>22.9</v>
@@ -9734,37 +9734,37 @@
         <v>371.9555555555556</v>
       </c>
       <c r="M100">
-        <v>1027.6998732</v>
+        <v>1038.1866066</v>
       </c>
       <c r="N100">
-        <v>-655.7443176444447</v>
+        <v>-666.2310510444445</v>
       </c>
       <c r="O100">
-        <v>-196.7232952933334</v>
+        <v>-199.8693153133333</v>
       </c>
       <c r="P100">
-        <v>-459.0210223511112</v>
+        <v>-466.3617357311111</v>
       </c>
       <c r="Q100">
-        <v>-362.4210223511113</v>
+        <v>-369.7617357311112</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.492926715416976</v>
+        <v>4.940053430833952</v>
       </c>
       <c r="T100">
-        <v>56.51562853156991</v>
+        <v>113.0312570631398</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.1085790409988217</v>
+        <v>0.1074822830089346</v>
       </c>
       <c r="W100">
-        <v>0.2101970621324779</v>
+        <v>0.2104556776664932</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9772,91 +9772,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3619301366627389</v>
+        <v>0.3582742766964487</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2577516551981678</v>
-      </c>
-      <c r="C101">
-        <v>-3379.918468062197</v>
-      </c>
-      <c r="D101">
-        <v>1000.008531937803</v>
-      </c>
-      <c r="E101">
-        <v>3104.827</v>
-      </c>
-      <c r="F101">
-        <v>4402.827</v>
-      </c>
-      <c r="G101">
-        <v>22.9</v>
-      </c>
-      <c r="H101">
-        <v>3149.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>468.5555555555555</v>
-      </c>
-      <c r="K101">
-        <v>96.59999999999997</v>
-      </c>
-      <c r="L101">
-        <v>371.9555555555556</v>
-      </c>
-      <c r="M101">
-        <v>1038.1866066</v>
-      </c>
-      <c r="N101">
-        <v>-666.2310510444445</v>
-      </c>
-      <c r="O101">
-        <v>-199.8693153133333</v>
-      </c>
-      <c r="P101">
-        <v>-466.3617357311111</v>
-      </c>
-      <c r="Q101">
-        <v>-369.7617357311112</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.940053430833952</v>
-      </c>
-      <c r="T101">
-        <v>113.0312570631398</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.1074822830089346</v>
-      </c>
-      <c r="W101">
-        <v>0.2104556776664932</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3582742766964487</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
